--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_transportation.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_transportation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="plse_wassel" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00756</v>
+        <v>0.218</v>
       </c>
       <c r="E2">
-        <v>1.038</v>
+        <v>0.221</v>
       </c>
       <c r="G2">
-        <v>-0.01993127147766323</v>
+        <v>0.01385321100917431</v>
       </c>
       <c r="H2">
-        <v>-0.01993127147766323</v>
+        <v>0.01385321100917431</v>
       </c>
       <c r="I2">
-        <v>-0.005383734249713631</v>
+        <v>0.05385321100917431</v>
       </c>
       <c r="J2">
-        <v>-0.005018273059510173</v>
+        <v>0.04281552809159147</v>
       </c>
       <c r="K2">
-        <v>0.902</v>
+        <v>0.961</v>
       </c>
       <c r="L2">
-        <v>0.1033218785796105</v>
+        <v>0.0881651376146789</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="V2">
-        <v>0.2732491389207807</v>
+        <v>0.1065693430656934</v>
       </c>
       <c r="W2">
-        <v>0.1389830508474576</v>
+        <v>0.1300405953991881</v>
       </c>
       <c r="X2">
-        <v>0.0673243337017066</v>
+        <v>0.1152375424639012</v>
       </c>
       <c r="Y2">
-        <v>0.07165871714575103</v>
+        <v>0.01480305293528685</v>
       </c>
       <c r="Z2">
-        <v>1.450166112956811</v>
+        <v>1.76948051948052</v>
       </c>
       <c r="AA2">
-        <v>-0.00727732953646575</v>
+        <v>0.07576124288934206</v>
       </c>
       <c r="AB2">
-        <v>0.06314411093515408</v>
+        <v>0.1105442774892637</v>
       </c>
       <c r="AC2">
-        <v>-0.07042144047161983</v>
+        <v>-0.03478303459992164</v>
       </c>
       <c r="AD2">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AG2">
-        <v>-1.23</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="AH2">
-        <v>0.1166328600405679</v>
+        <v>0.09331568497683652</v>
       </c>
       <c r="AI2">
-        <v>0.1351351351351351</v>
+        <v>0.1391905231984205</v>
       </c>
       <c r="AJ2">
-        <v>-0.1644385026737968</v>
+        <v>-0.003663003663003666</v>
       </c>
       <c r="AK2">
-        <v>-0.200652528548124</v>
+        <v>-0.005767012687427918</v>
       </c>
       <c r="AL2">
-        <v>0.083</v>
+        <v>0.093</v>
       </c>
       <c r="AM2">
-        <v>-0.16</v>
+        <v>-0.064</v>
       </c>
       <c r="AN2">
-        <v>9.829059829059828</v>
+        <v>1.78030303030303</v>
       </c>
       <c r="AO2">
-        <v>-0.5662650602409638</v>
+        <v>6.311827956989247</v>
       </c>
       <c r="AP2">
-        <v>-10.51282051282051</v>
+        <v>-0.06313131313131319</v>
       </c>
       <c r="AQ2">
-        <v>0.2937500000000001</v>
+        <v>-9.171875</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00756</v>
+        <v>0.218</v>
       </c>
       <c r="E3">
-        <v>1.038</v>
+        <v>0.221</v>
       </c>
       <c r="G3">
-        <v>-0.01993127147766323</v>
+        <v>0.01385321100917431</v>
       </c>
       <c r="H3">
-        <v>-0.01993127147766323</v>
+        <v>0.01385321100917431</v>
       </c>
       <c r="I3">
-        <v>-0.005383734249713631</v>
+        <v>0.05385321100917431</v>
       </c>
       <c r="J3">
-        <v>-0.005018273059510173</v>
+        <v>0.04281552809159147</v>
       </c>
       <c r="K3">
-        <v>0.902</v>
+        <v>0.961</v>
       </c>
       <c r="L3">
-        <v>0.1033218785796105</v>
+        <v>0.0881651376146789</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +766,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="V3">
-        <v>0.2732491389207807</v>
+        <v>0.1065693430656934</v>
       </c>
       <c r="W3">
-        <v>0.1389830508474576</v>
+        <v>0.1300405953991881</v>
       </c>
       <c r="X3">
-        <v>0.0673243337017066</v>
+        <v>0.1152375424639012</v>
       </c>
       <c r="Y3">
-        <v>0.07165871714575103</v>
+        <v>0.01480305293528685</v>
       </c>
       <c r="Z3">
-        <v>1.450166112956811</v>
+        <v>1.76948051948052</v>
       </c>
       <c r="AA3">
-        <v>-0.00727732953646575</v>
+        <v>0.07576124288934206</v>
       </c>
       <c r="AB3">
-        <v>0.06314411093515408</v>
+        <v>0.1105442774892637</v>
       </c>
       <c r="AC3">
-        <v>-0.07042144047161983</v>
+        <v>-0.03478303459992164</v>
       </c>
       <c r="AD3">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AG3">
-        <v>-1.23</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="AH3">
-        <v>0.1166328600405679</v>
+        <v>0.09331568497683652</v>
       </c>
       <c r="AI3">
-        <v>0.1351351351351351</v>
+        <v>0.1391905231984205</v>
       </c>
       <c r="AJ3">
-        <v>-0.1644385026737968</v>
+        <v>-0.003663003663003666</v>
       </c>
       <c r="AK3">
-        <v>-0.200652528548124</v>
+        <v>-0.005767012687427918</v>
       </c>
       <c r="AL3">
-        <v>0.083</v>
+        <v>0.093</v>
       </c>
       <c r="AM3">
-        <v>-0.16</v>
+        <v>-0.064</v>
       </c>
       <c r="AN3">
-        <v>9.829059829059828</v>
+        <v>1.78030303030303</v>
       </c>
       <c r="AO3">
-        <v>-0.5662650602409638</v>
+        <v>6.311827956989247</v>
       </c>
       <c r="AP3">
-        <v>-10.51282051282051</v>
+        <v>-0.06313131313131319</v>
       </c>
       <c r="AQ3">
-        <v>0.2937500000000001</v>
+        <v>-9.171875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The Palestinian Company for Distribution &amp; Logistics Services LLC (PLSE:WASSEL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PLSE:WASSEL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Palestinian Authority</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0933156849768365</v>
+      </c>
+      <c r="F2">
+        <v>0.08</v>
+      </c>
+      <c r="G2">
+        <v>13.7</v>
+      </c>
+      <c r="H2">
+        <v>14.3313724468196</v>
+      </c>
+      <c r="I2">
+        <v>13.65</v>
+      </c>
+      <c r="J2">
+        <v>14.0801724468196</v>
+      </c>
+      <c r="K2">
+        <v>1.41</v>
+      </c>
+      <c r="L2">
+        <v>1.2088</v>
+      </c>
+      <c r="M2">
+        <v>0.110544277489264</v>
+      </c>
+      <c r="N2">
+        <v>0.10835237170761</v>
+      </c>
+      <c r="O2">
+        <v>0.0649430504307288</v>
+      </c>
+      <c r="P2">
+        <v>0.0401192275197843</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.115237542463901</v>
+      </c>
+      <c r="T2">
+        <v>0.114285688593508</v>
+      </c>
+      <c r="U2">
+        <v>0.907756696301206</v>
+      </c>
+      <c r="V2">
+        <v>0.896452673475542</v>
+      </c>
+      <c r="W2">
+        <v>10.37144100416537</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>13.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.08420487865895976</v>
+      </c>
+      <c r="AC2">
+        <v>0.07656693499042704</v>
+      </c>
+      <c r="AD2">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.792</v>
+      </c>
+      <c r="AH2">
+        <v>0.199</v>
+      </c>
+      <c r="AI2">
+        <v>0.143</v>
+      </c>
+      <c r="AJ2">
+        <v>1.41</v>
+      </c>
+      <c r="AK2">
+        <v>1.41</v>
+      </c>
+      <c r="AL2">
+        <v>0.093</v>
+      </c>
+      <c r="AM2">
+        <v>1.41</v>
+      </c>
+      <c r="AN2">
+        <v>1.46</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.109100639677251</v>
+      </c>
+      <c r="C2">
+        <v>15.39030550254509</v>
+      </c>
+      <c r="D2">
+        <v>13.93030550254509</v>
+      </c>
+      <c r="E2">
+        <v>-1.41</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.46</v>
+      </c>
+      <c r="H2">
+        <v>13.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.792</v>
+      </c>
+      <c r="K2">
+        <v>0.199</v>
+      </c>
+      <c r="L2">
+        <v>0.593</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.593</v>
+      </c>
+      <c r="O2">
+        <v>0.09002532940312731</v>
+      </c>
+      <c r="P2">
+        <v>0.5029746705968726</v>
+      </c>
+      <c r="Q2">
+        <v>0.7019746705968726</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.109100639677251</v>
+      </c>
+      <c r="T2">
+        <v>0.8348760879043289</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W2">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1089935351949927</v>
+      </c>
+      <c r="C3">
+        <v>15.26046099501182</v>
+      </c>
+      <c r="D3">
+        <v>13.95156099501182</v>
+      </c>
+      <c r="E3">
+        <v>-1.2589</v>
+      </c>
+      <c r="F3">
+        <v>0.1511</v>
+      </c>
+      <c r="G3">
+        <v>1.46</v>
+      </c>
+      <c r="H3">
+        <v>13.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.792</v>
+      </c>
+      <c r="K3">
+        <v>0.199</v>
+      </c>
+      <c r="L3">
+        <v>0.593</v>
+      </c>
+      <c r="M3">
+        <v>0.00690527</v>
+      </c>
+      <c r="N3">
+        <v>0.58609473</v>
+      </c>
+      <c r="O3">
+        <v>0.0889770170821028</v>
+      </c>
+      <c r="P3">
+        <v>0.4971177129178972</v>
+      </c>
+      <c r="Q3">
+        <v>0.6961177129178973</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1097029433392405</v>
+      </c>
+      <c r="T3">
+        <v>0.842028923601995</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W3">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>85.87643929925984</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1088864307127344</v>
+      </c>
+      <c r="C4">
+        <v>15.13068145179454</v>
+      </c>
+      <c r="D4">
+        <v>13.97288145179454</v>
+      </c>
+      <c r="E4">
+        <v>-1.1078</v>
+      </c>
+      <c r="F4">
+        <v>0.3022</v>
+      </c>
+      <c r="G4">
+        <v>1.46</v>
+      </c>
+      <c r="H4">
+        <v>13.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.792</v>
+      </c>
+      <c r="K4">
+        <v>0.199</v>
+      </c>
+      <c r="L4">
+        <v>0.593</v>
+      </c>
+      <c r="M4">
+        <v>0.01381054</v>
+      </c>
+      <c r="N4">
+        <v>0.5791894599999999</v>
+      </c>
+      <c r="O4">
+        <v>0.08792870476107829</v>
+      </c>
+      <c r="P4">
+        <v>0.4912607552389217</v>
+      </c>
+      <c r="Q4">
+        <v>0.6902607552389217</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1103175389126991</v>
+      </c>
+      <c r="T4">
+        <v>0.8493277355383889</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W4">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>42.93821964962991</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1087793262304761</v>
+      </c>
+      <c r="C5">
+        <v>15.00096717118003</v>
+      </c>
+      <c r="D5">
+        <v>13.99426717118004</v>
+      </c>
+      <c r="E5">
+        <v>-0.9566999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.4533</v>
+      </c>
+      <c r="G5">
+        <v>1.46</v>
+      </c>
+      <c r="H5">
+        <v>13.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.792</v>
+      </c>
+      <c r="K5">
+        <v>0.199</v>
+      </c>
+      <c r="L5">
+        <v>0.593</v>
+      </c>
+      <c r="M5">
+        <v>0.02071581</v>
+      </c>
+      <c r="N5">
+        <v>0.57228419</v>
+      </c>
+      <c r="O5">
+        <v>0.08688039244005379</v>
+      </c>
+      <c r="P5">
+        <v>0.4854037975599462</v>
+      </c>
+      <c r="Q5">
+        <v>0.6844037975599462</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1109448065598373</v>
+      </c>
+      <c r="T5">
+        <v>0.8567770384425437</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W5">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>28.62547976641994</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1086722217482178</v>
+      </c>
+      <c r="C6">
+        <v>14.87131845328403</v>
+      </c>
+      <c r="D6">
+        <v>14.01571845328403</v>
+      </c>
+      <c r="E6">
+        <v>-0.8056</v>
+      </c>
+      <c r="F6">
+        <v>0.6043999999999999</v>
+      </c>
+      <c r="G6">
+        <v>1.46</v>
+      </c>
+      <c r="H6">
+        <v>13.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.792</v>
+      </c>
+      <c r="K6">
+        <v>0.199</v>
+      </c>
+      <c r="L6">
+        <v>0.593</v>
+      </c>
+      <c r="M6">
+        <v>0.02762108</v>
+      </c>
+      <c r="N6">
+        <v>0.56537892</v>
+      </c>
+      <c r="O6">
+        <v>0.08583208011902929</v>
+      </c>
+      <c r="P6">
+        <v>0.4795468398809707</v>
+      </c>
+      <c r="Q6">
+        <v>0.6785468398809706</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1115851422829575</v>
+      </c>
+      <c r="T6">
+        <v>0.8643815351572017</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W6">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>21.46910982481496</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1085651172659595</v>
+      </c>
+      <c r="C7">
+        <v>14.7417356000652</v>
+      </c>
+      <c r="D7">
+        <v>14.0372356000652</v>
+      </c>
+      <c r="E7">
+        <v>-0.6544999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.7555000000000001</v>
+      </c>
+      <c r="G7">
+        <v>1.46</v>
+      </c>
+      <c r="H7">
+        <v>13.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.792</v>
+      </c>
+      <c r="K7">
+        <v>0.199</v>
+      </c>
+      <c r="L7">
+        <v>0.593</v>
+      </c>
+      <c r="M7">
+        <v>0.03452635</v>
+      </c>
+      <c r="N7">
+        <v>0.5584736499999999</v>
+      </c>
+      <c r="O7">
+        <v>0.08478376779800477</v>
+      </c>
+      <c r="P7">
+        <v>0.4736898822019951</v>
+      </c>
+      <c r="Q7">
+        <v>0.6726898822019951</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1122389587581435</v>
+      </c>
+      <c r="T7">
+        <v>0.8721461265395366</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W7">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>17.17528785985196</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1084580127837011</v>
+      </c>
+      <c r="C8">
+        <v>14.61221891533937</v>
+      </c>
+      <c r="D8">
+        <v>14.05881891533937</v>
+      </c>
+      <c r="E8">
+        <v>-0.5034</v>
+      </c>
+      <c r="F8">
+        <v>0.9066</v>
+      </c>
+      <c r="G8">
+        <v>1.46</v>
+      </c>
+      <c r="H8">
+        <v>13.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.792</v>
+      </c>
+      <c r="K8">
+        <v>0.199</v>
+      </c>
+      <c r="L8">
+        <v>0.593</v>
+      </c>
+      <c r="M8">
+        <v>0.04143162</v>
+      </c>
+      <c r="N8">
+        <v>0.55156838</v>
+      </c>
+      <c r="O8">
+        <v>0.08373545547698026</v>
+      </c>
+      <c r="P8">
+        <v>0.4678329245230197</v>
+      </c>
+      <c r="Q8">
+        <v>0.6668329245230198</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1129066862221631</v>
+      </c>
+      <c r="T8">
+        <v>0.880075921993836</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W8">
+        <v>0.03876212891446389</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>14.31273988320997</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1084459052038153</v>
+      </c>
+      <c r="C9">
+        <v>14.46356296818958</v>
+      </c>
+      <c r="D9">
+        <v>14.06126296818958</v>
+      </c>
+      <c r="E9">
+        <v>-0.3522999999999998</v>
+      </c>
+      <c r="F9">
+        <v>1.0577</v>
+      </c>
+      <c r="G9">
+        <v>1.46</v>
+      </c>
+      <c r="H9">
+        <v>13.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.792</v>
+      </c>
+      <c r="K9">
+        <v>0.199</v>
+      </c>
+      <c r="L9">
+        <v>0.593</v>
+      </c>
+      <c r="M9">
+        <v>0.05002921</v>
+      </c>
+      <c r="N9">
+        <v>0.5429707899999999</v>
+      </c>
+      <c r="O9">
+        <v>0.08243022635080313</v>
+      </c>
+      <c r="P9">
+        <v>0.4605405636491968</v>
+      </c>
+      <c r="Q9">
+        <v>0.6595405636491969</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1135887734165918</v>
+      </c>
+      <c r="T9">
+        <v>0.888176250683712</v>
+      </c>
+      <c r="U9">
+        <v>0.0473</v>
+      </c>
+      <c r="V9">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W9">
+        <v>0.04011922751978428</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.85307543333185</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1083523717076102</v>
+      </c>
+      <c r="C10">
+        <v>14.33137244681962</v>
+      </c>
+      <c r="D10">
+        <v>14.08017244681963</v>
+      </c>
+      <c r="E10">
+        <v>-0.2012</v>
+      </c>
+      <c r="F10">
+        <v>1.2088</v>
+      </c>
+      <c r="G10">
+        <v>1.46</v>
+      </c>
+      <c r="H10">
+        <v>13.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.792</v>
+      </c>
+      <c r="K10">
+        <v>0.199</v>
+      </c>
+      <c r="L10">
+        <v>0.593</v>
+      </c>
+      <c r="M10">
+        <v>0.05717624</v>
+      </c>
+      <c r="N10">
+        <v>0.53582376</v>
+      </c>
+      <c r="O10">
+        <v>0.08134521162904255</v>
+      </c>
+      <c r="P10">
+        <v>0.4544785483709574</v>
+      </c>
+      <c r="Q10">
+        <v>0.6534785483709574</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1142856885935081</v>
+      </c>
+      <c r="T10">
+        <v>0.8964526734755417</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W10">
+        <v>0.04011922751978428</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>10.37144100416537</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1085489180382923</v>
+      </c>
+      <c r="C11">
+        <v>14.14059575637584</v>
+      </c>
+      <c r="D11">
+        <v>14.04049575637584</v>
+      </c>
+      <c r="E11">
+        <v>-0.05010000000000003</v>
+      </c>
+      <c r="F11">
+        <v>1.3599</v>
+      </c>
+      <c r="G11">
+        <v>1.46</v>
+      </c>
+      <c r="H11">
+        <v>13.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.792</v>
+      </c>
+      <c r="K11">
+        <v>0.199</v>
+      </c>
+      <c r="L11">
+        <v>0.593</v>
+      </c>
+      <c r="M11">
+        <v>0.06949089</v>
+      </c>
+      <c r="N11">
+        <v>0.52350911</v>
+      </c>
+      <c r="O11">
+        <v>0.07947568309154808</v>
+      </c>
+      <c r="P11">
+        <v>0.4440334269084519</v>
+      </c>
+      <c r="Q11">
+        <v>0.6430334269084519</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1149979205874994</v>
+      </c>
+      <c r="T11">
+        <v>0.9049109956693896</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W11">
+        <v>0.04334233670742023</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.533492663570721</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1086487710933453</v>
+      </c>
+      <c r="C12">
+        <v>13.96942401604616</v>
+      </c>
+      <c r="D12">
+        <v>14.02042401604616</v>
+      </c>
+      <c r="E12">
+        <v>0.1010000000000002</v>
+      </c>
+      <c r="F12">
+        <v>1.511</v>
+      </c>
+      <c r="G12">
+        <v>1.46</v>
+      </c>
+      <c r="H12">
+        <v>13.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.792</v>
+      </c>
+      <c r="K12">
+        <v>0.199</v>
+      </c>
+      <c r="L12">
+        <v>0.593</v>
+      </c>
+      <c r="M12">
+        <v>0.08008300000000002</v>
+      </c>
+      <c r="N12">
+        <v>0.512917</v>
+      </c>
+      <c r="O12">
+        <v>0.07786765915929823</v>
+      </c>
+      <c r="P12">
+        <v>0.4350493408407017</v>
+      </c>
+      <c r="Q12">
+        <v>0.6340493408407017</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.115725979959135</v>
+      </c>
+      <c r="T12">
+        <v>0.9135572805786564</v>
+      </c>
+      <c r="U12">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W12">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.404817501841837</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1086035842349548</v>
+      </c>
+      <c r="C13">
+        <v>13.82740003873944</v>
+      </c>
+      <c r="D13">
+        <v>14.02950003873944</v>
+      </c>
+      <c r="E13">
+        <v>0.2521</v>
+      </c>
+      <c r="F13">
+        <v>1.6621</v>
+      </c>
+      <c r="G13">
+        <v>1.46</v>
+      </c>
+      <c r="H13">
+        <v>13.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.792</v>
+      </c>
+      <c r="K13">
+        <v>0.199</v>
+      </c>
+      <c r="L13">
+        <v>0.593</v>
+      </c>
+      <c r="M13">
+        <v>0.0880913</v>
+      </c>
+      <c r="N13">
+        <v>0.5049087</v>
+      </c>
+      <c r="O13">
+        <v>0.07665189213491533</v>
+      </c>
+      <c r="P13">
+        <v>0.4282568078650847</v>
+      </c>
+      <c r="Q13">
+        <v>0.6272568078650846</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1164704002155265</v>
+      </c>
+      <c r="T13">
+        <v>0.92239786402521</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W13">
+        <v>0.0449538913012382</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.731652274401672</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1087619621673623</v>
+      </c>
+      <c r="C14">
+        <v>13.64454044909941</v>
+      </c>
+      <c r="D14">
+        <v>13.99774044909941</v>
+      </c>
+      <c r="E14">
+        <v>0.4032</v>
+      </c>
+      <c r="F14">
+        <v>1.8132</v>
+      </c>
+      <c r="G14">
+        <v>1.46</v>
+      </c>
+      <c r="H14">
+        <v>13.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.792</v>
+      </c>
+      <c r="K14">
+        <v>0.199</v>
+      </c>
+      <c r="L14">
+        <v>0.593</v>
+      </c>
+      <c r="M14">
+        <v>0.099726</v>
+      </c>
+      <c r="N14">
+        <v>0.493274</v>
+      </c>
+      <c r="O14">
+        <v>0.0748855890994911</v>
+      </c>
+      <c r="P14">
+        <v>0.4183884109005089</v>
+      </c>
+      <c r="Q14">
+        <v>0.6173884109005089</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1172317391141086</v>
+      </c>
+      <c r="T14">
+        <v>0.9314393698228216</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W14">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.946292842388144</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1087337390415382</v>
+      </c>
+      <c r="C15">
+        <v>13.49908951055905</v>
+      </c>
+      <c r="D15">
+        <v>14.00338951055905</v>
+      </c>
+      <c r="E15">
+        <v>0.5543</v>
+      </c>
+      <c r="F15">
+        <v>1.9643</v>
+      </c>
+      <c r="G15">
+        <v>1.46</v>
+      </c>
+      <c r="H15">
+        <v>13.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.792</v>
+      </c>
+      <c r="K15">
+        <v>0.199</v>
+      </c>
+      <c r="L15">
+        <v>0.593</v>
+      </c>
+      <c r="M15">
+        <v>0.1080365</v>
+      </c>
+      <c r="N15">
+        <v>0.4849635</v>
+      </c>
+      <c r="O15">
+        <v>0.07362394407418808</v>
+      </c>
+      <c r="P15">
+        <v>0.4113395559258119</v>
+      </c>
+      <c r="Q15">
+        <v>0.6103395559258119</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1180105800563364</v>
+      </c>
+      <c r="T15">
+        <v>0.9406887263284245</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W15">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.488885700665979</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1087055159157141</v>
+      </c>
+      <c r="C16">
+        <v>13.35364313343763</v>
+      </c>
+      <c r="D16">
+        <v>14.00904313343763</v>
+      </c>
+      <c r="E16">
+        <v>0.7054000000000002</v>
+      </c>
+      <c r="F16">
+        <v>2.1154</v>
+      </c>
+      <c r="G16">
+        <v>1.46</v>
+      </c>
+      <c r="H16">
+        <v>13.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.792</v>
+      </c>
+      <c r="K16">
+        <v>0.199</v>
+      </c>
+      <c r="L16">
+        <v>0.593</v>
+      </c>
+      <c r="M16">
+        <v>0.116347</v>
+      </c>
+      <c r="N16">
+        <v>0.476653</v>
+      </c>
+      <c r="O16">
+        <v>0.07236229904888507</v>
+      </c>
+      <c r="P16">
+        <v>0.4042907009511149</v>
+      </c>
+      <c r="Q16">
+        <v>0.6032907009511149</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1188075335786159</v>
+      </c>
+      <c r="T16">
+        <v>0.950153184148111</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W16">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.096822436332694</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1086772927898901</v>
+      </c>
+      <c r="C17">
+        <v>13.20820132326216</v>
+      </c>
+      <c r="D17">
+        <v>14.01470132326216</v>
+      </c>
+      <c r="E17">
+        <v>0.8564999999999998</v>
+      </c>
+      <c r="F17">
+        <v>2.2665</v>
+      </c>
+      <c r="G17">
+        <v>1.46</v>
+      </c>
+      <c r="H17">
+        <v>13.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.792</v>
+      </c>
+      <c r="K17">
+        <v>0.199</v>
+      </c>
+      <c r="L17">
+        <v>0.593</v>
+      </c>
+      <c r="M17">
+        <v>0.1246575</v>
+      </c>
+      <c r="N17">
+        <v>0.4683425</v>
+      </c>
+      <c r="O17">
+        <v>0.07110065402358205</v>
+      </c>
+      <c r="P17">
+        <v>0.3972418459764179</v>
+      </c>
+      <c r="Q17">
+        <v>0.5962418459764179</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1196232389484785</v>
+      </c>
+      <c r="T17">
+        <v>0.9598403350929666</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W17">
+        <v>0.0466502645578887</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.757034273910515</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1091647671340877</v>
+      </c>
+      <c r="C18">
+        <v>12.9600100144305</v>
+      </c>
+      <c r="D18">
+        <v>13.9176100144305</v>
+      </c>
+      <c r="E18">
+        <v>1.0076</v>
+      </c>
+      <c r="F18">
+        <v>2.4176</v>
+      </c>
+      <c r="G18">
+        <v>1.46</v>
+      </c>
+      <c r="H18">
+        <v>13.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.792</v>
+      </c>
+      <c r="K18">
+        <v>0.199</v>
+      </c>
+      <c r="L18">
+        <v>0.593</v>
+      </c>
+      <c r="M18">
+        <v>0.14215488</v>
+      </c>
+      <c r="N18">
+        <v>0.45084512</v>
+      </c>
+      <c r="O18">
+        <v>0.0684443177703077</v>
+      </c>
+      <c r="P18">
+        <v>0.3824008022296923</v>
+      </c>
+      <c r="Q18">
+        <v>0.5814008022296924</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1204583658747664</v>
+      </c>
+      <c r="T18">
+        <v>0.9697581324888902</v>
+      </c>
+      <c r="U18">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W18">
+        <v>0.04987337374552465</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.171506458308008</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1097743803527643</v>
+      </c>
+      <c r="C19">
+        <v>12.68936886458161</v>
+      </c>
+      <c r="D19">
+        <v>13.79806886458161</v>
+      </c>
+      <c r="E19">
+        <v>1.1587</v>
+      </c>
+      <c r="F19">
+        <v>2.5687</v>
+      </c>
+      <c r="G19">
+        <v>1.46</v>
+      </c>
+      <c r="H19">
+        <v>13.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.792</v>
+      </c>
+      <c r="K19">
+        <v>0.199</v>
+      </c>
+      <c r="L19">
+        <v>0.593</v>
+      </c>
+      <c r="M19">
+        <v>0.1618281</v>
+      </c>
+      <c r="N19">
+        <v>0.4311718999999999</v>
+      </c>
+      <c r="O19">
+        <v>0.06545765991040854</v>
+      </c>
+      <c r="P19">
+        <v>0.3657142400895914</v>
+      </c>
+      <c r="Q19">
+        <v>0.5647142400895915</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1213136163414468</v>
+      </c>
+      <c r="T19">
+        <v>0.9799149129545952</v>
+      </c>
+      <c r="U19">
+        <v>0.063</v>
+      </c>
+      <c r="V19">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W19">
+        <v>0.05343575758449069</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.664382143768603</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1108979946682059</v>
+      </c>
+      <c r="C20">
+        <v>12.32323226372966</v>
+      </c>
+      <c r="D20">
+        <v>13.58303226372966</v>
+      </c>
+      <c r="E20">
+        <v>1.3098</v>
+      </c>
+      <c r="F20">
+        <v>2.7198</v>
+      </c>
+      <c r="G20">
+        <v>1.46</v>
+      </c>
+      <c r="H20">
+        <v>13.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.792</v>
+      </c>
+      <c r="K20">
+        <v>0.199</v>
+      </c>
+      <c r="L20">
+        <v>0.593</v>
+      </c>
+      <c r="M20">
+        <v>0.19065798</v>
+      </c>
+      <c r="N20">
+        <v>0.40234202</v>
+      </c>
+      <c r="O20">
+        <v>0.06108089862263007</v>
+      </c>
+      <c r="P20">
+        <v>0.3412611213773699</v>
+      </c>
+      <c r="Q20">
+        <v>0.5402611213773699</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1221897265756072</v>
+      </c>
+      <c r="T20">
+        <v>0.9903194197731221</v>
+      </c>
+      <c r="U20">
+        <v>0.0701</v>
+      </c>
+      <c r="V20">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W20">
+        <v>0.05945788264559995</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.110281562827845</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1144304590080912</v>
+      </c>
+      <c r="C21">
+        <v>11.53771092438536</v>
+      </c>
+      <c r="D21">
+        <v>12.94861092438536</v>
+      </c>
+      <c r="E21">
+        <v>1.4609</v>
+      </c>
+      <c r="F21">
+        <v>2.8709</v>
+      </c>
+      <c r="G21">
+        <v>1.46</v>
+      </c>
+      <c r="H21">
+        <v>13.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.792</v>
+      </c>
+      <c r="K21">
+        <v>0.199</v>
+      </c>
+      <c r="L21">
+        <v>0.593</v>
+      </c>
+      <c r="M21">
+        <v>0.26240026</v>
+      </c>
+      <c r="N21">
+        <v>0.33059974</v>
+      </c>
+      <c r="O21">
+        <v>0.05018946120419603</v>
+      </c>
+      <c r="P21">
+        <v>0.2804102787958039</v>
+      </c>
+      <c r="Q21">
+        <v>0.4794102787958039</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1230874691612283</v>
+      </c>
+      <c r="T21">
+        <v>1.000980827994576</v>
+      </c>
+      <c r="U21">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W21">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.259906297348943</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1147109758149776</v>
+      </c>
+      <c r="C22">
+        <v>11.33876141446765</v>
+      </c>
+      <c r="D22">
+        <v>12.90076141446765</v>
+      </c>
+      <c r="E22">
+        <v>1.612</v>
+      </c>
+      <c r="F22">
+        <v>3.022</v>
+      </c>
+      <c r="G22">
+        <v>1.46</v>
+      </c>
+      <c r="H22">
+        <v>13.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.792</v>
+      </c>
+      <c r="K22">
+        <v>0.199</v>
+      </c>
+      <c r="L22">
+        <v>0.593</v>
+      </c>
+      <c r="M22">
+        <v>0.2762108</v>
+      </c>
+      <c r="N22">
+        <v>0.3167891999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.048092836562147</v>
+      </c>
+      <c r="P22">
+        <v>0.2686963634378529</v>
+      </c>
+      <c r="Q22">
+        <v>0.4676963634378529</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.12400765531149</v>
+      </c>
+      <c r="T22">
+        <v>1.011908771421566</v>
+      </c>
+      <c r="U22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W22">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.146910982481495</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1149914926218639</v>
+      </c>
+      <c r="C23">
+        <v>11.14016424288251</v>
+      </c>
+      <c r="D23">
+        <v>12.85326424288251</v>
+      </c>
+      <c r="E23">
+        <v>1.7631</v>
+      </c>
+      <c r="F23">
+        <v>3.1731</v>
+      </c>
+      <c r="G23">
+        <v>1.46</v>
+      </c>
+      <c r="H23">
+        <v>13.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.792</v>
+      </c>
+      <c r="K23">
+        <v>0.199</v>
+      </c>
+      <c r="L23">
+        <v>0.593</v>
+      </c>
+      <c r="M23">
+        <v>0.29002134</v>
+      </c>
+      <c r="N23">
+        <v>0.30297866</v>
+      </c>
+      <c r="O23">
+        <v>0.04599621192009799</v>
+      </c>
+      <c r="P23">
+        <v>0.2569824480799019</v>
+      </c>
+      <c r="Q23">
+        <v>0.455982448079902</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.124951137313657</v>
+      </c>
+      <c r="T23">
+        <v>1.023113371644176</v>
+      </c>
+      <c r="U23">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W23">
+        <v>0.07752425782892777</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.044677126172853</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.119209291757436</v>
+      </c>
+      <c r="C24">
+        <v>10.31485749851212</v>
+      </c>
+      <c r="D24">
+        <v>12.17905749851212</v>
+      </c>
+      <c r="E24">
+        <v>1.9142</v>
+      </c>
+      <c r="F24">
+        <v>3.3242</v>
+      </c>
+      <c r="G24">
+        <v>1.46</v>
+      </c>
+      <c r="H24">
+        <v>13.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.792</v>
+      </c>
+      <c r="K24">
+        <v>0.199</v>
+      </c>
+      <c r="L24">
+        <v>0.593</v>
+      </c>
+      <c r="M24">
+        <v>0.3739725</v>
+      </c>
+      <c r="N24">
+        <v>0.2190275</v>
+      </c>
+      <c r="O24">
+        <v>0.03325130326449151</v>
+      </c>
+      <c r="P24">
+        <v>0.1857761967355085</v>
+      </c>
+      <c r="Q24">
+        <v>0.3847761967355084</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1259188111620334</v>
+      </c>
+      <c r="T24">
+        <v>1.034605269308391</v>
+      </c>
+      <c r="U24">
+        <v>0.1125</v>
+      </c>
+      <c r="V24">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W24">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.585678091303505</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1196687759428989</v>
+      </c>
+      <c r="C25">
+        <v>10.09455793107509</v>
+      </c>
+      <c r="D25">
+        <v>12.10985793107509</v>
+      </c>
+      <c r="E25">
+        <v>2.0653</v>
+      </c>
+      <c r="F25">
+        <v>3.4753</v>
+      </c>
+      <c r="G25">
+        <v>1.46</v>
+      </c>
+      <c r="H25">
+        <v>13.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.792</v>
+      </c>
+      <c r="K25">
+        <v>0.199</v>
+      </c>
+      <c r="L25">
+        <v>0.593</v>
+      </c>
+      <c r="M25">
+        <v>0.39097125</v>
+      </c>
+      <c r="N25">
+        <v>0.20202875</v>
+      </c>
+      <c r="O25">
+        <v>0.03067066571273534</v>
+      </c>
+      <c r="P25">
+        <v>0.1713580842872647</v>
+      </c>
+      <c r="Q25">
+        <v>0.3703580842872647</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.126911619396082</v>
+      </c>
+      <c r="T25">
+        <v>1.046395657821027</v>
+      </c>
+      <c r="U25">
+        <v>0.1125</v>
+      </c>
+      <c r="V25">
+        <v>0.151813371674751</v>
+      </c>
+      <c r="W25">
+        <v>0.09542099568659052</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>1.516735565594657</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1388841701072513</v>
+      </c>
+      <c r="C26">
+        <v>7.618457951852033</v>
+      </c>
+      <c r="D26">
+        <v>9.784857951852032</v>
+      </c>
+      <c r="E26">
+        <v>2.2164</v>
+      </c>
+      <c r="F26">
+        <v>3.6264</v>
+      </c>
+      <c r="G26">
+        <v>1.46</v>
+      </c>
+      <c r="H26">
+        <v>13.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.792</v>
+      </c>
+      <c r="K26">
+        <v>0.199</v>
+      </c>
+      <c r="L26">
+        <v>0.593</v>
+      </c>
+      <c r="M26">
+        <v>0.71295024</v>
+      </c>
+      <c r="N26">
+        <v>-0.11995024</v>
+      </c>
+      <c r="O26">
+        <v>-0.01821005036759558</v>
+      </c>
+      <c r="P26">
+        <v>-0.1017401896324044</v>
+      </c>
+      <c r="Q26">
+        <v>0.09725981036759559</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1284975878403719</v>
+      </c>
+      <c r="T26">
+        <v>1.065230296259416</v>
+      </c>
+      <c r="U26">
+        <v>0.1966</v>
+      </c>
+      <c r="V26">
+        <v>0.1262715465291481</v>
+      </c>
+      <c r="W26">
+        <v>0.1717750139523695</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8317551025720954</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1449335645609434</v>
+      </c>
+      <c r="C27">
+        <v>6.909641213806268</v>
+      </c>
+      <c r="D27">
+        <v>9.227141213806267</v>
+      </c>
+      <c r="E27">
+        <v>2.3675</v>
+      </c>
+      <c r="F27">
+        <v>3.7775</v>
+      </c>
+      <c r="G27">
+        <v>1.46</v>
+      </c>
+      <c r="H27">
+        <v>13.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.792</v>
+      </c>
+      <c r="K27">
+        <v>0.199</v>
+      </c>
+      <c r="L27">
+        <v>0.593</v>
+      </c>
+      <c r="M27">
+        <v>0.8076294999999999</v>
+      </c>
+      <c r="N27">
+        <v>-0.2146294999999999</v>
+      </c>
+      <c r="O27">
+        <v>-0.03258362805586595</v>
+      </c>
+      <c r="P27">
+        <v>-0.182045871944134</v>
+      </c>
+      <c r="Q27">
+        <v>0.01695412805586605</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1299220816164997</v>
+      </c>
+      <c r="T27">
+        <v>1.08214729440506</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.1114685996525973</v>
+      </c>
+      <c r="W27">
+        <v>0.1899680133942747</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.7342475726802946</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1466835645609435</v>
+      </c>
+      <c r="C28">
+        <v>6.608865985796541</v>
+      </c>
+      <c r="D28">
+        <v>9.077465985796541</v>
+      </c>
+      <c r="E28">
+        <v>2.5186</v>
+      </c>
+      <c r="F28">
+        <v>3.9286</v>
+      </c>
+      <c r="G28">
+        <v>1.46</v>
+      </c>
+      <c r="H28">
+        <v>13.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.792</v>
+      </c>
+      <c r="K28">
+        <v>0.199</v>
+      </c>
+      <c r="L28">
+        <v>0.593</v>
+      </c>
+      <c r="M28">
+        <v>0.8399346799999999</v>
+      </c>
+      <c r="N28">
+        <v>-0.24693468</v>
+      </c>
+      <c r="O28">
+        <v>-0.03748798635422568</v>
+      </c>
+      <c r="P28">
+        <v>-0.2094466936457743</v>
+      </c>
+      <c r="Q28">
+        <v>-0.01044669364577427</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1311534610978038</v>
+      </c>
+      <c r="T28">
+        <v>1.096770906491615</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.1071813458198051</v>
+      </c>
+      <c r="W28">
+        <v>0.1908846282637257</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.7060072814233602</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1484335645609435</v>
+      </c>
+      <c r="C29">
+        <v>6.312869069065228</v>
+      </c>
+      <c r="D29">
+        <v>8.932569069065229</v>
+      </c>
+      <c r="E29">
+        <v>2.6697</v>
+      </c>
+      <c r="F29">
+        <v>4.0797</v>
+      </c>
+      <c r="G29">
+        <v>1.46</v>
+      </c>
+      <c r="H29">
+        <v>13.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.792</v>
+      </c>
+      <c r="K29">
+        <v>0.199</v>
+      </c>
+      <c r="L29">
+        <v>0.593</v>
+      </c>
+      <c r="M29">
+        <v>0.87223986</v>
+      </c>
+      <c r="N29">
+        <v>-0.27923986</v>
+      </c>
+      <c r="O29">
+        <v>-0.04239234465258542</v>
+      </c>
+      <c r="P29">
+        <v>-0.2368475153474146</v>
+      </c>
+      <c r="Q29">
+        <v>-0.03784751534741457</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1324185770032532</v>
+      </c>
+      <c r="T29">
+        <v>1.111795165484651</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.1032116663449975</v>
+      </c>
+      <c r="W29">
+        <v>0.1917333457354395</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.6798588635928653</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1501835645609435</v>
+      </c>
+      <c r="C30">
+        <v>6.021425240669332</v>
+      </c>
+      <c r="D30">
+        <v>8.792225240669332</v>
+      </c>
+      <c r="E30">
+        <v>2.8208</v>
+      </c>
+      <c r="F30">
+        <v>4.2308</v>
+      </c>
+      <c r="G30">
+        <v>1.46</v>
+      </c>
+      <c r="H30">
+        <v>13.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.792</v>
+      </c>
+      <c r="K30">
+        <v>0.199</v>
+      </c>
+      <c r="L30">
+        <v>0.593</v>
+      </c>
+      <c r="M30">
+        <v>0.90454504</v>
+      </c>
+      <c r="N30">
+        <v>-0.3115450400000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.04729670295094516</v>
+      </c>
+      <c r="P30">
+        <v>-0.2642483370490549</v>
+      </c>
+      <c r="Q30">
+        <v>-0.06524833704905486</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1337188350171872</v>
+      </c>
+      <c r="T30">
+        <v>1.127236765005271</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.09952553540410471</v>
+      </c>
+      <c r="W30">
+        <v>0.1925214405306024</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.6555781898931201</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1519335645609435</v>
+      </c>
+      <c r="C31">
+        <v>5.734323213058131</v>
+      </c>
+      <c r="D31">
+        <v>8.656223213058132</v>
+      </c>
+      <c r="E31">
+        <v>2.9719</v>
+      </c>
+      <c r="F31">
+        <v>4.3819</v>
+      </c>
+      <c r="G31">
+        <v>1.46</v>
+      </c>
+      <c r="H31">
+        <v>13.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.792</v>
+      </c>
+      <c r="K31">
+        <v>0.199</v>
+      </c>
+      <c r="L31">
+        <v>0.593</v>
+      </c>
+      <c r="M31">
+        <v>0.93685022</v>
+      </c>
+      <c r="N31">
+        <v>-0.34385022</v>
+      </c>
+      <c r="O31">
+        <v>-0.05220106124930488</v>
+      </c>
+      <c r="P31">
+        <v>-0.2916491587506951</v>
+      </c>
+      <c r="Q31">
+        <v>-0.09264915875069507</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1350557200174293</v>
+      </c>
+      <c r="T31">
+        <v>1.143113339160275</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.09609362039017007</v>
+      </c>
+      <c r="W31">
+        <v>0.1932551839605816</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.6329720454140471</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1536835645609435</v>
+      </c>
+      <c r="C32">
+        <v>5.451364572696955</v>
+      </c>
+      <c r="D32">
+        <v>8.524364572696953</v>
+      </c>
+      <c r="E32">
+        <v>3.122999999999999</v>
+      </c>
+      <c r="F32">
+        <v>4.532999999999999</v>
+      </c>
+      <c r="G32">
+        <v>1.46</v>
+      </c>
+      <c r="H32">
+        <v>13.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.792</v>
+      </c>
+      <c r="K32">
+        <v>0.199</v>
+      </c>
+      <c r="L32">
+        <v>0.593</v>
+      </c>
+      <c r="M32">
+        <v>0.9691553999999999</v>
+      </c>
+      <c r="N32">
+        <v>-0.3761553999999999</v>
+      </c>
+      <c r="O32">
+        <v>-0.0571054195476646</v>
+      </c>
+      <c r="P32">
+        <v>-0.3190499804523353</v>
+      </c>
+      <c r="Q32">
+        <v>-0.1200499804523353</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.136430801731964</v>
+      </c>
+      <c r="T32">
+        <v>1.159443529719708</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.09289049971049775</v>
+      </c>
+      <c r="W32">
+        <v>0.1939400111618956</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6118729772335789</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1554335645609435</v>
+      </c>
+      <c r="C33">
+        <v>5.172362814241951</v>
+      </c>
+      <c r="D33">
+        <v>8.39646281424195</v>
+      </c>
+      <c r="E33">
+        <v>3.2741</v>
+      </c>
+      <c r="F33">
+        <v>4.6841</v>
+      </c>
+      <c r="G33">
+        <v>1.46</v>
+      </c>
+      <c r="H33">
+        <v>13.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.792</v>
+      </c>
+      <c r="K33">
+        <v>0.199</v>
+      </c>
+      <c r="L33">
+        <v>0.593</v>
+      </c>
+      <c r="M33">
+        <v>1.00146058</v>
+      </c>
+      <c r="N33">
+        <v>-0.4084605800000001</v>
+      </c>
+      <c r="O33">
+        <v>-0.06200977784602436</v>
+      </c>
+      <c r="P33">
+        <v>-0.3464508021539757</v>
+      </c>
+      <c r="Q33">
+        <v>-0.1474508021539757</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1378457408874997</v>
+      </c>
+      <c r="T33">
+        <v>1.176247059135935</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.08989403197790102</v>
+      </c>
+      <c r="W33">
+        <v>0.1945806559631248</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5921351392583021</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1571835645609435</v>
+      </c>
+      <c r="C34">
+        <v>4.89714246037848</v>
+      </c>
+      <c r="D34">
+        <v>8.272342460378479</v>
+      </c>
+      <c r="E34">
+        <v>3.425199999999999</v>
+      </c>
+      <c r="F34">
+        <v>4.835199999999999</v>
+      </c>
+      <c r="G34">
+        <v>1.46</v>
+      </c>
+      <c r="H34">
+        <v>13.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.792</v>
+      </c>
+      <c r="K34">
+        <v>0.199</v>
+      </c>
+      <c r="L34">
+        <v>0.593</v>
+      </c>
+      <c r="M34">
+        <v>1.03376576</v>
+      </c>
+      <c r="N34">
+        <v>-0.4407657599999999</v>
+      </c>
+      <c r="O34">
+        <v>-0.06691413614438406</v>
+      </c>
+      <c r="P34">
+        <v>-0.3738516238556158</v>
+      </c>
+      <c r="Q34">
+        <v>-0.1748516238556158</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1393022959005512</v>
+      </c>
+      <c r="T34">
+        <v>1.193544810005581</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.08708484347859163</v>
+      </c>
+      <c r="W34">
+        <v>0.1951812604642771</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.5736309161564802</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1589335645609434</v>
+      </c>
+      <c r="C35">
+        <v>4.625538258587994</v>
+      </c>
+      <c r="D35">
+        <v>8.151838258587995</v>
+      </c>
+      <c r="E35">
+        <v>3.5763</v>
+      </c>
+      <c r="F35">
+        <v>4.9863</v>
+      </c>
+      <c r="G35">
+        <v>1.46</v>
+      </c>
+      <c r="H35">
+        <v>13.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.792</v>
+      </c>
+      <c r="K35">
+        <v>0.199</v>
+      </c>
+      <c r="L35">
+        <v>0.593</v>
+      </c>
+      <c r="M35">
+        <v>1.06607094</v>
+      </c>
+      <c r="N35">
+        <v>-0.4730709399999999</v>
+      </c>
+      <c r="O35">
+        <v>-0.0718184944427438</v>
+      </c>
+      <c r="P35">
+        <v>-0.4012524455572561</v>
+      </c>
+      <c r="Q35">
+        <v>-0.2022524455572561</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1408023301677236</v>
+      </c>
+      <c r="T35">
+        <v>1.211358911647456</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.08444590882772522</v>
+      </c>
+      <c r="W35">
+        <v>0.1957454646926323</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5562481611214354</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1606835645609435</v>
+      </c>
+      <c r="C36">
+        <v>4.357394447111704</v>
+      </c>
+      <c r="D36">
+        <v>8.034794447111706</v>
+      </c>
+      <c r="E36">
+        <v>3.7274</v>
+      </c>
+      <c r="F36">
+        <v>5.1374</v>
+      </c>
+      <c r="G36">
+        <v>1.46</v>
+      </c>
+      <c r="H36">
+        <v>13.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.792</v>
+      </c>
+      <c r="K36">
+        <v>0.199</v>
+      </c>
+      <c r="L36">
+        <v>0.593</v>
+      </c>
+      <c r="M36">
+        <v>1.09837612</v>
+      </c>
+      <c r="N36">
+        <v>-0.50537612</v>
+      </c>
+      <c r="O36">
+        <v>-0.07672285274110353</v>
+      </c>
+      <c r="P36">
+        <v>-0.4286532672588965</v>
+      </c>
+      <c r="Q36">
+        <v>-0.2296532672588965</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1423478200187497</v>
+      </c>
+      <c r="T36">
+        <v>1.229712834551205</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.08196220562690977</v>
+      </c>
+      <c r="W36">
+        <v>0.1962764804369667</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.539887921088452</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1624335645609435</v>
+      </c>
+      <c r="C37">
+        <v>4.092564083254771</v>
+      </c>
+      <c r="D37">
+        <v>7.921064083254771</v>
+      </c>
+      <c r="E37">
+        <v>3.8785</v>
+      </c>
+      <c r="F37">
+        <v>5.2885</v>
+      </c>
+      <c r="G37">
+        <v>1.46</v>
+      </c>
+      <c r="H37">
+        <v>13.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.792</v>
+      </c>
+      <c r="K37">
+        <v>0.199</v>
+      </c>
+      <c r="L37">
+        <v>0.593</v>
+      </c>
+      <c r="M37">
+        <v>1.1306813</v>
+      </c>
+      <c r="N37">
+        <v>-0.5376813</v>
+      </c>
+      <c r="O37">
+        <v>-0.08162721103946327</v>
+      </c>
+      <c r="P37">
+        <v>-0.4560540889605368</v>
+      </c>
+      <c r="Q37">
+        <v>-0.2570540889605368</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1439408634036535</v>
+      </c>
+      <c r="T37">
+        <v>1.248631493544301</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.07962042832328377</v>
+      </c>
+      <c r="W37">
+        <v>0.1967771524244819</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5244625519144961</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1641835645609435</v>
+      </c>
+      <c r="C38">
+        <v>3.830908427940332</v>
+      </c>
+      <c r="D38">
+        <v>7.810508427940332</v>
+      </c>
+      <c r="E38">
+        <v>4.029599999999999</v>
+      </c>
+      <c r="F38">
+        <v>5.4396</v>
+      </c>
+      <c r="G38">
+        <v>1.46</v>
+      </c>
+      <c r="H38">
+        <v>13.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.792</v>
+      </c>
+      <c r="K38">
+        <v>0.199</v>
+      </c>
+      <c r="L38">
+        <v>0.593</v>
+      </c>
+      <c r="M38">
+        <v>1.16298648</v>
+      </c>
+      <c r="N38">
+        <v>-0.5699864799999999</v>
+      </c>
+      <c r="O38">
+        <v>-0.08653156933782298</v>
+      </c>
+      <c r="P38">
+        <v>-0.4834549106621769</v>
+      </c>
+      <c r="Q38">
+        <v>-0.2844549106621769</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1455836893943356</v>
+      </c>
+      <c r="T38">
+        <v>1.26814136063093</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.07740874975874812</v>
+      </c>
+      <c r="W38">
+        <v>0.1972500093015797</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.509894147694649</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.175388660715139</v>
+      </c>
+      <c r="C39">
+        <v>3.039070774536237</v>
+      </c>
+      <c r="D39">
+        <v>7.169770774536236</v>
+      </c>
+      <c r="E39">
+        <v>4.1807</v>
+      </c>
+      <c r="F39">
+        <v>5.5907</v>
+      </c>
+      <c r="G39">
+        <v>1.46</v>
+      </c>
+      <c r="H39">
+        <v>13.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.792</v>
+      </c>
+      <c r="K39">
+        <v>0.199</v>
+      </c>
+      <c r="L39">
+        <v>0.593</v>
+      </c>
+      <c r="M39">
+        <v>1.33505916</v>
+      </c>
+      <c r="N39">
+        <v>-0.7420591600000002</v>
+      </c>
+      <c r="O39">
+        <v>-0.1126545030617335</v>
+      </c>
+      <c r="P39">
+        <v>-0.6294046569382666</v>
+      </c>
+      <c r="Q39">
+        <v>-0.4304046569382666</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1476042180421752</v>
+      </c>
+      <c r="T39">
+        <v>1.292136747596844</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0674317154628019</v>
+      </c>
+      <c r="W39">
+        <v>0.2226973063474829</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4441750731106178</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1773886607151391</v>
+      </c>
+      <c r="C40">
+        <v>2.784502413740496</v>
+      </c>
+      <c r="D40">
+        <v>7.066302413740495</v>
+      </c>
+      <c r="E40">
+        <v>4.331799999999999</v>
+      </c>
+      <c r="F40">
+        <v>5.7418</v>
+      </c>
+      <c r="G40">
+        <v>1.46</v>
+      </c>
+      <c r="H40">
+        <v>13.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.792</v>
+      </c>
+      <c r="K40">
+        <v>0.199</v>
+      </c>
+      <c r="L40">
+        <v>0.593</v>
+      </c>
+      <c r="M40">
+        <v>1.37114184</v>
+      </c>
+      <c r="N40">
+        <v>-0.77814184</v>
+      </c>
+      <c r="O40">
+        <v>-0.1181323363715946</v>
+      </c>
+      <c r="P40">
+        <v>-0.6600095036284054</v>
+      </c>
+      <c r="Q40">
+        <v>-0.4610095036284054</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1493591247847909</v>
+      </c>
+      <c r="T40">
+        <v>1.312977662880665</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06565719663483342</v>
+      </c>
+      <c r="W40">
+        <v>0.2231210614436018</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4324862553971804</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.179388660715139</v>
+      </c>
+      <c r="C41">
+        <v>2.532877913716153</v>
+      </c>
+      <c r="D41">
+        <v>6.965777913716154</v>
+      </c>
+      <c r="E41">
+        <v>4.4829</v>
+      </c>
+      <c r="F41">
+        <v>5.8929</v>
+      </c>
+      <c r="G41">
+        <v>1.46</v>
+      </c>
+      <c r="H41">
+        <v>13.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.792</v>
+      </c>
+      <c r="K41">
+        <v>0.199</v>
+      </c>
+      <c r="L41">
+        <v>0.593</v>
+      </c>
+      <c r="M41">
+        <v>1.40722452</v>
+      </c>
+      <c r="N41">
+        <v>-0.81422452</v>
+      </c>
+      <c r="O41">
+        <v>-0.1236101696814557</v>
+      </c>
+      <c r="P41">
+        <v>-0.6906143503185443</v>
+      </c>
+      <c r="Q41">
+        <v>-0.4916143503185443</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1511715694533941</v>
+      </c>
+      <c r="T41">
+        <v>1.334501886862315</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.0639736787724018</v>
+      </c>
+      <c r="W41">
+        <v>0.2235230855091505</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4213968642331503</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.181388660715139</v>
+      </c>
+      <c r="C42">
+        <v>2.284073399503313</v>
+      </c>
+      <c r="D42">
+        <v>6.868073399503314</v>
+      </c>
+      <c r="E42">
+        <v>4.634</v>
+      </c>
+      <c r="F42">
+        <v>6.044</v>
+      </c>
+      <c r="G42">
+        <v>1.46</v>
+      </c>
+      <c r="H42">
+        <v>13.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.792</v>
+      </c>
+      <c r="K42">
+        <v>0.199</v>
+      </c>
+      <c r="L42">
+        <v>0.593</v>
+      </c>
+      <c r="M42">
+        <v>1.4433072</v>
+      </c>
+      <c r="N42">
+        <v>-0.8503072000000003</v>
+      </c>
+      <c r="O42">
+        <v>-0.1290880029913168</v>
+      </c>
+      <c r="P42">
+        <v>-0.7212191970086834</v>
+      </c>
+      <c r="Q42">
+        <v>-0.5222191970086834</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.153044428944284</v>
+      </c>
+      <c r="T42">
+        <v>1.356743584976687</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06237433680309175</v>
+      </c>
+      <c r="W42">
+        <v>0.2239050083714217</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4108619426273213</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.183388660715139</v>
+      </c>
+      <c r="C43">
+        <v>2.037971850065983</v>
+      </c>
+      <c r="D43">
+        <v>6.773071850065984</v>
+      </c>
+      <c r="E43">
+        <v>4.7851</v>
+      </c>
+      <c r="F43">
+        <v>6.1951</v>
+      </c>
+      <c r="G43">
+        <v>1.46</v>
+      </c>
+      <c r="H43">
+        <v>13.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.792</v>
+      </c>
+      <c r="K43">
+        <v>0.199</v>
+      </c>
+      <c r="L43">
+        <v>0.593</v>
+      </c>
+      <c r="M43">
+        <v>1.47938988</v>
+      </c>
+      <c r="N43">
+        <v>-0.8863898800000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.1345658363011779</v>
+      </c>
+      <c r="P43">
+        <v>-0.7518240436988222</v>
+      </c>
+      <c r="Q43">
+        <v>-0.5528240436988221</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1549807751975769</v>
+      </c>
+      <c r="T43">
+        <v>1.379739238959342</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06085301151521146</v>
+      </c>
+      <c r="W43">
+        <v>0.2242683008501675</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.4008409196364111</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1853886607151391</v>
+      </c>
+      <c r="C44">
+        <v>1.794462630730418</v>
+      </c>
+      <c r="D44">
+        <v>6.680662630730417</v>
+      </c>
+      <c r="E44">
+        <v>4.936199999999999</v>
+      </c>
+      <c r="F44">
+        <v>6.3462</v>
+      </c>
+      <c r="G44">
+        <v>1.46</v>
+      </c>
+      <c r="H44">
+        <v>13.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.792</v>
+      </c>
+      <c r="K44">
+        <v>0.199</v>
+      </c>
+      <c r="L44">
+        <v>0.593</v>
+      </c>
+      <c r="M44">
+        <v>1.51547256</v>
+      </c>
+      <c r="N44">
+        <v>-0.9224725600000001</v>
+      </c>
+      <c r="O44">
+        <v>-0.140043669611039</v>
+      </c>
+      <c r="P44">
+        <v>-0.7824288903889611</v>
+      </c>
+      <c r="Q44">
+        <v>-0.5834288903889611</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1569838920113282</v>
+      </c>
+      <c r="T44">
+        <v>1.403527846527607</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05940413028865881</v>
+      </c>
+      <c r="W44">
+        <v>0.2246142936870683</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3912970882164966</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.187388660715139</v>
+      </c>
+      <c r="C45">
+        <v>1.553441063383661</v>
+      </c>
+      <c r="D45">
+        <v>6.590741063383661</v>
+      </c>
+      <c r="E45">
+        <v>5.0873</v>
+      </c>
+      <c r="F45">
+        <v>6.4973</v>
+      </c>
+      <c r="G45">
+        <v>1.46</v>
+      </c>
+      <c r="H45">
+        <v>13.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.792</v>
+      </c>
+      <c r="K45">
+        <v>0.199</v>
+      </c>
+      <c r="L45">
+        <v>0.593</v>
+      </c>
+      <c r="M45">
+        <v>1.55155524</v>
+      </c>
+      <c r="N45">
+        <v>-0.9585552400000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.1455215029209001</v>
+      </c>
+      <c r="P45">
+        <v>-0.8130337370791</v>
+      </c>
+      <c r="Q45">
+        <v>-0.6140337370791</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.159057293625562</v>
+      </c>
+      <c r="T45">
+        <v>1.428151142080723</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05802263888659697</v>
+      </c>
+      <c r="W45">
+        <v>0.2249441938338806</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.382197155932392</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1893886607151391</v>
+      </c>
+      <c r="C46">
+        <v>1.314808030921793</v>
+      </c>
+      <c r="D46">
+        <v>6.503208030921793</v>
+      </c>
+      <c r="E46">
+        <v>5.2384</v>
+      </c>
+      <c r="F46">
+        <v>6.6484</v>
+      </c>
+      <c r="G46">
+        <v>1.46</v>
+      </c>
+      <c r="H46">
+        <v>13.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.792</v>
+      </c>
+      <c r="K46">
+        <v>0.199</v>
+      </c>
+      <c r="L46">
+        <v>0.593</v>
+      </c>
+      <c r="M46">
+        <v>1.58763792</v>
+      </c>
+      <c r="N46">
+        <v>-0.99463792</v>
+      </c>
+      <c r="O46">
+        <v>-0.1509993362307612</v>
+      </c>
+      <c r="P46">
+        <v>-0.8436385837692387</v>
+      </c>
+      <c r="Q46">
+        <v>-0.6446385837692388</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1612047452974471</v>
+      </c>
+      <c r="T46">
+        <v>1.45365384104645</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05670394254826523</v>
+      </c>
+      <c r="W46">
+        <v>0.2252590985194743</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3735108569339286</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1913886607151391</v>
+      </c>
+      <c r="C47">
+        <v>1.07846961280549</v>
+      </c>
+      <c r="D47">
+        <v>6.41796961280549</v>
+      </c>
+      <c r="E47">
+        <v>5.3895</v>
+      </c>
+      <c r="F47">
+        <v>6.7995</v>
+      </c>
+      <c r="G47">
+        <v>1.46</v>
+      </c>
+      <c r="H47">
+        <v>13.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.792</v>
+      </c>
+      <c r="K47">
+        <v>0.199</v>
+      </c>
+      <c r="L47">
+        <v>0.593</v>
+      </c>
+      <c r="M47">
+        <v>1.6237206</v>
+      </c>
+      <c r="N47">
+        <v>-1.0307206</v>
+      </c>
+      <c r="O47">
+        <v>-0.1564771695406224</v>
+      </c>
+      <c r="P47">
+        <v>-0.8742434304593778</v>
+      </c>
+      <c r="Q47">
+        <v>-0.6752434304593777</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.163430286121037</v>
+      </c>
+      <c r="T47">
+        <v>1.480083910883658</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05544385493608155</v>
+      </c>
+      <c r="W47">
+        <v>0.2255600074412638</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3652106156687301</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.193388660715139</v>
+      </c>
+      <c r="C48">
+        <v>0.8443367489057012</v>
+      </c>
+      <c r="D48">
+        <v>6.334936748905701</v>
+      </c>
+      <c r="E48">
+        <v>5.5406</v>
+      </c>
+      <c r="F48">
+        <v>6.9506</v>
+      </c>
+      <c r="G48">
+        <v>1.46</v>
+      </c>
+      <c r="H48">
+        <v>13.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.792</v>
+      </c>
+      <c r="K48">
+        <v>0.199</v>
+      </c>
+      <c r="L48">
+        <v>0.593</v>
+      </c>
+      <c r="M48">
+        <v>1.65980328</v>
+      </c>
+      <c r="N48">
+        <v>-1.06680328</v>
+      </c>
+      <c r="O48">
+        <v>-0.1619550028504834</v>
+      </c>
+      <c r="P48">
+        <v>-0.9048482771495165</v>
+      </c>
+      <c r="Q48">
+        <v>-0.7058482771495165</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1657382543825377</v>
+      </c>
+      <c r="T48">
+        <v>1.507492872196319</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05423855374181892</v>
+      </c>
+      <c r="W48">
+        <v>0.2258478333664536</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3572712544585404</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1953886607151391</v>
+      </c>
+      <c r="C49">
+        <v>0.6123249291101418</v>
+      </c>
+      <c r="D49">
+        <v>6.254024929110142</v>
+      </c>
+      <c r="E49">
+        <v>5.6917</v>
+      </c>
+      <c r="F49">
+        <v>7.1017</v>
+      </c>
+      <c r="G49">
+        <v>1.46</v>
+      </c>
+      <c r="H49">
+        <v>13.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.792</v>
+      </c>
+      <c r="K49">
+        <v>0.199</v>
+      </c>
+      <c r="L49">
+        <v>0.593</v>
+      </c>
+      <c r="M49">
+        <v>1.69588596</v>
+      </c>
+      <c r="N49">
+        <v>-1.10288596</v>
+      </c>
+      <c r="O49">
+        <v>-0.1674328361603445</v>
+      </c>
+      <c r="P49">
+        <v>-0.9354531238396555</v>
+      </c>
+      <c r="Q49">
+        <v>-0.7364531238396554</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1681333157859818</v>
+      </c>
+      <c r="T49">
+        <v>1.535936133935872</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05308454196007809</v>
+      </c>
+      <c r="W49">
+        <v>0.2261234113799334</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3496697384062311</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1973886607151391</v>
+      </c>
+      <c r="C50">
+        <v>0.382353906416486</v>
+      </c>
+      <c r="D50">
+        <v>6.175153906416486</v>
+      </c>
+      <c r="E50">
+        <v>5.8428</v>
+      </c>
+      <c r="F50">
+        <v>7.2528</v>
+      </c>
+      <c r="G50">
+        <v>1.46</v>
+      </c>
+      <c r="H50">
+        <v>13.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.792</v>
+      </c>
+      <c r="K50">
+        <v>0.199</v>
+      </c>
+      <c r="L50">
+        <v>0.593</v>
+      </c>
+      <c r="M50">
+        <v>1.73196864</v>
+      </c>
+      <c r="N50">
+        <v>-1.13896864</v>
+      </c>
+      <c r="O50">
+        <v>-0.1729106694702056</v>
+      </c>
+      <c r="P50">
+        <v>-0.9660579705297945</v>
+      </c>
+      <c r="Q50">
+        <v>-0.7670579705297944</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1706204949357123</v>
+      </c>
+      <c r="T50">
+        <v>1.565473367280792</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05197861400257646</v>
+      </c>
+      <c r="W50">
+        <v>0.2263875069761848</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3423849521894345</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1993886607151391</v>
+      </c>
+      <c r="C51">
+        <v>0.1543474314646796</v>
+      </c>
+      <c r="D51">
+        <v>6.098247431464679</v>
+      </c>
+      <c r="E51">
+        <v>5.993899999999999</v>
+      </c>
+      <c r="F51">
+        <v>7.403899999999999</v>
+      </c>
+      <c r="G51">
+        <v>1.46</v>
+      </c>
+      <c r="H51">
+        <v>13.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.792</v>
+      </c>
+      <c r="K51">
+        <v>0.199</v>
+      </c>
+      <c r="L51">
+        <v>0.593</v>
+      </c>
+      <c r="M51">
+        <v>1.76805132</v>
+      </c>
+      <c r="N51">
+        <v>-1.17505132</v>
+      </c>
+      <c r="O51">
+        <v>-0.1783885027800667</v>
+      </c>
+      <c r="P51">
+        <v>-0.9966628172199332</v>
+      </c>
+      <c r="Q51">
+        <v>-0.7976628172199332</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.173205210522687</v>
+      </c>
+      <c r="T51">
+        <v>1.596168923501984</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.05091782596170756</v>
+      </c>
+      <c r="W51">
+        <v>0.2266408231603442</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3353975041855686</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2013886607151391</v>
+      </c>
+      <c r="C52">
+        <v>-0.07176699333766301</v>
+      </c>
+      <c r="D52">
+        <v>6.023233006662337</v>
+      </c>
+      <c r="E52">
+        <v>6.145</v>
+      </c>
+      <c r="F52">
+        <v>7.555</v>
+      </c>
+      <c r="G52">
+        <v>1.46</v>
+      </c>
+      <c r="H52">
+        <v>13.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.792</v>
+      </c>
+      <c r="K52">
+        <v>0.199</v>
+      </c>
+      <c r="L52">
+        <v>0.593</v>
+      </c>
+      <c r="M52">
+        <v>1.804134</v>
+      </c>
+      <c r="N52">
+        <v>-1.211134</v>
+      </c>
+      <c r="O52">
+        <v>-0.1838663360899278</v>
+      </c>
+      <c r="P52">
+        <v>-1.027267663910072</v>
+      </c>
+      <c r="Q52">
+        <v>-0.8282676639100723</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1758933147331408</v>
+      </c>
+      <c r="T52">
+        <v>1.628092301972024</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0498994694424734</v>
+      </c>
+      <c r="W52">
+        <v>0.2268840066971374</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3286895541018572</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2033886607151391</v>
+      </c>
+      <c r="C53">
+        <v>-0.2960583417633851</v>
+      </c>
+      <c r="D53">
+        <v>5.950041658236615</v>
+      </c>
+      <c r="E53">
+        <v>6.2961</v>
+      </c>
+      <c r="F53">
+        <v>7.7061</v>
+      </c>
+      <c r="G53">
+        <v>1.46</v>
+      </c>
+      <c r="H53">
+        <v>13.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.792</v>
+      </c>
+      <c r="K53">
+        <v>0.199</v>
+      </c>
+      <c r="L53">
+        <v>0.593</v>
+      </c>
+      <c r="M53">
+        <v>1.84021668</v>
+      </c>
+      <c r="N53">
+        <v>-1.24721668</v>
+      </c>
+      <c r="O53">
+        <v>-0.189344169399789</v>
+      </c>
+      <c r="P53">
+        <v>-1.057872510600211</v>
+      </c>
+      <c r="Q53">
+        <v>-0.8588725106002111</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1786911374827967</v>
+      </c>
+      <c r="T53">
+        <v>1.661318675481657</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04892104847301313</v>
+      </c>
+      <c r="W53">
+        <v>0.2271176536246445</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3222446608841737</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2053886607151391</v>
+      </c>
+      <c r="C54">
+        <v>-0.5185922752939636</v>
+      </c>
+      <c r="D54">
+        <v>5.878607724706036</v>
+      </c>
+      <c r="E54">
+        <v>6.4472</v>
+      </c>
+      <c r="F54">
+        <v>7.8572</v>
+      </c>
+      <c r="G54">
+        <v>1.46</v>
+      </c>
+      <c r="H54">
+        <v>13.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.792</v>
+      </c>
+      <c r="K54">
+        <v>0.199</v>
+      </c>
+      <c r="L54">
+        <v>0.593</v>
+      </c>
+      <c r="M54">
+        <v>1.87629936</v>
+      </c>
+      <c r="N54">
+        <v>-1.28329936</v>
+      </c>
+      <c r="O54">
+        <v>-0.19482200270965</v>
+      </c>
+      <c r="P54">
+        <v>-1.08847735729035</v>
+      </c>
+      <c r="Q54">
+        <v>-0.8894773572903498</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.181605536180355</v>
+      </c>
+      <c r="T54">
+        <v>1.695929481220859</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04798025907930135</v>
+      </c>
+      <c r="W54">
+        <v>0.2273423141318628</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3160476481748626</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2073886607151391</v>
+      </c>
+      <c r="C55">
+        <v>-0.7394313395912837</v>
+      </c>
+      <c r="D55">
+        <v>5.808868660408717</v>
+      </c>
+      <c r="E55">
+        <v>6.5983</v>
+      </c>
+      <c r="F55">
+        <v>8.0083</v>
+      </c>
+      <c r="G55">
+        <v>1.46</v>
+      </c>
+      <c r="H55">
+        <v>13.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.792</v>
+      </c>
+      <c r="K55">
+        <v>0.199</v>
+      </c>
+      <c r="L55">
+        <v>0.593</v>
+      </c>
+      <c r="M55">
+        <v>1.91238204</v>
+      </c>
+      <c r="N55">
+        <v>-1.31938204</v>
+      </c>
+      <c r="O55">
+        <v>-0.2002998360195112</v>
+      </c>
+      <c r="P55">
+        <v>-1.119082203980489</v>
+      </c>
+      <c r="Q55">
+        <v>-0.920082203980489</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1846439518437668</v>
+      </c>
+      <c r="T55">
+        <v>1.732013087204281</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04707497117214472</v>
+      </c>
+      <c r="W55">
+        <v>0.2275584968840919</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.310084485001752</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2093886607151391</v>
+      </c>
+      <c r="C56">
+        <v>-0.9586351471486774</v>
+      </c>
+      <c r="D56">
+        <v>5.740764852851322</v>
+      </c>
+      <c r="E56">
+        <v>6.7494</v>
+      </c>
+      <c r="F56">
+        <v>8.1594</v>
+      </c>
+      <c r="G56">
+        <v>1.46</v>
+      </c>
+      <c r="H56">
+        <v>13.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.792</v>
+      </c>
+      <c r="K56">
+        <v>0.199</v>
+      </c>
+      <c r="L56">
+        <v>0.593</v>
+      </c>
+      <c r="M56">
+        <v>1.94846472</v>
+      </c>
+      <c r="N56">
+        <v>-1.35546472</v>
+      </c>
+      <c r="O56">
+        <v>-0.2057776693293722</v>
+      </c>
+      <c r="P56">
+        <v>-1.149687050670628</v>
+      </c>
+      <c r="Q56">
+        <v>-0.9506870506706278</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1878144725360226</v>
+      </c>
+      <c r="T56">
+        <v>1.769665545621766</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04620321244673463</v>
+      </c>
+      <c r="W56">
+        <v>0.2277666728677198</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3043421797239418</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2113886607151391</v>
+      </c>
+      <c r="C57">
+        <v>-1.176260547242332</v>
+      </c>
+      <c r="D57">
+        <v>5.674239452757669</v>
+      </c>
+      <c r="E57">
+        <v>6.900500000000001</v>
+      </c>
+      <c r="F57">
+        <v>8.310500000000001</v>
+      </c>
+      <c r="G57">
+        <v>1.46</v>
+      </c>
+      <c r="H57">
+        <v>13.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.792</v>
+      </c>
+      <c r="K57">
+        <v>0.199</v>
+      </c>
+      <c r="L57">
+        <v>0.593</v>
+      </c>
+      <c r="M57">
+        <v>1.9845474</v>
+      </c>
+      <c r="N57">
+        <v>-1.3915474</v>
+      </c>
+      <c r="O57">
+        <v>-0.2112555026392334</v>
+      </c>
+      <c r="P57">
+        <v>-1.180291897360767</v>
+      </c>
+      <c r="Q57">
+        <v>-0.9812918973607669</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1911259052590453</v>
+      </c>
+      <c r="T57">
+        <v>1.808991446635582</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04536315403861218</v>
+      </c>
+      <c r="W57">
+        <v>0.2279672788155794</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2988086855471428</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2133886607151391</v>
+      </c>
+      <c r="C58">
+        <v>-1.392361784201425</v>
+      </c>
+      <c r="D58">
+        <v>5.609238215798576</v>
+      </c>
+      <c r="E58">
+        <v>7.051600000000001</v>
+      </c>
+      <c r="F58">
+        <v>8.461600000000001</v>
+      </c>
+      <c r="G58">
+        <v>1.46</v>
+      </c>
+      <c r="H58">
+        <v>13.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.792</v>
+      </c>
+      <c r="K58">
+        <v>0.199</v>
+      </c>
+      <c r="L58">
+        <v>0.593</v>
+      </c>
+      <c r="M58">
+        <v>2.02063008</v>
+      </c>
+      <c r="N58">
+        <v>-1.42763008</v>
+      </c>
+      <c r="O58">
+        <v>-0.2167333359490945</v>
+      </c>
+      <c r="P58">
+        <v>-1.210896744050906</v>
+      </c>
+      <c r="Q58">
+        <v>-1.011896744050906</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1945878576512963</v>
+      </c>
+      <c r="T58">
+        <v>1.850104888604573</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04455309771649411</v>
+      </c>
+      <c r="W58">
+        <v>0.2281607202653012</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2934728161623724</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2153886607151391</v>
+      </c>
+      <c r="C59">
+        <v>-1.606990644923089</v>
+      </c>
+      <c r="D59">
+        <v>5.545709355076911</v>
+      </c>
+      <c r="E59">
+        <v>7.2027</v>
+      </c>
+      <c r="F59">
+        <v>8.6127</v>
+      </c>
+      <c r="G59">
+        <v>1.46</v>
+      </c>
+      <c r="H59">
+        <v>13.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.792</v>
+      </c>
+      <c r="K59">
+        <v>0.199</v>
+      </c>
+      <c r="L59">
+        <v>0.593</v>
+      </c>
+      <c r="M59">
+        <v>2.05671276</v>
+      </c>
+      <c r="N59">
+        <v>-1.46371276</v>
+      </c>
+      <c r="O59">
+        <v>-0.2222111692589556</v>
+      </c>
+      <c r="P59">
+        <v>-1.241501590741045</v>
+      </c>
+      <c r="Q59">
+        <v>-1.042501590741045</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1982108310850474</v>
+      </c>
+      <c r="T59">
+        <v>1.8931305836884</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04377146442322228</v>
+      </c>
+      <c r="W59">
+        <v>0.2283473742957345</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.288324170264787</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.217388660715139</v>
+      </c>
+      <c r="C60">
+        <v>-1.820196596475326</v>
+      </c>
+      <c r="D60">
+        <v>5.483603403524674</v>
+      </c>
+      <c r="E60">
+        <v>7.3538</v>
+      </c>
+      <c r="F60">
+        <v>8.7638</v>
+      </c>
+      <c r="G60">
+        <v>1.46</v>
+      </c>
+      <c r="H60">
+        <v>13.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.792</v>
+      </c>
+      <c r="K60">
+        <v>0.199</v>
+      </c>
+      <c r="L60">
+        <v>0.593</v>
+      </c>
+      <c r="M60">
+        <v>2.09279544</v>
+      </c>
+      <c r="N60">
+        <v>-1.49979544</v>
+      </c>
+      <c r="O60">
+        <v>-0.2276890025688167</v>
+      </c>
+      <c r="P60">
+        <v>-1.272106437431183</v>
+      </c>
+      <c r="Q60">
+        <v>-1.073106437431183</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2020063270632628</v>
+      </c>
+      <c r="T60">
+        <v>1.938205121395266</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04301678400213223</v>
+      </c>
+      <c r="W60">
+        <v>0.2285275919802908</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2833530638809113</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2193886607151391</v>
+      </c>
+      <c r="C61">
+        <v>-2.032026914556312</v>
+      </c>
+      <c r="D61">
+        <v>5.422873085443688</v>
+      </c>
+      <c r="E61">
+        <v>7.504899999999999</v>
+      </c>
+      <c r="F61">
+        <v>8.914899999999999</v>
+      </c>
+      <c r="G61">
+        <v>1.46</v>
+      </c>
+      <c r="H61">
+        <v>13.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.792</v>
+      </c>
+      <c r="K61">
+        <v>0.199</v>
+      </c>
+      <c r="L61">
+        <v>0.593</v>
+      </c>
+      <c r="M61">
+        <v>2.12887812</v>
+      </c>
+      <c r="N61">
+        <v>-1.53587812</v>
+      </c>
+      <c r="O61">
+        <v>-0.2331668358786778</v>
+      </c>
+      <c r="P61">
+        <v>-1.302711284121322</v>
+      </c>
+      <c r="Q61">
+        <v>-1.103711284121322</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.205986969186757</v>
+      </c>
+      <c r="T61">
+        <v>1.985478417039053</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04228768596819781</v>
+      </c>
+      <c r="W61">
+        <v>0.2287017005907944</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.278550469577845</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.221388660715139</v>
+      </c>
+      <c r="C62">
+        <v>-2.242526803511124</v>
+      </c>
+      <c r="D62">
+        <v>5.363473196488875</v>
+      </c>
+      <c r="E62">
+        <v>7.655999999999999</v>
+      </c>
+      <c r="F62">
+        <v>9.065999999999999</v>
+      </c>
+      <c r="G62">
+        <v>1.46</v>
+      </c>
+      <c r="H62">
+        <v>13.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.792</v>
+      </c>
+      <c r="K62">
+        <v>0.199</v>
+      </c>
+      <c r="L62">
+        <v>0.593</v>
+      </c>
+      <c r="M62">
+        <v>2.1649608</v>
+      </c>
+      <c r="N62">
+        <v>-1.5719608</v>
+      </c>
+      <c r="O62">
+        <v>-0.2386446691885388</v>
+      </c>
+      <c r="P62">
+        <v>-1.333316130811461</v>
+      </c>
+      <c r="Q62">
+        <v>-1.134316130811461</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2101666434164259</v>
+      </c>
+      <c r="T62">
+        <v>2.03511537746503</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04158289120206117</v>
+      </c>
+      <c r="W62">
+        <v>0.2288700055809478</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2739079617515476</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2233886607151391</v>
+      </c>
+      <c r="C63">
+        <v>-2.451739508546305</v>
+      </c>
+      <c r="D63">
+        <v>5.305360491453695</v>
+      </c>
+      <c r="E63">
+        <v>7.8071</v>
+      </c>
+      <c r="F63">
+        <v>9.2171</v>
+      </c>
+      <c r="G63">
+        <v>1.46</v>
+      </c>
+      <c r="H63">
+        <v>13.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.792</v>
+      </c>
+      <c r="K63">
+        <v>0.199</v>
+      </c>
+      <c r="L63">
+        <v>0.593</v>
+      </c>
+      <c r="M63">
+        <v>2.20104348</v>
+      </c>
+      <c r="N63">
+        <v>-1.60804348</v>
+      </c>
+      <c r="O63">
+        <v>-0.2441225024984</v>
+      </c>
+      <c r="P63">
+        <v>-1.3639209775016</v>
+      </c>
+      <c r="Q63">
+        <v>-1.1649209775016</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.214560659914283</v>
+      </c>
+      <c r="T63">
+        <v>2.087297823041056</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04090120446104377</v>
+      </c>
+      <c r="W63">
+        <v>0.2290327923747028</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2694176672966042</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2253886607151391</v>
+      </c>
+      <c r="C64">
+        <v>-2.659706420727569</v>
+      </c>
+      <c r="D64">
+        <v>5.248493579272431</v>
+      </c>
+      <c r="E64">
+        <v>7.9582</v>
+      </c>
+      <c r="F64">
+        <v>9.3682</v>
+      </c>
+      <c r="G64">
+        <v>1.46</v>
+      </c>
+      <c r="H64">
+        <v>13.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.792</v>
+      </c>
+      <c r="K64">
+        <v>0.199</v>
+      </c>
+      <c r="L64">
+        <v>0.593</v>
+      </c>
+      <c r="M64">
+        <v>2.23712616</v>
+      </c>
+      <c r="N64">
+        <v>-1.64412616</v>
+      </c>
+      <c r="O64">
+        <v>-0.249600335808261</v>
+      </c>
+      <c r="P64">
+        <v>-1.394525824191739</v>
+      </c>
+      <c r="Q64">
+        <v>-1.195525824191739</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2191859404383431</v>
+      </c>
+      <c r="T64">
+        <v>2.142226713121084</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04024150761489791</v>
+      </c>
+      <c r="W64">
+        <v>0.2291903279815624</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2650722210498848</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2273886607151391</v>
+      </c>
+      <c r="C65">
+        <v>-2.866467175296479</v>
+      </c>
+      <c r="D65">
+        <v>5.192832824703521</v>
+      </c>
+      <c r="E65">
+        <v>8.109299999999999</v>
+      </c>
+      <c r="F65">
+        <v>9.519299999999999</v>
+      </c>
+      <c r="G65">
+        <v>1.46</v>
+      </c>
+      <c r="H65">
+        <v>13.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.792</v>
+      </c>
+      <c r="K65">
+        <v>0.199</v>
+      </c>
+      <c r="L65">
+        <v>0.593</v>
+      </c>
+      <c r="M65">
+        <v>2.27320884</v>
+      </c>
+      <c r="N65">
+        <v>-1.68020884</v>
+      </c>
+      <c r="O65">
+        <v>-0.2550781691181222</v>
+      </c>
+      <c r="P65">
+        <v>-1.425130670881878</v>
+      </c>
+      <c r="Q65">
+        <v>-1.226130670881878</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2240612361258659</v>
+      </c>
+      <c r="T65">
+        <v>2.200124732394627</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03960275352577254</v>
+      </c>
+      <c r="W65">
+        <v>0.2293428624580455</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2608647254776644</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2293886607151391</v>
+      </c>
+      <c r="C66">
+        <v>-3.072059743796815</v>
+      </c>
+      <c r="D66">
+        <v>5.138340256203184</v>
+      </c>
+      <c r="E66">
+        <v>8.260399999999999</v>
+      </c>
+      <c r="F66">
+        <v>9.670399999999999</v>
+      </c>
+      <c r="G66">
+        <v>1.46</v>
+      </c>
+      <c r="H66">
+        <v>13.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.792</v>
+      </c>
+      <c r="K66">
+        <v>0.199</v>
+      </c>
+      <c r="L66">
+        <v>0.593</v>
+      </c>
+      <c r="M66">
+        <v>2.30929152</v>
+      </c>
+      <c r="N66">
+        <v>-1.71629152</v>
+      </c>
+      <c r="O66">
+        <v>-0.2605560024279833</v>
+      </c>
+      <c r="P66">
+        <v>-1.455735517572017</v>
+      </c>
+      <c r="Q66">
+        <v>-1.256735517572017</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2292073815738066</v>
+      </c>
+      <c r="T66">
+        <v>2.261239308294478</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03898396050193235</v>
+      </c>
+      <c r="W66">
+        <v>0.2294906302321386</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2567887141420759</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2313886607151391</v>
+      </c>
+      <c r="C67">
+        <v>-3.276520520460645</v>
+      </c>
+      <c r="D67">
+        <v>5.084979479539355</v>
+      </c>
+      <c r="E67">
+        <v>8.4115</v>
+      </c>
+      <c r="F67">
+        <v>9.8215</v>
+      </c>
+      <c r="G67">
+        <v>1.46</v>
+      </c>
+      <c r="H67">
+        <v>13.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.792</v>
+      </c>
+      <c r="K67">
+        <v>0.199</v>
+      </c>
+      <c r="L67">
+        <v>0.593</v>
+      </c>
+      <c r="M67">
+        <v>2.3453742</v>
+      </c>
+      <c r="N67">
+        <v>-1.7523742</v>
+      </c>
+      <c r="O67">
+        <v>-0.2660338357378444</v>
+      </c>
+      <c r="P67">
+        <v>-1.486340364262156</v>
+      </c>
+      <c r="Q67">
+        <v>-1.287340364262156</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2346475924759154</v>
+      </c>
+      <c r="T67">
+        <v>2.32584614567432</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03838420726344108</v>
+      </c>
+      <c r="W67">
+        <v>0.2296338513054903</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2528381185398901</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2333886607151391</v>
+      </c>
+      <c r="C68">
+        <v>-3.479884403267086</v>
+      </c>
+      <c r="D68">
+        <v>5.032715596732914</v>
+      </c>
+      <c r="E68">
+        <v>8.5626</v>
+      </c>
+      <c r="F68">
+        <v>9.9726</v>
+      </c>
+      <c r="G68">
+        <v>1.46</v>
+      </c>
+      <c r="H68">
+        <v>13.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.792</v>
+      </c>
+      <c r="K68">
+        <v>0.199</v>
+      </c>
+      <c r="L68">
+        <v>0.593</v>
+      </c>
+      <c r="M68">
+        <v>2.38145688</v>
+      </c>
+      <c r="N68">
+        <v>-1.78845688</v>
+      </c>
+      <c r="O68">
+        <v>-0.2715116690477055</v>
+      </c>
+      <c r="P68">
+        <v>-1.516945210952295</v>
+      </c>
+      <c r="Q68">
+        <v>-1.317945210952294</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2404078157840305</v>
+      </c>
+      <c r="T68">
+        <v>2.394253385252977</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03780262836551015</v>
+      </c>
+      <c r="W68">
+        <v>0.2297727323463162</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2490072379559524</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2353886607151391</v>
+      </c>
+      <c r="C69">
+        <v>-3.682184870053169</v>
+      </c>
+      <c r="D69">
+        <v>4.981515129946831</v>
+      </c>
+      <c r="E69">
+        <v>8.713699999999999</v>
+      </c>
+      <c r="F69">
+        <v>10.1237</v>
+      </c>
+      <c r="G69">
+        <v>1.46</v>
+      </c>
+      <c r="H69">
+        <v>13.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.792</v>
+      </c>
+      <c r="K69">
+        <v>0.199</v>
+      </c>
+      <c r="L69">
+        <v>0.593</v>
+      </c>
+      <c r="M69">
+        <v>2.41753956</v>
+      </c>
+      <c r="N69">
+        <v>-1.82453956</v>
+      </c>
+      <c r="O69">
+        <v>-0.2769895023575665</v>
+      </c>
+      <c r="P69">
+        <v>-1.547550057642433</v>
+      </c>
+      <c r="Q69">
+        <v>-1.348550057642433</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2465171435350618</v>
+      </c>
+      <c r="T69">
+        <v>2.466806518139431</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03723841003169658</v>
+      </c>
+      <c r="W69">
+        <v>0.2299074676844309</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2452907120163114</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.237388660715139</v>
+      </c>
+      <c r="C70">
+        <v>-3.883454050025559</v>
+      </c>
+      <c r="D70">
+        <v>4.931345949974442</v>
+      </c>
+      <c r="E70">
+        <v>8.864800000000001</v>
+      </c>
+      <c r="F70">
+        <v>10.2748</v>
+      </c>
+      <c r="G70">
+        <v>1.46</v>
+      </c>
+      <c r="H70">
+        <v>13.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.792</v>
+      </c>
+      <c r="K70">
+        <v>0.199</v>
+      </c>
+      <c r="L70">
+        <v>0.593</v>
+      </c>
+      <c r="M70">
+        <v>2.453622240000001</v>
+      </c>
+      <c r="N70">
+        <v>-1.860622240000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.2824673356674278</v>
+      </c>
+      <c r="P70">
+        <v>-1.578154904332573</v>
+      </c>
+      <c r="Q70">
+        <v>-1.379154904332573</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2530083042705324</v>
+      </c>
+      <c r="T70">
+        <v>2.543894221831288</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03669078635475985</v>
+      </c>
+      <c r="W70">
+        <v>0.2300382402184833</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2416834956631302</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2393886607151391</v>
+      </c>
+      <c r="C71">
+        <v>-4.083722790994199</v>
+      </c>
+      <c r="D71">
+        <v>4.882177209005802</v>
+      </c>
+      <c r="E71">
+        <v>9.0159</v>
+      </c>
+      <c r="F71">
+        <v>10.4259</v>
+      </c>
+      <c r="G71">
+        <v>1.46</v>
+      </c>
+      <c r="H71">
+        <v>13.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.792</v>
+      </c>
+      <c r="K71">
+        <v>0.199</v>
+      </c>
+      <c r="L71">
+        <v>0.593</v>
+      </c>
+      <c r="M71">
+        <v>2.48970492</v>
+      </c>
+      <c r="N71">
+        <v>-1.89670492</v>
+      </c>
+      <c r="O71">
+        <v>-0.2879451689772888</v>
+      </c>
+      <c r="P71">
+        <v>-1.608759751022712</v>
+      </c>
+      <c r="Q71">
+        <v>-1.409759751022712</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2599182495695819</v>
+      </c>
+      <c r="T71">
+        <v>2.62595532576133</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03615903582787927</v>
+      </c>
+      <c r="W71">
+        <v>0.2301652222443024</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2381808363056935</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.241388660715139</v>
+      </c>
+      <c r="C72">
+        <v>-4.283020722623457</v>
+      </c>
+      <c r="D72">
+        <v>4.833979277376543</v>
+      </c>
+      <c r="E72">
+        <v>9.167</v>
+      </c>
+      <c r="F72">
+        <v>10.577</v>
+      </c>
+      <c r="G72">
+        <v>1.46</v>
+      </c>
+      <c r="H72">
+        <v>13.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.792</v>
+      </c>
+      <c r="K72">
+        <v>0.199</v>
+      </c>
+      <c r="L72">
+        <v>0.593</v>
+      </c>
+      <c r="M72">
+        <v>2.5257876</v>
+      </c>
+      <c r="N72">
+        <v>-1.9327876</v>
+      </c>
+      <c r="O72">
+        <v>-0.2934230022871499</v>
+      </c>
+      <c r="P72">
+        <v>-1.63936459771285</v>
+      </c>
+      <c r="Q72">
+        <v>-1.44036459771285</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2672888578885679</v>
+      </c>
+      <c r="T72">
+        <v>2.713487169953374</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03564247817319528</v>
+      </c>
+      <c r="W72">
+        <v>0.230288576212241</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.234778252929898</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.243388660715139</v>
+      </c>
+      <c r="C73">
+        <v>-4.481376315973346</v>
+      </c>
+      <c r="D73">
+        <v>4.786723684026653</v>
+      </c>
+      <c r="E73">
+        <v>9.318099999999999</v>
+      </c>
+      <c r="F73">
+        <v>10.7281</v>
+      </c>
+      <c r="G73">
+        <v>1.46</v>
+      </c>
+      <c r="H73">
+        <v>13.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.792</v>
+      </c>
+      <c r="K73">
+        <v>0.199</v>
+      </c>
+      <c r="L73">
+        <v>0.593</v>
+      </c>
+      <c r="M73">
+        <v>2.56187028</v>
+      </c>
+      <c r="N73">
+        <v>-1.96887028</v>
+      </c>
+      <c r="O73">
+        <v>-0.298900835597011</v>
+      </c>
+      <c r="P73">
+        <v>-1.669969444402989</v>
+      </c>
+      <c r="Q73">
+        <v>-1.470969444402989</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2751677840226564</v>
+      </c>
+      <c r="T73">
+        <v>2.807055693055213</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03514047143836155</v>
+      </c>
+      <c r="W73">
+        <v>0.2304084554205193</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2314715169731388</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.245388660715139</v>
+      </c>
+      <c r="C74">
+        <v>-4.678816939582179</v>
+      </c>
+      <c r="D74">
+        <v>4.740383060417821</v>
+      </c>
+      <c r="E74">
+        <v>9.469199999999999</v>
+      </c>
+      <c r="F74">
+        <v>10.8792</v>
+      </c>
+      <c r="G74">
+        <v>1.46</v>
+      </c>
+      <c r="H74">
+        <v>13.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.792</v>
+      </c>
+      <c r="K74">
+        <v>0.199</v>
+      </c>
+      <c r="L74">
+        <v>0.593</v>
+      </c>
+      <c r="M74">
+        <v>2.59795296</v>
+      </c>
+      <c r="N74">
+        <v>-2.00495296</v>
+      </c>
+      <c r="O74">
+        <v>-0.304378668906872</v>
+      </c>
+      <c r="P74">
+        <v>-1.700574291093128</v>
+      </c>
+      <c r="Q74">
+        <v>-1.501574291093128</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2836094905948942</v>
+      </c>
+      <c r="T74">
+        <v>2.9073076820929</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03465240933505098</v>
+      </c>
+      <c r="W74">
+        <v>0.2305250046507898</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2282566347929564</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2473886607151391</v>
+      </c>
+      <c r="C75">
+        <v>-4.875368912322841</v>
+      </c>
+      <c r="D75">
+        <v>4.694931087677157</v>
+      </c>
+      <c r="E75">
+        <v>9.620299999999999</v>
+      </c>
+      <c r="F75">
+        <v>11.0303</v>
+      </c>
+      <c r="G75">
+        <v>1.46</v>
+      </c>
+      <c r="H75">
+        <v>13.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.792</v>
+      </c>
+      <c r="K75">
+        <v>0.199</v>
+      </c>
+      <c r="L75">
+        <v>0.593</v>
+      </c>
+      <c r="M75">
+        <v>2.63403564</v>
+      </c>
+      <c r="N75">
+        <v>-2.04103564</v>
+      </c>
+      <c r="O75">
+        <v>-0.3098565022167332</v>
+      </c>
+      <c r="P75">
+        <v>-1.731179137783267</v>
+      </c>
+      <c r="Q75">
+        <v>-1.532179137783267</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2926765087650754</v>
+      </c>
+      <c r="T75">
+        <v>3.014985744392637</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03417771879621466</v>
+      </c>
+      <c r="W75">
+        <v>0.230638360751464</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2251298315766145</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.249388660715139</v>
+      </c>
+      <c r="C76">
+        <v>-5.071057553247131</v>
+      </c>
+      <c r="D76">
+        <v>4.650342446752869</v>
+      </c>
+      <c r="E76">
+        <v>9.7714</v>
+      </c>
+      <c r="F76">
+        <v>11.1814</v>
+      </c>
+      <c r="G76">
+        <v>1.46</v>
+      </c>
+      <c r="H76">
+        <v>13.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.792</v>
+      </c>
+      <c r="K76">
+        <v>0.199</v>
+      </c>
+      <c r="L76">
+        <v>0.593</v>
+      </c>
+      <c r="M76">
+        <v>2.67011832</v>
+      </c>
+      <c r="N76">
+        <v>-2.07711832</v>
+      </c>
+      <c r="O76">
+        <v>-0.3153343355265943</v>
+      </c>
+      <c r="P76">
+        <v>-1.761783984473406</v>
+      </c>
+      <c r="Q76">
+        <v>-1.562783984473406</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3024409898714245</v>
+      </c>
+      <c r="T76">
+        <v>3.130946734561584</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03371585773140095</v>
+      </c>
+      <c r="W76">
+        <v>0.2307486531737415</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2220875365553089</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.251388660715139</v>
+      </c>
+      <c r="C77">
+        <v>-5.265907228616545</v>
+      </c>
+      <c r="D77">
+        <v>4.606592771383455</v>
+      </c>
+      <c r="E77">
+        <v>9.922499999999999</v>
+      </c>
+      <c r="F77">
+        <v>11.3325</v>
+      </c>
+      <c r="G77">
+        <v>1.46</v>
+      </c>
+      <c r="H77">
+        <v>13.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.792</v>
+      </c>
+      <c r="K77">
+        <v>0.199</v>
+      </c>
+      <c r="L77">
+        <v>0.593</v>
+      </c>
+      <c r="M77">
+        <v>2.706201</v>
+      </c>
+      <c r="N77">
+        <v>-2.113201</v>
+      </c>
+      <c r="O77">
+        <v>-0.3208121688364554</v>
+      </c>
+      <c r="P77">
+        <v>-1.792388831163545</v>
+      </c>
+      <c r="Q77">
+        <v>-1.593388831163545</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3129866294662815</v>
+      </c>
+      <c r="T77">
+        <v>3.256184603944048</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03326631296164893</v>
+      </c>
+      <c r="W77">
+        <v>0.2308560044647582</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2191263694012381</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2533886607151391</v>
+      </c>
+      <c r="C78">
+        <v>-5.459941396303053</v>
+      </c>
+      <c r="D78">
+        <v>4.563658603696946</v>
+      </c>
+      <c r="E78">
+        <v>10.0736</v>
+      </c>
+      <c r="F78">
+        <v>11.4836</v>
+      </c>
+      <c r="G78">
+        <v>1.46</v>
+      </c>
+      <c r="H78">
+        <v>13.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.792</v>
+      </c>
+      <c r="K78">
+        <v>0.199</v>
+      </c>
+      <c r="L78">
+        <v>0.593</v>
+      </c>
+      <c r="M78">
+        <v>2.74228368</v>
+      </c>
+      <c r="N78">
+        <v>-2.14928368</v>
+      </c>
+      <c r="O78">
+        <v>-0.3262900021463165</v>
+      </c>
+      <c r="P78">
+        <v>-1.822993677853683</v>
+      </c>
+      <c r="Q78">
+        <v>-1.623993677853683</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3244110723607099</v>
+      </c>
+      <c r="T78">
+        <v>3.391858962441717</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03282859831741671</v>
+      </c>
+      <c r="W78">
+        <v>0.2309605307218009</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2162431276985902</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2553886607151391</v>
+      </c>
+      <c r="C79">
+        <v>-5.65318264772987</v>
+      </c>
+      <c r="D79">
+        <v>4.521517352270131</v>
+      </c>
+      <c r="E79">
+        <v>10.2247</v>
+      </c>
+      <c r="F79">
+        <v>11.6347</v>
+      </c>
+      <c r="G79">
+        <v>1.46</v>
+      </c>
+      <c r="H79">
+        <v>13.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.792</v>
+      </c>
+      <c r="K79">
+        <v>0.199</v>
+      </c>
+      <c r="L79">
+        <v>0.593</v>
+      </c>
+      <c r="M79">
+        <v>2.77836636</v>
+      </c>
+      <c r="N79">
+        <v>-2.18536636</v>
+      </c>
+      <c r="O79">
+        <v>-0.3317678354561776</v>
+      </c>
+      <c r="P79">
+        <v>-1.853598524543822</v>
+      </c>
+      <c r="Q79">
+        <v>-1.654598524543822</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3368289450720452</v>
+      </c>
+      <c r="T79">
+        <v>3.539331091243531</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03240225288472299</v>
+      </c>
+      <c r="W79">
+        <v>0.2310623420111282</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2134347753908163</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2573886607151391</v>
+      </c>
+      <c r="C80">
+        <v>-5.845652747509769</v>
+      </c>
+      <c r="D80">
+        <v>4.480147252490231</v>
+      </c>
+      <c r="E80">
+        <v>10.3758</v>
+      </c>
+      <c r="F80">
+        <v>11.7858</v>
+      </c>
+      <c r="G80">
+        <v>1.46</v>
+      </c>
+      <c r="H80">
+        <v>13.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.792</v>
+      </c>
+      <c r="K80">
+        <v>0.199</v>
+      </c>
+      <c r="L80">
+        <v>0.593</v>
+      </c>
+      <c r="M80">
+        <v>2.81444904</v>
+      </c>
+      <c r="N80">
+        <v>-2.22144904</v>
+      </c>
+      <c r="O80">
+        <v>-0.3372456687660387</v>
+      </c>
+      <c r="P80">
+        <v>-1.884203371233961</v>
+      </c>
+      <c r="Q80">
+        <v>-1.685203371233961</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3503757153025926</v>
+      </c>
+      <c r="T80">
+        <v>3.700209777209146</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0319868393862009</v>
+      </c>
+      <c r="W80">
+        <v>0.2311615427545752</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2106984321165751</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2593886607151391</v>
+      </c>
+      <c r="C81">
+        <v>-6.037372670927099</v>
+      </c>
+      <c r="D81">
+        <v>4.4395273290729</v>
+      </c>
+      <c r="E81">
+        <v>10.5269</v>
+      </c>
+      <c r="F81">
+        <v>11.9369</v>
+      </c>
+      <c r="G81">
+        <v>1.46</v>
+      </c>
+      <c r="H81">
+        <v>13.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.792</v>
+      </c>
+      <c r="K81">
+        <v>0.199</v>
+      </c>
+      <c r="L81">
+        <v>0.593</v>
+      </c>
+      <c r="M81">
+        <v>2.85053172</v>
+      </c>
+      <c r="N81">
+        <v>-2.25753172</v>
+      </c>
+      <c r="O81">
+        <v>-0.3427235020758999</v>
+      </c>
+      <c r="P81">
+        <v>-1.9148082179241</v>
+      </c>
+      <c r="Q81">
+        <v>-1.7158082179241</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3652126541265256</v>
+      </c>
+      <c r="T81">
+        <v>3.876410242790534</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03158194268510975</v>
+      </c>
+      <c r="W81">
+        <v>0.2312582320867958</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2080313633556058</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2613886607151391</v>
+      </c>
+      <c r="C82">
+        <v>-6.228362639399076</v>
+      </c>
+      <c r="D82">
+        <v>4.399637360600925</v>
+      </c>
+      <c r="E82">
+        <v>10.678</v>
+      </c>
+      <c r="F82">
+        <v>12.088</v>
+      </c>
+      <c r="G82">
+        <v>1.46</v>
+      </c>
+      <c r="H82">
+        <v>13.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.792</v>
+      </c>
+      <c r="K82">
+        <v>0.199</v>
+      </c>
+      <c r="L82">
+        <v>0.593</v>
+      </c>
+      <c r="M82">
+        <v>2.8866144</v>
+      </c>
+      <c r="N82">
+        <v>-2.2936144</v>
+      </c>
+      <c r="O82">
+        <v>-0.348201335385761</v>
+      </c>
+      <c r="P82">
+        <v>-1.94541306461424</v>
+      </c>
+      <c r="Q82">
+        <v>-1.74641306461424</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3815332868328519</v>
+      </c>
+      <c r="T82">
+        <v>4.07023075493006</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03118716840154587</v>
+      </c>
+      <c r="W82">
+        <v>0.2313525041857108</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2054309713136607</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2633886607151391</v>
+      </c>
+      <c r="C83">
+        <v>-6.418642154042348</v>
+      </c>
+      <c r="D83">
+        <v>4.360457845957653</v>
+      </c>
+      <c r="E83">
+        <v>10.8291</v>
+      </c>
+      <c r="F83">
+        <v>12.2391</v>
+      </c>
+      <c r="G83">
+        <v>1.46</v>
+      </c>
+      <c r="H83">
+        <v>13.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.792</v>
+      </c>
+      <c r="K83">
+        <v>0.199</v>
+      </c>
+      <c r="L83">
+        <v>0.593</v>
+      </c>
+      <c r="M83">
+        <v>2.92269708</v>
+      </c>
+      <c r="N83">
+        <v>-2.32969708</v>
+      </c>
+      <c r="O83">
+        <v>-0.353679168695622</v>
+      </c>
+      <c r="P83">
+        <v>-1.976017911304378</v>
+      </c>
+      <c r="Q83">
+        <v>-1.777017911304378</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3995718808766862</v>
+      </c>
+      <c r="T83">
+        <v>4.284453426242169</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03080214163115642</v>
+      </c>
+      <c r="W83">
+        <v>0.2314444485784798</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2028947864826278</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2653886607151391</v>
+      </c>
+      <c r="C84">
+        <v>-6.608230027461921</v>
+      </c>
+      <c r="D84">
+        <v>4.321969972538079</v>
+      </c>
+      <c r="E84">
+        <v>10.9802</v>
+      </c>
+      <c r="F84">
+        <v>12.3902</v>
+      </c>
+      <c r="G84">
+        <v>1.46</v>
+      </c>
+      <c r="H84">
+        <v>13.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.792</v>
+      </c>
+      <c r="K84">
+        <v>0.199</v>
+      </c>
+      <c r="L84">
+        <v>0.593</v>
+      </c>
+      <c r="M84">
+        <v>2.95877976</v>
+      </c>
+      <c r="N84">
+        <v>-2.36577976</v>
+      </c>
+      <c r="O84">
+        <v>-0.3591570020054831</v>
+      </c>
+      <c r="P84">
+        <v>-2.006622757994517</v>
+      </c>
+      <c r="Q84">
+        <v>-1.807622757994517</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4196147631476133</v>
+      </c>
+      <c r="T84">
+        <v>4.522478616588956</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03042650575760573</v>
+      </c>
+      <c r="W84">
+        <v>0.2315341504250838</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2004204598182056</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2673886607151391</v>
+      </c>
+      <c r="C85">
+        <v>-6.797144413871266</v>
+      </c>
+      <c r="D85">
+        <v>4.284155586128736</v>
+      </c>
+      <c r="E85">
+        <v>11.1313</v>
+      </c>
+      <c r="F85">
+        <v>12.5413</v>
+      </c>
+      <c r="G85">
+        <v>1.46</v>
+      </c>
+      <c r="H85">
+        <v>13.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.792</v>
+      </c>
+      <c r="K85">
+        <v>0.199</v>
+      </c>
+      <c r="L85">
+        <v>0.593</v>
+      </c>
+      <c r="M85">
+        <v>2.99486244</v>
+      </c>
+      <c r="N85">
+        <v>-2.40186244</v>
+      </c>
+      <c r="O85">
+        <v>-0.3646348353153442</v>
+      </c>
+      <c r="P85">
+        <v>-2.037227604684656</v>
+      </c>
+      <c r="Q85">
+        <v>-1.838227604684656</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4420156315680612</v>
+      </c>
+      <c r="T85">
+        <v>4.788506770505955</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03005992135088759</v>
+      </c>
+      <c r="W85">
+        <v>0.231621690781408</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1980057554830464</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2693886607151391</v>
+      </c>
+      <c r="C86">
+        <v>-6.98540283764494</v>
+      </c>
+      <c r="D86">
+        <v>4.24699716235506</v>
+      </c>
+      <c r="E86">
+        <v>11.2824</v>
+      </c>
+      <c r="F86">
+        <v>12.6924</v>
+      </c>
+      <c r="G86">
+        <v>1.46</v>
+      </c>
+      <c r="H86">
+        <v>13.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.792</v>
+      </c>
+      <c r="K86">
+        <v>0.199</v>
+      </c>
+      <c r="L86">
+        <v>0.593</v>
+      </c>
+      <c r="M86">
+        <v>3.03094512</v>
+      </c>
+      <c r="N86">
+        <v>-2.43794512</v>
+      </c>
+      <c r="O86">
+        <v>-0.3701126686252054</v>
+      </c>
+      <c r="P86">
+        <v>-2.067832451374795</v>
+      </c>
+      <c r="Q86">
+        <v>-1.868832451374795</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4672166085410648</v>
+      </c>
+      <c r="T86">
+        <v>5.087788443662575</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02970206514432941</v>
+      </c>
+      <c r="W86">
+        <v>0.2317071468435342</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1956485441082483</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2713886607151391</v>
+      </c>
+      <c r="C87">
+        <v>-7.173022220398138</v>
+      </c>
+      <c r="D87">
+        <v>4.21047777960186</v>
+      </c>
+      <c r="E87">
+        <v>11.4335</v>
+      </c>
+      <c r="F87">
+        <v>12.8435</v>
+      </c>
+      <c r="G87">
+        <v>1.46</v>
+      </c>
+      <c r="H87">
+        <v>13.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.792</v>
+      </c>
+      <c r="K87">
+        <v>0.199</v>
+      </c>
+      <c r="L87">
+        <v>0.593</v>
+      </c>
+      <c r="M87">
+        <v>3.0670278</v>
+      </c>
+      <c r="N87">
+        <v>-2.4740278</v>
+      </c>
+      <c r="O87">
+        <v>-0.3755905019350664</v>
+      </c>
+      <c r="P87">
+        <v>-2.098437298064934</v>
+      </c>
+      <c r="Q87">
+        <v>-1.899437298064934</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4957777157771359</v>
+      </c>
+      <c r="T87">
+        <v>5.426974339906747</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02935262908380788</v>
+      </c>
+      <c r="W87">
+        <v>0.2317905921747867</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1933467965305042</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2733886607151391</v>
+      </c>
+      <c r="C88">
+        <v>-7.360018906680982</v>
+      </c>
+      <c r="D88">
+        <v>4.174581093319018</v>
+      </c>
+      <c r="E88">
+        <v>11.5846</v>
+      </c>
+      <c r="F88">
+        <v>12.9946</v>
+      </c>
+      <c r="G88">
+        <v>1.46</v>
+      </c>
+      <c r="H88">
+        <v>13.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.792</v>
+      </c>
+      <c r="K88">
+        <v>0.199</v>
+      </c>
+      <c r="L88">
+        <v>0.593</v>
+      </c>
+      <c r="M88">
+        <v>3.10311048</v>
+      </c>
+      <c r="N88">
+        <v>-2.51011048</v>
+      </c>
+      <c r="O88">
+        <v>-0.3810683352449276</v>
+      </c>
+      <c r="P88">
+        <v>-2.129042144755073</v>
+      </c>
+      <c r="Q88">
+        <v>-1.930042144755073</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5284189811897884</v>
+      </c>
+      <c r="T88">
+        <v>5.8146153641858</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02901131944329849</v>
+      </c>
+      <c r="W88">
+        <v>0.2318720969169403</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.191098577966196</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.275388660715139</v>
+      </c>
+      <c r="C89">
+        <v>-7.546408688369591</v>
+      </c>
+      <c r="D89">
+        <v>4.139291311630409</v>
+      </c>
+      <c r="E89">
+        <v>11.7357</v>
+      </c>
+      <c r="F89">
+        <v>13.1457</v>
+      </c>
+      <c r="G89">
+        <v>1.46</v>
+      </c>
+      <c r="H89">
+        <v>13.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.792</v>
+      </c>
+      <c r="K89">
+        <v>0.199</v>
+      </c>
+      <c r="L89">
+        <v>0.593</v>
+      </c>
+      <c r="M89">
+        <v>3.13919316</v>
+      </c>
+      <c r="N89">
+        <v>-2.54619316</v>
+      </c>
+      <c r="O89">
+        <v>-0.3865461685547886</v>
+      </c>
+      <c r="P89">
+        <v>-2.159646991445212</v>
+      </c>
+      <c r="Q89">
+        <v>-1.960646991445212</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5660819797428489</v>
+      </c>
+      <c r="T89">
+        <v>6.261893469123168</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02867785600142149</v>
+      </c>
+      <c r="W89">
+        <v>0.2319517279868606</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1889020425872743</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2773886607151391</v>
+      </c>
+      <c r="C90">
+        <v>-7.732206827830398</v>
+      </c>
+      <c r="D90">
+        <v>4.104593172169602</v>
+      </c>
+      <c r="E90">
+        <v>11.8868</v>
+      </c>
+      <c r="F90">
+        <v>13.2968</v>
+      </c>
+      <c r="G90">
+        <v>1.46</v>
+      </c>
+      <c r="H90">
+        <v>13.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.792</v>
+      </c>
+      <c r="K90">
+        <v>0.199</v>
+      </c>
+      <c r="L90">
+        <v>0.593</v>
+      </c>
+      <c r="M90">
+        <v>3.17527584</v>
+      </c>
+      <c r="N90">
+        <v>-2.58227584</v>
+      </c>
+      <c r="O90">
+        <v>-0.3920240018646497</v>
+      </c>
+      <c r="P90">
+        <v>-2.19025183813535</v>
+      </c>
+      <c r="Q90">
+        <v>-1.99125183813535</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6100221447214198</v>
+      </c>
+      <c r="T90">
+        <v>6.783717924883434</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02835197127413262</v>
+      </c>
+      <c r="W90">
+        <v>0.2320295492597372</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1867554284669644</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2793886607151391</v>
+      </c>
+      <c r="C91">
+        <v>-7.917428079929054</v>
+      </c>
+      <c r="D91">
+        <v>4.070471920070945</v>
+      </c>
+      <c r="E91">
+        <v>12.0379</v>
+      </c>
+      <c r="F91">
+        <v>13.4479</v>
+      </c>
+      <c r="G91">
+        <v>1.46</v>
+      </c>
+      <c r="H91">
+        <v>13.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.792</v>
+      </c>
+      <c r="K91">
+        <v>0.199</v>
+      </c>
+      <c r="L91">
+        <v>0.593</v>
+      </c>
+      <c r="M91">
+        <v>3.21135852</v>
+      </c>
+      <c r="N91">
+        <v>-2.61835852</v>
+      </c>
+      <c r="O91">
+        <v>-0.3975018351745108</v>
+      </c>
+      <c r="P91">
+        <v>-2.220856684825489</v>
+      </c>
+      <c r="Q91">
+        <v>-2.021856684825489</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6619514306051852</v>
+      </c>
+      <c r="T91">
+        <v>7.400419554418291</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02803340979914236</v>
+      </c>
+      <c r="W91">
+        <v>0.2321056217399648</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1846570528662119</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2813886607151391</v>
+      </c>
+      <c r="C92">
+        <v>-8.102086712950658</v>
+      </c>
+      <c r="D92">
+        <v>4.036913287049342</v>
+      </c>
+      <c r="E92">
+        <v>12.189</v>
+      </c>
+      <c r="F92">
+        <v>13.599</v>
+      </c>
+      <c r="G92">
+        <v>1.46</v>
+      </c>
+      <c r="H92">
+        <v>13.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.792</v>
+      </c>
+      <c r="K92">
+        <v>0.199</v>
+      </c>
+      <c r="L92">
+        <v>0.593</v>
+      </c>
+      <c r="M92">
+        <v>3.2474412</v>
+      </c>
+      <c r="N92">
+        <v>-2.6544412</v>
+      </c>
+      <c r="O92">
+        <v>-0.402979668484372</v>
+      </c>
+      <c r="P92">
+        <v>-2.251461531515628</v>
+      </c>
+      <c r="Q92">
+        <v>-2.052461531515628</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7242665736657039</v>
+      </c>
+      <c r="T92">
+        <v>8.140461509860121</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02772192746804078</v>
+      </c>
+      <c r="W92">
+        <v>0.2321800037206319</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.182605307834365</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.283388660715139</v>
+      </c>
+      <c r="C93">
+        <v>-8.286196528493585</v>
+      </c>
+      <c r="D93">
+        <v>4.003903471506415</v>
+      </c>
+      <c r="E93">
+        <v>12.3401</v>
+      </c>
+      <c r="F93">
+        <v>13.7501</v>
+      </c>
+      <c r="G93">
+        <v>1.46</v>
+      </c>
+      <c r="H93">
+        <v>13.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.792</v>
+      </c>
+      <c r="K93">
+        <v>0.199</v>
+      </c>
+      <c r="L93">
+        <v>0.593</v>
+      </c>
+      <c r="M93">
+        <v>3.28352388</v>
+      </c>
+      <c r="N93">
+        <v>-2.69052388</v>
+      </c>
+      <c r="O93">
+        <v>-0.4084575017942331</v>
+      </c>
+      <c r="P93">
+        <v>-2.282066378205767</v>
+      </c>
+      <c r="Q93">
+        <v>-2.083066378205767</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8004295262952266</v>
+      </c>
+      <c r="T93">
+        <v>9.044957233177913</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02741729090245791</v>
+      </c>
+      <c r="W93">
+        <v>0.2322527509324931</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1805986560999215</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2853886607151391</v>
+      </c>
+      <c r="C94">
+        <v>-8.469770880395208</v>
+      </c>
+      <c r="D94">
+        <v>3.971429119604792</v>
+      </c>
+      <c r="E94">
+        <v>12.4912</v>
+      </c>
+      <c r="F94">
+        <v>13.9012</v>
+      </c>
+      <c r="G94">
+        <v>1.46</v>
+      </c>
+      <c r="H94">
+        <v>13.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.792</v>
+      </c>
+      <c r="K94">
+        <v>0.199</v>
+      </c>
+      <c r="L94">
+        <v>0.593</v>
+      </c>
+      <c r="M94">
+        <v>3.31960656</v>
+      </c>
+      <c r="N94">
+        <v>-2.72660656</v>
+      </c>
+      <c r="O94">
+        <v>-0.4139353351040941</v>
+      </c>
+      <c r="P94">
+        <v>-2.312671224895906</v>
+      </c>
+      <c r="Q94">
+        <v>-2.113671224895906</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8956332170821302</v>
+      </c>
+      <c r="T94">
+        <v>10.17557688732516</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02711927687090946</v>
+      </c>
+      <c r="W94">
+        <v>0.2323239166832268</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1786356272292702</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.287388660715139</v>
+      </c>
+      <c r="C95">
+        <v>-8.652822692744008</v>
+      </c>
+      <c r="D95">
+        <v>3.939477307255992</v>
+      </c>
+      <c r="E95">
+        <v>12.6423</v>
+      </c>
+      <c r="F95">
+        <v>14.0523</v>
+      </c>
+      <c r="G95">
+        <v>1.46</v>
+      </c>
+      <c r="H95">
+        <v>13.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.792</v>
+      </c>
+      <c r="K95">
+        <v>0.199</v>
+      </c>
+      <c r="L95">
+        <v>0.593</v>
+      </c>
+      <c r="M95">
+        <v>3.35568924</v>
+      </c>
+      <c r="N95">
+        <v>-2.76268924</v>
+      </c>
+      <c r="O95">
+        <v>-0.4194131684139553</v>
+      </c>
+      <c r="P95">
+        <v>-2.343276071586045</v>
+      </c>
+      <c r="Q95">
+        <v>-2.144276071586045</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.018037962379577</v>
+      </c>
+      <c r="T95">
+        <v>11.62923072837161</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02682767174326527</v>
+      </c>
+      <c r="W95">
+        <v>0.2323935519877083</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1767148140332565</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.289388660715139</v>
+      </c>
+      <c r="C96">
+        <v>-8.835364477029165</v>
+      </c>
+      <c r="D96">
+        <v>3.908035522970836</v>
+      </c>
+      <c r="E96">
+        <v>12.7934</v>
+      </c>
+      <c r="F96">
+        <v>14.2034</v>
+      </c>
+      <c r="G96">
+        <v>1.46</v>
+      </c>
+      <c r="H96">
+        <v>13.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.792</v>
+      </c>
+      <c r="K96">
+        <v>0.199</v>
+      </c>
+      <c r="L96">
+        <v>0.593</v>
+      </c>
+      <c r="M96">
+        <v>3.39177192</v>
+      </c>
+      <c r="N96">
+        <v>-2.79877192</v>
+      </c>
+      <c r="O96">
+        <v>-0.4248910017238163</v>
+      </c>
+      <c r="P96">
+        <v>-2.373880918276184</v>
+      </c>
+      <c r="Q96">
+        <v>-2.174880918276184</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.181244289442841</v>
+      </c>
+      <c r="T96">
+        <v>13.56743584976688</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02654227098003904</v>
+      </c>
+      <c r="W96">
+        <v>0.2324617056899667</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1748348692031155</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2913886607151391</v>
+      </c>
+      <c r="C97">
+        <v>-9.017408348475383</v>
+      </c>
+      <c r="D97">
+        <v>3.877091651524617</v>
+      </c>
+      <c r="E97">
+        <v>12.9445</v>
+      </c>
+      <c r="F97">
+        <v>14.3545</v>
+      </c>
+      <c r="G97">
+        <v>1.46</v>
+      </c>
+      <c r="H97">
+        <v>13.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.792</v>
+      </c>
+      <c r="K97">
+        <v>0.199</v>
+      </c>
+      <c r="L97">
+        <v>0.593</v>
+      </c>
+      <c r="M97">
+        <v>3.4278546</v>
+      </c>
+      <c r="N97">
+        <v>-2.8348546</v>
+      </c>
+      <c r="O97">
+        <v>-0.4303688350336775</v>
+      </c>
+      <c r="P97">
+        <v>-2.404485764966323</v>
+      </c>
+      <c r="Q97">
+        <v>-2.205485764966323</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.409733147331409</v>
+      </c>
+      <c r="T97">
+        <v>16.28092301972026</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02626287865393337</v>
+      </c>
+      <c r="W97">
+        <v>0.2325284245774407</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1729945021588721</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2933886607151391</v>
+      </c>
+      <c r="C98">
+        <v>-9.198966041607779</v>
+      </c>
+      <c r="D98">
+        <v>3.846633958392221</v>
+      </c>
+      <c r="E98">
+        <v>13.0956</v>
+      </c>
+      <c r="F98">
+        <v>14.5056</v>
+      </c>
+      <c r="G98">
+        <v>1.46</v>
+      </c>
+      <c r="H98">
+        <v>13.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.792</v>
+      </c>
+      <c r="K98">
+        <v>0.199</v>
+      </c>
+      <c r="L98">
+        <v>0.593</v>
+      </c>
+      <c r="M98">
+        <v>3.46393728</v>
+      </c>
+      <c r="N98">
+        <v>-2.87093728</v>
+      </c>
+      <c r="O98">
+        <v>-0.4358466683435386</v>
+      </c>
+      <c r="P98">
+        <v>-2.435090611656462</v>
+      </c>
+      <c r="Q98">
+        <v>-2.236090611656462</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.752466434164258</v>
+      </c>
+      <c r="T98">
+        <v>20.35115377465029</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02598930700128823</v>
+      </c>
+      <c r="W98">
+        <v>0.2325937534880924</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1711924760947172</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.295388660715139</v>
+      </c>
+      <c r="C99">
+        <v>-9.380048925088841</v>
+      </c>
+      <c r="D99">
+        <v>3.816651074911158</v>
+      </c>
+      <c r="E99">
+        <v>13.2467</v>
+      </c>
+      <c r="F99">
+        <v>14.6567</v>
+      </c>
+      <c r="G99">
+        <v>1.46</v>
+      </c>
+      <c r="H99">
+        <v>13.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.792</v>
+      </c>
+      <c r="K99">
+        <v>0.199</v>
+      </c>
+      <c r="L99">
+        <v>0.593</v>
+      </c>
+      <c r="M99">
+        <v>3.50001996</v>
+      </c>
+      <c r="N99">
+        <v>-2.90701996</v>
+      </c>
+      <c r="O99">
+        <v>-0.4413245016533996</v>
+      </c>
+      <c r="P99">
+        <v>-2.4656954583466</v>
+      </c>
+      <c r="Q99">
+        <v>-2.266695458346601</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.323688578885677</v>
+      </c>
+      <c r="T99">
+        <v>27.13487169953371</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02572137600127495</v>
+      </c>
+      <c r="W99">
+        <v>0.2326577354108955</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1694276052071428</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.297388660715139</v>
+      </c>
+      <c r="C100">
+        <v>-9.560668015866883</v>
+      </c>
+      <c r="D100">
+        <v>3.787131984133115</v>
+      </c>
+      <c r="E100">
+        <v>13.3978</v>
+      </c>
+      <c r="F100">
+        <v>14.8078</v>
+      </c>
+      <c r="G100">
+        <v>1.46</v>
+      </c>
+      <c r="H100">
+        <v>13.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.792</v>
+      </c>
+      <c r="K100">
+        <v>0.199</v>
+      </c>
+      <c r="L100">
+        <v>0.593</v>
+      </c>
+      <c r="M100">
+        <v>3.53610264</v>
+      </c>
+      <c r="N100">
+        <v>-2.94310264</v>
+      </c>
+      <c r="O100">
+        <v>-0.4468023349632607</v>
+      </c>
+      <c r="P100">
+        <v>-2.496300305036739</v>
+      </c>
+      <c r="Q100">
+        <v>-2.297300305036739</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.466132868328516</v>
+      </c>
+      <c r="T100">
+        <v>40.70230754930056</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02545891298085378</v>
+      </c>
+      <c r="W100">
+        <v>0.2327204115801721</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1676987520927843</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2993886607151391</v>
+      </c>
+      <c r="C101">
+        <v>-9.740833992672936</v>
+      </c>
+      <c r="D101">
+        <v>3.758066007327063</v>
+      </c>
+      <c r="E101">
+        <v>13.5489</v>
+      </c>
+      <c r="F101">
+        <v>14.9589</v>
+      </c>
+      <c r="G101">
+        <v>1.46</v>
+      </c>
+      <c r="H101">
+        <v>13.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.792</v>
+      </c>
+      <c r="K101">
+        <v>0.199</v>
+      </c>
+      <c r="L101">
+        <v>0.593</v>
+      </c>
+      <c r="M101">
+        <v>3.57218532</v>
+      </c>
+      <c r="N101">
+        <v>-2.97918532</v>
+      </c>
+      <c r="O101">
+        <v>-0.4522801682731218</v>
+      </c>
+      <c r="P101">
+        <v>-2.526905151726878</v>
+      </c>
+      <c r="Q101">
+        <v>-2.327905151726879</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.893465736657033</v>
+      </c>
+      <c r="T101">
+        <v>81.40461509860114</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02520175224367344</v>
+      </c>
+      <c r="W101">
+        <v>0.2327818215642108</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1660048253039683</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_transportation.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_transportation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2747239686578873</v>
+        <v>0.2742942879111689</v>
       </c>
       <c r="C2">
-        <v>14.27354000334623</v>
+        <v>14.1563207591093</v>
       </c>
       <c r="D2">
-        <v>11.68354000334623</v>
+        <v>11.70551075910929</v>
       </c>
       <c r="E2">
-        <v>-0.9190000000000002</v>
+        <v>-0.7798100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.13919</v>
       </c>
       <c r="G2">
         <v>2.59</v>
@@ -1445,28 +1445,28 @@
         <v>0.529</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.007001257</v>
       </c>
       <c r="N2">
-        <v>0.529</v>
+        <v>0.521998743</v>
       </c>
       <c r="O2">
-        <v>0.08993000000000001</v>
+        <v>0.08873978631000001</v>
       </c>
       <c r="P2">
-        <v>0.43907</v>
+        <v>0.43325895669</v>
       </c>
       <c r="Q2">
-        <v>0.6100699999999999</v>
+        <v>0.60425895669</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2747239686578873</v>
+        <v>0.2766432302133019</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8267234494815396</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>75.55786053847189</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2742942879111689</v>
+        <v>0.2738646071644504</v>
       </c>
       <c r="C3">
-        <v>14.1563207591093</v>
+        <v>14.03918430203395</v>
       </c>
       <c r="D3">
-        <v>11.70551075910929</v>
+        <v>11.72756430203395</v>
       </c>
       <c r="E3">
-        <v>-0.7798100000000001</v>
+        <v>-0.6406200000000002</v>
       </c>
       <c r="F3">
-        <v>0.13919</v>
+        <v>0.27838</v>
       </c>
       <c r="G3">
         <v>2.59</v>
@@ -1527,28 +1527,28 @@
         <v>0.529</v>
       </c>
       <c r="M3">
-        <v>0.007001257</v>
+        <v>0.014002514</v>
       </c>
       <c r="N3">
-        <v>0.521998743</v>
+        <v>0.5149974860000001</v>
       </c>
       <c r="O3">
-        <v>0.08873978631000001</v>
+        <v>0.08754957262000002</v>
       </c>
       <c r="P3">
-        <v>0.43325895669</v>
+        <v>0.42744791338</v>
       </c>
       <c r="Q3">
-        <v>0.60425895669</v>
+        <v>0.59844791338</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2766432302133019</v>
+        <v>0.2786016603718882</v>
       </c>
       <c r="T3">
-        <v>0.8267234494815396</v>
+        <v>0.8337372143416967</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>75.55786053847189</v>
+        <v>37.77893026923594</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2738646071644504</v>
+        <v>0.273434926417732</v>
       </c>
       <c r="C4">
-        <v>14.03918430203395</v>
+        <v>13.92213110092411</v>
       </c>
       <c r="D4">
-        <v>11.72756430203395</v>
+        <v>11.74970110092411</v>
       </c>
       <c r="E4">
-        <v>-0.6406200000000002</v>
+        <v>-0.5014300000000002</v>
       </c>
       <c r="F4">
-        <v>0.27838</v>
+        <v>0.41757</v>
       </c>
       <c r="G4">
         <v>2.59</v>
@@ -1609,28 +1609,28 @@
         <v>0.529</v>
       </c>
       <c r="M4">
-        <v>0.014002514</v>
+        <v>0.021003771</v>
       </c>
       <c r="N4">
-        <v>0.5149974860000001</v>
+        <v>0.5079962290000001</v>
       </c>
       <c r="O4">
-        <v>0.08754957262000002</v>
+        <v>0.08635935893000002</v>
       </c>
       <c r="P4">
-        <v>0.42744791338</v>
+        <v>0.4216368700700001</v>
       </c>
       <c r="Q4">
-        <v>0.59844791338</v>
+        <v>0.59263687007</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2786016603718882</v>
+        <v>0.2806004705337444</v>
       </c>
       <c r="T4">
-        <v>0.8337372143416967</v>
+        <v>0.8408955929103105</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>37.77893026923594</v>
+        <v>25.18595351282396</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.273434926417732</v>
+        <v>0.2730052456710136</v>
       </c>
       <c r="C5">
-        <v>13.92213110092411</v>
+        <v>13.80516162813004</v>
       </c>
       <c r="D5">
-        <v>11.74970110092411</v>
+        <v>11.77192162813004</v>
       </c>
       <c r="E5">
-        <v>-0.5014300000000002</v>
+        <v>-0.3622400000000001</v>
       </c>
       <c r="F5">
-        <v>0.41757</v>
+        <v>0.55676</v>
       </c>
       <c r="G5">
         <v>2.59</v>
@@ -1691,28 +1691,28 @@
         <v>0.529</v>
       </c>
       <c r="M5">
-        <v>0.021003771</v>
+        <v>0.028005028</v>
       </c>
       <c r="N5">
-        <v>0.5079962290000001</v>
+        <v>0.500994972</v>
       </c>
       <c r="O5">
-        <v>0.08635935893000002</v>
+        <v>0.08516914524000001</v>
       </c>
       <c r="P5">
-        <v>0.4216368700700001</v>
+        <v>0.41582582676</v>
       </c>
       <c r="Q5">
-        <v>0.59263687007</v>
+        <v>0.5868258267599999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2806004705337444</v>
+        <v>0.2826409225739726</v>
       </c>
       <c r="T5">
-        <v>0.8408955929103105</v>
+        <v>0.8482031043657704</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.18595351282396</v>
+        <v>18.88946513461797</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2730052456710136</v>
+        <v>0.2725755649242952</v>
       </c>
       <c r="C6">
-        <v>13.80516162813004</v>
+        <v>13.68827635958192</v>
       </c>
       <c r="D6">
-        <v>11.77192162813004</v>
+        <v>11.79422635958192</v>
       </c>
       <c r="E6">
-        <v>-0.3622400000000001</v>
+        <v>-0.2230500000000001</v>
       </c>
       <c r="F6">
-        <v>0.55676</v>
+        <v>0.6959500000000001</v>
       </c>
       <c r="G6">
         <v>2.59</v>
@@ -1773,28 +1773,28 @@
         <v>0.529</v>
       </c>
       <c r="M6">
-        <v>0.028005028</v>
+        <v>0.03500628500000001</v>
       </c>
       <c r="N6">
-        <v>0.500994972</v>
+        <v>0.493993715</v>
       </c>
       <c r="O6">
-        <v>0.08516914524000001</v>
+        <v>0.08397893155000001</v>
       </c>
       <c r="P6">
-        <v>0.41582582676</v>
+        <v>0.41001478345</v>
       </c>
       <c r="Q6">
-        <v>0.5868258267599999</v>
+        <v>0.5810147834499999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2826409225739726</v>
+        <v>0.2847243314992581</v>
       </c>
       <c r="T6">
-        <v>0.8482031043657704</v>
+        <v>0.8556644581676609</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.88946513461797</v>
+        <v>15.11157210769437</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2725755649242952</v>
+        <v>0.2722205841775768</v>
       </c>
       <c r="C7">
-        <v>13.68827635958192</v>
+        <v>13.56757727239048</v>
       </c>
       <c r="D7">
-        <v>11.79422635958192</v>
+        <v>11.81271727239048</v>
       </c>
       <c r="E7">
-        <v>-0.2230500000000001</v>
+        <v>-0.08386000000000005</v>
       </c>
       <c r="F7">
-        <v>0.6959500000000001</v>
+        <v>0.8351400000000001</v>
       </c>
       <c r="G7">
         <v>2.59</v>
@@ -1855,45 +1855,45 @@
         <v>0.529</v>
       </c>
       <c r="M7">
-        <v>0.03500628500000001</v>
+        <v>0.04326025200000001</v>
       </c>
       <c r="N7">
-        <v>0.493993715</v>
+        <v>0.485739748</v>
       </c>
       <c r="O7">
-        <v>0.08397893155000001</v>
+        <v>0.08257575716000001</v>
       </c>
       <c r="P7">
-        <v>0.41001478345</v>
+        <v>0.40316399084</v>
       </c>
       <c r="Q7">
-        <v>0.5810147834499999</v>
+        <v>0.5741639908399999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2847243314992581</v>
+        <v>0.2868520682740179</v>
       </c>
       <c r="T7">
-        <v>0.8556644581676609</v>
+        <v>0.8632845641781025</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.17</v>
       </c>
       <c r="W7">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>15.11157210769437</v>
+        <v>12.22831526732669</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2722205841775768</v>
+        <v>0.2718033534308584</v>
       </c>
       <c r="C8">
-        <v>13.56757727239048</v>
+        <v>13.45019504105193</v>
       </c>
       <c r="D8">
-        <v>11.81271727239048</v>
+        <v>11.83452504105193</v>
       </c>
       <c r="E8">
-        <v>-0.08386000000000016</v>
+        <v>0.05532999999999977</v>
       </c>
       <c r="F8">
-        <v>0.83514</v>
+        <v>0.9743299999999999</v>
       </c>
       <c r="G8">
         <v>2.59</v>
@@ -1937,28 +1937,28 @@
         <v>0.529</v>
       </c>
       <c r="M8">
-        <v>0.043260252</v>
+        <v>0.05047029399999999</v>
       </c>
       <c r="N8">
-        <v>0.485739748</v>
+        <v>0.4785297060000001</v>
       </c>
       <c r="O8">
-        <v>0.08257575716000001</v>
+        <v>0.08135005002000001</v>
       </c>
       <c r="P8">
-        <v>0.40316399084</v>
+        <v>0.39717965598</v>
       </c>
       <c r="Q8">
-        <v>0.5741639908399999</v>
+        <v>0.56817965598</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2868520682740179</v>
+        <v>0.28902556282888</v>
       </c>
       <c r="T8">
-        <v>0.8632845641781025</v>
+        <v>0.8710685434360803</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.22831526732669</v>
+        <v>10.48141308628002</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2718033534308584</v>
+        <v>0.27149900268414</v>
       </c>
       <c r="C9">
-        <v>13.45019504105193</v>
+        <v>13.32696366953707</v>
       </c>
       <c r="D9">
-        <v>11.83452504105193</v>
+        <v>11.85048366953707</v>
       </c>
       <c r="E9">
-        <v>0.05532999999999999</v>
+        <v>0.1945199999999999</v>
       </c>
       <c r="F9">
-        <v>0.9743300000000001</v>
+        <v>1.11352</v>
       </c>
       <c r="G9">
         <v>2.59</v>
@@ -2019,45 +2019,45 @@
         <v>0.529</v>
       </c>
       <c r="M9">
-        <v>0.05047029400000001</v>
+        <v>0.05957332</v>
       </c>
       <c r="N9">
-        <v>0.478529706</v>
+        <v>0.46942668</v>
       </c>
       <c r="O9">
-        <v>0.08135005002000001</v>
+        <v>0.07980253560000002</v>
       </c>
       <c r="P9">
-        <v>0.39717965598</v>
+        <v>0.3896241444</v>
       </c>
       <c r="Q9">
-        <v>0.5681796559799999</v>
+        <v>0.5606241444</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.28902556282888</v>
+        <v>0.2912463072653695</v>
       </c>
       <c r="T9">
-        <v>0.8710685434360803</v>
+        <v>0.879021739634449</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.17</v>
       </c>
       <c r="W9">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.48141308628002</v>
+        <v>8.879813983843775</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.27149900268414</v>
+        <v>0.2710958819374216</v>
       </c>
       <c r="C10">
-        <v>13.32696366953707</v>
+        <v>13.20897767817121</v>
       </c>
       <c r="D10">
-        <v>11.85048366953707</v>
+        <v>11.87168767817121</v>
       </c>
       <c r="E10">
-        <v>0.1945199999999999</v>
+        <v>0.3337099999999998</v>
       </c>
       <c r="F10">
-        <v>1.11352</v>
+        <v>1.25271</v>
       </c>
       <c r="G10">
         <v>2.59</v>
@@ -2101,28 +2101,28 @@
         <v>0.529</v>
       </c>
       <c r="M10">
-        <v>0.05957332</v>
+        <v>0.067019985</v>
       </c>
       <c r="N10">
-        <v>0.46942668</v>
+        <v>0.461980015</v>
       </c>
       <c r="O10">
-        <v>0.07980253560000002</v>
+        <v>0.07853660255000001</v>
       </c>
       <c r="P10">
-        <v>0.3896241444</v>
+        <v>0.38344341245</v>
       </c>
       <c r="Q10">
-        <v>0.5606241444</v>
+        <v>0.55444341245</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2912463072653695</v>
+        <v>0.2935158592718919</v>
       </c>
       <c r="T10">
-        <v>0.879021739634449</v>
+        <v>0.887149731353661</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.879813983843775</v>
+        <v>7.89316798563891</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2710958819374216</v>
+        <v>0.2707591611907031</v>
       </c>
       <c r="C11">
-        <v>13.20897767817121</v>
+        <v>13.08755731919691</v>
       </c>
       <c r="D11">
-        <v>11.87168767817121</v>
+        <v>11.88945731919691</v>
       </c>
       <c r="E11">
-        <v>0.3337099999999998</v>
+        <v>0.4728999999999998</v>
       </c>
       <c r="F11">
-        <v>1.25271</v>
+        <v>1.3919</v>
       </c>
       <c r="G11">
         <v>2.59</v>
@@ -2183,45 +2183,45 @@
         <v>0.529</v>
       </c>
       <c r="M11">
-        <v>0.067019985</v>
+        <v>0.07558017</v>
       </c>
       <c r="N11">
-        <v>0.461980015</v>
+        <v>0.45341983</v>
       </c>
       <c r="O11">
-        <v>0.07853660255000001</v>
+        <v>0.0770813711</v>
       </c>
       <c r="P11">
-        <v>0.38344341245</v>
+        <v>0.3763384589</v>
       </c>
       <c r="Q11">
-        <v>0.55444341245</v>
+        <v>0.5473384588999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2935158592718919</v>
+        <v>0.295835845767448</v>
       </c>
       <c r="T11">
-        <v>0.887149731353661</v>
+        <v>0.8954583451110777</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.17</v>
       </c>
       <c r="W11">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.89316798563891</v>
+        <v>6.999190396105222</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2707591611907031</v>
+        <v>0.2703626804439848</v>
       </c>
       <c r="C12">
-        <v>13.08755731919691</v>
+        <v>12.96935896797253</v>
       </c>
       <c r="D12">
-        <v>11.88945731919691</v>
+        <v>11.91044896797253</v>
       </c>
       <c r="E12">
-        <v>0.4729</v>
+        <v>0.6120899999999999</v>
       </c>
       <c r="F12">
-        <v>1.3919</v>
+        <v>1.53109</v>
       </c>
       <c r="G12">
         <v>2.59</v>
@@ -2265,28 +2265,28 @@
         <v>0.529</v>
       </c>
       <c r="M12">
-        <v>0.07558017</v>
+        <v>0.083138187</v>
       </c>
       <c r="N12">
-        <v>0.45341983</v>
+        <v>0.4458618130000001</v>
       </c>
       <c r="O12">
-        <v>0.0770813711</v>
+        <v>0.07579650821000002</v>
       </c>
       <c r="P12">
-        <v>0.3763384589</v>
+        <v>0.37006530479</v>
       </c>
       <c r="Q12">
-        <v>0.5473384588999999</v>
+        <v>0.54106530479</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.295835845767448</v>
+        <v>0.2982079667909942</v>
       </c>
       <c r="T12">
-        <v>0.8954583451110777</v>
+        <v>0.9039536692900093</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.999190396105222</v>
+        <v>6.362900360095657</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2703626804439848</v>
+        <v>0.2700657996972664</v>
       </c>
       <c r="C13">
-        <v>12.96935896797253</v>
+        <v>12.84593589716163</v>
       </c>
       <c r="D13">
-        <v>11.91044896797253</v>
+        <v>11.92621589716163</v>
       </c>
       <c r="E13">
-        <v>0.6120899999999999</v>
+        <v>0.7512799999999998</v>
       </c>
       <c r="F13">
-        <v>1.53109</v>
+        <v>1.67028</v>
       </c>
       <c r="G13">
         <v>2.59</v>
@@ -2347,45 +2347,45 @@
         <v>0.529</v>
       </c>
       <c r="M13">
-        <v>0.083138187</v>
+        <v>0.092366484</v>
       </c>
       <c r="N13">
-        <v>0.4458618130000001</v>
+        <v>0.436633516</v>
       </c>
       <c r="O13">
-        <v>0.07579650821000002</v>
+        <v>0.07422769772</v>
       </c>
       <c r="P13">
-        <v>0.37006530479</v>
+        <v>0.36240581828</v>
       </c>
       <c r="Q13">
-        <v>0.54106530479</v>
+        <v>0.5334058182799999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2982079667909942</v>
+        <v>0.3006339996559845</v>
       </c>
       <c r="T13">
-        <v>0.9039536692900093</v>
+        <v>0.9126420690184622</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.17</v>
       </c>
       <c r="W13">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.362900360095657</v>
+        <v>5.727185631532754</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2700657996972664</v>
+        <v>0.269677618950548</v>
       </c>
       <c r="C14">
-        <v>12.84593589716163</v>
+        <v>12.7274247279183</v>
       </c>
       <c r="D14">
-        <v>11.92621589716163</v>
+        <v>11.9468947279183</v>
       </c>
       <c r="E14">
-        <v>0.7512799999999998</v>
+        <v>0.89047</v>
       </c>
       <c r="F14">
-        <v>1.67028</v>
+        <v>1.80947</v>
       </c>
       <c r="G14">
         <v>2.59</v>
@@ -2429,28 +2429,28 @@
         <v>0.529</v>
       </c>
       <c r="M14">
-        <v>0.092366484</v>
+        <v>0.100063691</v>
       </c>
       <c r="N14">
-        <v>0.436633516</v>
+        <v>0.428936309</v>
       </c>
       <c r="O14">
-        <v>0.07422769772</v>
+        <v>0.07291917253000001</v>
       </c>
       <c r="P14">
-        <v>0.36240581828</v>
+        <v>0.35601713647</v>
       </c>
       <c r="Q14">
-        <v>0.5334058182799999</v>
+        <v>0.5270171364699999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.3006339996559845</v>
+        <v>0.3031158033914345</v>
       </c>
       <c r="T14">
-        <v>0.9126420690184622</v>
+        <v>0.9215302020740059</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.727185631532754</v>
+        <v>5.286632890645619</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.269677618950548</v>
+        <v>0.2692894382038296</v>
       </c>
       <c r="C15">
-        <v>12.7274247279183</v>
+        <v>12.60898539315654</v>
       </c>
       <c r="D15">
-        <v>11.9468947279183</v>
+        <v>11.96764539315654</v>
       </c>
       <c r="E15">
-        <v>0.89047</v>
+        <v>1.02966</v>
       </c>
       <c r="F15">
-        <v>1.80947</v>
+        <v>1.94866</v>
       </c>
       <c r="G15">
         <v>2.59</v>
@@ -2511,28 +2511,28 @@
         <v>0.529</v>
       </c>
       <c r="M15">
-        <v>0.100063691</v>
+        <v>0.107760898</v>
       </c>
       <c r="N15">
-        <v>0.428936309</v>
+        <v>0.421239102</v>
       </c>
       <c r="O15">
-        <v>0.07291917253000001</v>
+        <v>0.07161064734000001</v>
       </c>
       <c r="P15">
-        <v>0.35601713647</v>
+        <v>0.34962845466</v>
       </c>
       <c r="Q15">
-        <v>0.5270171364699999</v>
+        <v>0.52062845466</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.3031158033914345</v>
+        <v>0.3056553234928251</v>
       </c>
       <c r="T15">
-        <v>0.9215302020740059</v>
+        <v>0.9306250358982833</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.286632890645619</v>
+        <v>4.909016255599503</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2692894382038296</v>
+        <v>0.2689012574571111</v>
       </c>
       <c r="C16">
-        <v>12.60898539315654</v>
+        <v>12.49061826783742</v>
       </c>
       <c r="D16">
-        <v>11.96764539315654</v>
+        <v>11.98846826783742</v>
       </c>
       <c r="E16">
-        <v>1.02966</v>
+        <v>1.16885</v>
       </c>
       <c r="F16">
-        <v>1.94866</v>
+        <v>2.08785</v>
       </c>
       <c r="G16">
         <v>2.59</v>
@@ -2593,28 +2593,28 @@
         <v>0.529</v>
       </c>
       <c r="M16">
-        <v>0.107760898</v>
+        <v>0.115458105</v>
       </c>
       <c r="N16">
-        <v>0.421239102</v>
+        <v>0.413541895</v>
       </c>
       <c r="O16">
-        <v>0.07161064734000001</v>
+        <v>0.07030212215000001</v>
       </c>
       <c r="P16">
-        <v>0.34962845466</v>
+        <v>0.34323977285</v>
       </c>
       <c r="Q16">
-        <v>0.52062845466</v>
+        <v>0.5142397728499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.3056553234928251</v>
+        <v>0.308254597008366</v>
       </c>
       <c r="T16">
-        <v>0.9306250358982833</v>
+        <v>0.9399338658125435</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.909016255599503</v>
+        <v>4.581748505226201</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2689012574571111</v>
+        <v>0.2688450767103928</v>
       </c>
       <c r="C17">
-        <v>12.49061826783742</v>
+        <v>12.3544479314374</v>
       </c>
       <c r="D17">
-        <v>11.98846826783742</v>
+        <v>11.9914879314374</v>
       </c>
       <c r="E17">
-        <v>1.16885</v>
+        <v>1.30804</v>
       </c>
       <c r="F17">
-        <v>2.08785</v>
+        <v>2.22704</v>
       </c>
       <c r="G17">
         <v>2.59</v>
@@ -2675,45 +2675,45 @@
         <v>0.529</v>
       </c>
       <c r="M17">
-        <v>0.115458105</v>
+        <v>0.128722912</v>
       </c>
       <c r="N17">
-        <v>0.413541895</v>
+        <v>0.400277088</v>
       </c>
       <c r="O17">
-        <v>0.07030212215000001</v>
+        <v>0.06804710496000001</v>
       </c>
       <c r="P17">
-        <v>0.3432397728500001</v>
+        <v>0.33222998304</v>
       </c>
       <c r="Q17">
-        <v>0.51423977285</v>
+        <v>0.50322998304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.308254597008366</v>
+        <v>0.3109157579885628</v>
       </c>
       <c r="T17">
-        <v>0.9399338658125435</v>
+        <v>0.9494643345342861</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.17</v>
       </c>
       <c r="W17">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.581748505226203</v>
+        <v>4.109602492522853</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2688450767103928</v>
+        <v>0.2689714959636744</v>
       </c>
       <c r="C18">
-        <v>12.3544479314374</v>
+        <v>12.20846515109831</v>
       </c>
       <c r="D18">
-        <v>11.9914879314374</v>
+        <v>11.98469515109831</v>
       </c>
       <c r="E18">
-        <v>1.30804</v>
+        <v>1.44723</v>
       </c>
       <c r="F18">
-        <v>2.22704</v>
+        <v>2.36623</v>
       </c>
       <c r="G18">
         <v>2.59</v>
@@ -2757,45 +2757,45 @@
         <v>0.529</v>
       </c>
       <c r="M18">
-        <v>0.128722912</v>
+        <v>0.145049899</v>
       </c>
       <c r="N18">
-        <v>0.400277088</v>
+        <v>0.383950101</v>
       </c>
       <c r="O18">
-        <v>0.06804710496000001</v>
+        <v>0.06527151717000002</v>
       </c>
       <c r="P18">
-        <v>0.33222998304</v>
+        <v>0.31867858383</v>
       </c>
       <c r="Q18">
-        <v>0.50322998304</v>
+        <v>0.48967858383</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.3109157579885628</v>
+        <v>0.3136410433297281</v>
       </c>
       <c r="T18">
-        <v>0.9494643345342861</v>
+        <v>0.9592244531047455</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.17</v>
       </c>
       <c r="W18">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.109602492522853</v>
+        <v>3.647020809025176</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2689714959636744</v>
+        <v>0.269051435216956</v>
       </c>
       <c r="C19">
-        <v>12.20846515109831</v>
+        <v>12.06498381214116</v>
       </c>
       <c r="D19">
-        <v>11.98469515109831</v>
+        <v>11.98040381214116</v>
       </c>
       <c r="E19">
-        <v>1.44723</v>
+        <v>1.58642</v>
       </c>
       <c r="F19">
-        <v>2.36623</v>
+        <v>2.50542</v>
       </c>
       <c r="G19">
         <v>2.59</v>
@@ -2839,45 +2839,45 @@
         <v>0.529</v>
       </c>
       <c r="M19">
-        <v>0.145049899</v>
+        <v>0.160597422</v>
       </c>
       <c r="N19">
-        <v>0.383950101</v>
+        <v>0.368402578</v>
       </c>
       <c r="O19">
-        <v>0.06527151717000002</v>
+        <v>0.06262843826</v>
       </c>
       <c r="P19">
-        <v>0.31867858383</v>
+        <v>0.30577413974</v>
       </c>
       <c r="Q19">
-        <v>0.48967858383</v>
+        <v>0.4767741397399999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.3136410433297281</v>
+        <v>0.3164327990450682</v>
       </c>
       <c r="T19">
-        <v>0.9592244531047455</v>
+        <v>0.9692226233476551</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.647020809025176</v>
+        <v>3.293950758437454</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.269051435216956</v>
+        <v>0.2687362944702376</v>
       </c>
       <c r="C20">
-        <v>12.06498381214116</v>
+        <v>11.94272920353769</v>
       </c>
       <c r="D20">
-        <v>11.98040381214116</v>
+        <v>11.99733920353769</v>
       </c>
       <c r="E20">
-        <v>1.58642</v>
+        <v>1.72561</v>
       </c>
       <c r="F20">
-        <v>2.50542</v>
+        <v>2.64461</v>
       </c>
       <c r="G20">
         <v>2.59</v>
@@ -2921,28 +2921,28 @@
         <v>0.529</v>
       </c>
       <c r="M20">
-        <v>0.160597422</v>
+        <v>0.169519501</v>
       </c>
       <c r="N20">
-        <v>0.368402578</v>
+        <v>0.359480499</v>
       </c>
       <c r="O20">
-        <v>0.06262843826</v>
+        <v>0.06111168483000001</v>
       </c>
       <c r="P20">
-        <v>0.30577413974</v>
+        <v>0.29836881417</v>
       </c>
       <c r="Q20">
-        <v>0.4767741397399999</v>
+        <v>0.4693688141699999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.3164327990450682</v>
+        <v>0.3192934870002933</v>
       </c>
       <c r="T20">
-        <v>0.9692226233476551</v>
+        <v>0.9794676619916242</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.293950758437454</v>
+        <v>3.12058492904601</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2687362944702376</v>
+        <v>0.2697159537235191</v>
       </c>
       <c r="C21">
-        <v>11.94272920353769</v>
+        <v>11.75104940024294</v>
       </c>
       <c r="D21">
-        <v>11.99733920353769</v>
+        <v>11.94484940024295</v>
       </c>
       <c r="E21">
-        <v>1.72561</v>
+        <v>1.8648</v>
       </c>
       <c r="F21">
-        <v>2.64461</v>
+        <v>2.7838</v>
       </c>
       <c r="G21">
         <v>2.59</v>
@@ -3003,45 +3003,45 @@
         <v>0.529</v>
       </c>
       <c r="M21">
-        <v>0.169519501</v>
+        <v>0.20015522</v>
       </c>
       <c r="N21">
-        <v>0.359480499</v>
+        <v>0.32884478</v>
       </c>
       <c r="O21">
-        <v>0.06111168483000001</v>
+        <v>0.05590361260000001</v>
       </c>
       <c r="P21">
-        <v>0.29836881417</v>
+        <v>0.2729411674</v>
       </c>
       <c r="Q21">
-        <v>0.4693688141699999</v>
+        <v>0.4439411673999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.3192934870002933</v>
+        <v>0.3222256921543989</v>
       </c>
       <c r="T21">
-        <v>0.9794676619916242</v>
+        <v>0.9899688266016925</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.17</v>
       </c>
       <c r="W21">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.12058492904601</v>
+        <v>2.642948807430553</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2697159537235191</v>
+        <v>0.2694655529768007</v>
       </c>
       <c r="C22">
-        <v>11.75104940024294</v>
+        <v>11.6252320415346</v>
       </c>
       <c r="D22">
-        <v>11.94484940024295</v>
+        <v>11.9582220415346</v>
       </c>
       <c r="E22">
-        <v>1.8648</v>
+        <v>2.00399</v>
       </c>
       <c r="F22">
-        <v>2.7838</v>
+        <v>2.92299</v>
       </c>
       <c r="G22">
         <v>2.59</v>
@@ -3085,28 +3085,28 @@
         <v>0.529</v>
       </c>
       <c r="M22">
-        <v>0.20015522</v>
+        <v>0.2101629810000001</v>
       </c>
       <c r="N22">
-        <v>0.32884478</v>
+        <v>0.3188370189999999</v>
       </c>
       <c r="O22">
-        <v>0.05590361260000001</v>
+        <v>0.05420229323</v>
       </c>
       <c r="P22">
-        <v>0.2729411674</v>
+        <v>0.26463472577</v>
       </c>
       <c r="Q22">
-        <v>0.4439411673999999</v>
+        <v>0.4356347257699999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.3222256921543989</v>
+        <v>0.3252321303503807</v>
       </c>
       <c r="T22">
-        <v>0.9899688266016925</v>
+        <v>1.00073584348037</v>
       </c>
       <c r="U22">
         <v>0.07190000000000001</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.642948807430553</v>
+        <v>2.517094102314812</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2694655529768007</v>
+        <v>0.2699272922300823</v>
       </c>
       <c r="C23">
-        <v>11.6252320415346</v>
+        <v>11.4614061283395</v>
       </c>
       <c r="D23">
-        <v>11.9582220415346</v>
+        <v>11.9335861283395</v>
       </c>
       <c r="E23">
-        <v>2.00399</v>
+        <v>2.14318</v>
       </c>
       <c r="F23">
-        <v>2.92299</v>
+        <v>3.06218</v>
       </c>
       <c r="G23">
         <v>2.59</v>
@@ -3167,45 +3167,45 @@
         <v>0.529</v>
       </c>
       <c r="M23">
-        <v>0.210162981</v>
+        <v>0.232113244</v>
       </c>
       <c r="N23">
-        <v>0.318837019</v>
+        <v>0.296886756</v>
       </c>
       <c r="O23">
-        <v>0.05420229323</v>
+        <v>0.05047074852000001</v>
       </c>
       <c r="P23">
-        <v>0.26463472577</v>
+        <v>0.24641600748</v>
       </c>
       <c r="Q23">
-        <v>0.43563472577</v>
+        <v>0.41741600748</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.3252321303503807</v>
+        <v>0.3283156567052337</v>
       </c>
       <c r="T23">
-        <v>1.00073584348037</v>
+        <v>1.011778937714911</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.17</v>
       </c>
       <c r="W23">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.517094102314812</v>
+        <v>2.279059957474895</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2699272922300823</v>
+        <v>0.2697092614833639</v>
       </c>
       <c r="C24">
-        <v>11.4614061283395</v>
+        <v>11.33383641004359</v>
       </c>
       <c r="D24">
-        <v>11.9335861283395</v>
+        <v>11.94520641004359</v>
       </c>
       <c r="E24">
-        <v>2.14318</v>
+        <v>2.28237</v>
       </c>
       <c r="F24">
-        <v>3.06218</v>
+        <v>3.20137</v>
       </c>
       <c r="G24">
         <v>2.59</v>
@@ -3249,28 +3249,28 @@
         <v>0.529</v>
       </c>
       <c r="M24">
-        <v>0.232113244</v>
+        <v>0.242663846</v>
       </c>
       <c r="N24">
-        <v>0.296886756</v>
+        <v>0.286336154</v>
       </c>
       <c r="O24">
-        <v>0.05047074852000001</v>
+        <v>0.04867714618000001</v>
       </c>
       <c r="P24">
-        <v>0.24641600748</v>
+        <v>0.23765900782</v>
       </c>
       <c r="Q24">
-        <v>0.41741600748</v>
+        <v>0.4086590078199999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.3283156567052337</v>
+        <v>0.3314792746537193</v>
       </c>
       <c r="T24">
-        <v>1.011778937714911</v>
+        <v>1.023108865565934</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.279059957474895</v>
+        <v>2.179970394106421</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2697092614833639</v>
+        <v>0.2694912307366455</v>
       </c>
       <c r="C25">
-        <v>11.33383641004359</v>
+        <v>11.20628934421097</v>
       </c>
       <c r="D25">
-        <v>11.94520641004359</v>
+        <v>11.95684934421097</v>
       </c>
       <c r="E25">
-        <v>2.28237</v>
+        <v>2.42156</v>
       </c>
       <c r="F25">
-        <v>3.20137</v>
+        <v>3.34056</v>
       </c>
       <c r="G25">
         <v>2.59</v>
@@ -3331,28 +3331,28 @@
         <v>0.529</v>
       </c>
       <c r="M25">
-        <v>0.242663846</v>
+        <v>0.253214448</v>
       </c>
       <c r="N25">
-        <v>0.286336154</v>
+        <v>0.275785552</v>
       </c>
       <c r="O25">
-        <v>0.04867714618000001</v>
+        <v>0.04688354384</v>
       </c>
       <c r="P25">
-        <v>0.23765900782</v>
+        <v>0.22890200816</v>
       </c>
       <c r="Q25">
-        <v>0.4086590078199999</v>
+        <v>0.3999020081599999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.3314792746537193</v>
+        <v>0.3347261457061125</v>
       </c>
       <c r="T25">
-        <v>1.023108865565934</v>
+        <v>1.034736949413036</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.179970394106421</v>
+        <v>2.089138294351987</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2694912307366455</v>
+        <v>0.269273199989927</v>
       </c>
       <c r="C26">
-        <v>11.20628934421097</v>
+        <v>11.07876499714401</v>
       </c>
       <c r="D26">
-        <v>11.95684934421097</v>
+        <v>11.96851499714401</v>
       </c>
       <c r="E26">
-        <v>2.42156</v>
+        <v>2.56075</v>
       </c>
       <c r="F26">
-        <v>3.34056</v>
+        <v>3.47975</v>
       </c>
       <c r="G26">
         <v>2.59</v>
@@ -3413,28 +3413,28 @@
         <v>0.529</v>
       </c>
       <c r="M26">
-        <v>0.253214448</v>
+        <v>0.2637650500000001</v>
       </c>
       <c r="N26">
-        <v>0.275785552</v>
+        <v>0.26523495</v>
       </c>
       <c r="O26">
-        <v>0.04688354384</v>
+        <v>0.0450899415</v>
       </c>
       <c r="P26">
-        <v>0.22890200816</v>
+        <v>0.2201450085</v>
       </c>
       <c r="Q26">
-        <v>0.3999020081599999</v>
+        <v>0.3911450084999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.3347261457061125</v>
+        <v>0.3380595999865694</v>
       </c>
       <c r="T26">
-        <v>1.034736949413036</v>
+        <v>1.046675115496061</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.089138294351987</v>
+        <v>2.005572762577907</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.269273199989927</v>
+        <v>0.2721195292432087</v>
       </c>
       <c r="C27">
-        <v>11.07876499714401</v>
+        <v>10.78905182104592</v>
       </c>
       <c r="D27">
-        <v>11.96851499714401</v>
+        <v>11.81799182104592</v>
       </c>
       <c r="E27">
-        <v>2.56075</v>
+        <v>2.69994</v>
       </c>
       <c r="F27">
-        <v>3.47975</v>
+        <v>3.61894</v>
       </c>
       <c r="G27">
         <v>2.59</v>
@@ -3495,45 +3495,45 @@
         <v>0.529</v>
       </c>
       <c r="M27">
-        <v>0.2637650500000001</v>
+        <v>0.3257046</v>
       </c>
       <c r="N27">
-        <v>0.26523495</v>
+        <v>0.2032954</v>
       </c>
       <c r="O27">
-        <v>0.0450899415</v>
+        <v>0.034560218</v>
       </c>
       <c r="P27">
-        <v>0.2201450085</v>
+        <v>0.168735182</v>
       </c>
       <c r="Q27">
-        <v>0.3911450084999999</v>
+        <v>0.339735182</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.3380595999865694</v>
+        <v>0.3414831476259577</v>
       </c>
       <c r="T27">
-        <v>1.046675115496061</v>
+        <v>1.058935934716466</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.17</v>
       </c>
       <c r="W27">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.005572762577907</v>
+        <v>1.624171104737237</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2721195292432087</v>
+        <v>0.2720193584964903</v>
       </c>
       <c r="C28">
-        <v>10.78905182104592</v>
+        <v>10.65509487038925</v>
       </c>
       <c r="D28">
-        <v>11.81799182104592</v>
+        <v>11.82322487038924</v>
       </c>
       <c r="E28">
-        <v>2.69994</v>
+        <v>2.83913</v>
       </c>
       <c r="F28">
-        <v>3.61894</v>
+        <v>3.75813</v>
       </c>
       <c r="G28">
         <v>2.59</v>
@@ -3577,28 +3577,28 @@
         <v>0.529</v>
       </c>
       <c r="M28">
-        <v>0.3257046</v>
+        <v>0.3382317</v>
       </c>
       <c r="N28">
-        <v>0.2032954</v>
+        <v>0.1907683</v>
       </c>
       <c r="O28">
-        <v>0.034560218</v>
+        <v>0.03243061100000001</v>
       </c>
       <c r="P28">
-        <v>0.168735182</v>
+        <v>0.158337689</v>
       </c>
       <c r="Q28">
-        <v>0.339735182</v>
+        <v>0.3293376889999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.3414831476259577</v>
+        <v>0.3450004910910826</v>
       </c>
       <c r="T28">
-        <v>1.058935934716466</v>
+        <v>1.071532666792223</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.624171104737237</v>
+        <v>1.564016619376599</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2720193584964903</v>
+        <v>0.2719191877497719</v>
       </c>
       <c r="C29">
-        <v>10.65509487038925</v>
+        <v>10.52114255621181</v>
       </c>
       <c r="D29">
-        <v>11.82322487038924</v>
+        <v>11.82846255621181</v>
       </c>
       <c r="E29">
-        <v>2.83913</v>
+        <v>2.978320000000001</v>
       </c>
       <c r="F29">
-        <v>3.75813</v>
+        <v>3.897320000000001</v>
       </c>
       <c r="G29">
         <v>2.59</v>
@@ -3659,28 +3659,28 @@
         <v>0.529</v>
       </c>
       <c r="M29">
-        <v>0.3382317</v>
+        <v>0.3507588</v>
       </c>
       <c r="N29">
-        <v>0.1907683</v>
+        <v>0.1782412</v>
       </c>
       <c r="O29">
-        <v>0.03243061100000001</v>
+        <v>0.030301004</v>
       </c>
       <c r="P29">
-        <v>0.158337689</v>
+        <v>0.147940196</v>
       </c>
       <c r="Q29">
-        <v>0.3293376889999999</v>
+        <v>0.3189401959999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.3450004910910826</v>
+        <v>0.3486155385413498</v>
       </c>
       <c r="T29">
-        <v>1.071532666792223</v>
+        <v>1.084479308092307</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.564016619376599</v>
+        <v>1.508158882970292</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2719191877497719</v>
+        <v>0.2874776282443053</v>
       </c>
       <c r="C30">
-        <v>10.52114255621181</v>
+        <v>9.620473588714638</v>
       </c>
       <c r="D30">
-        <v>11.82846255621181</v>
+        <v>11.06698358871464</v>
       </c>
       <c r="E30">
-        <v>2.978320000000001</v>
+        <v>3.117510000000001</v>
       </c>
       <c r="F30">
-        <v>3.897320000000001</v>
+        <v>4.036510000000001</v>
       </c>
       <c r="G30">
         <v>2.59</v>
@@ -3741,45 +3741,45 @@
         <v>0.529</v>
       </c>
       <c r="M30">
-        <v>0.3507588</v>
+        <v>0.5925596680000002</v>
       </c>
       <c r="N30">
-        <v>0.1782412</v>
+        <v>-0.06355966800000012</v>
       </c>
       <c r="O30">
-        <v>0.030301004</v>
+        <v>-0.01080514356000002</v>
       </c>
       <c r="P30">
-        <v>0.147940196</v>
+        <v>-0.0527545244400001</v>
       </c>
       <c r="Q30">
-        <v>0.3189401959999999</v>
+        <v>0.1182454755599998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.3486155385413498</v>
+        <v>0.3540374378858452</v>
       </c>
       <c r="T30">
-        <v>1.084479308092307</v>
+        <v>1.103896864001056</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.17</v>
+        <v>0.1517653071184048</v>
       </c>
       <c r="W30">
-        <v>0.07469999999999999</v>
+        <v>0.1245208529150182</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.508158882970292</v>
+        <v>0.8927371006964988</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2874776282443053</v>
+        <v>0.2884876282443053</v>
       </c>
       <c r="C31">
-        <v>9.620473588714638</v>
+        <v>9.435225808573701</v>
       </c>
       <c r="D31">
-        <v>11.06698358871464</v>
+        <v>11.0209258085737</v>
       </c>
       <c r="E31">
-        <v>3.11751</v>
+        <v>3.2567</v>
       </c>
       <c r="F31">
-        <v>4.03651</v>
+        <v>4.1757</v>
       </c>
       <c r="G31">
         <v>2.59</v>
@@ -3823,37 +3823,37 @@
         <v>0.529</v>
       </c>
       <c r="M31">
-        <v>0.592559668</v>
+        <v>0.61299276</v>
       </c>
       <c r="N31">
-        <v>-0.06355966800000001</v>
+        <v>-0.08399276</v>
       </c>
       <c r="O31">
-        <v>-0.01080514356</v>
+        <v>-0.0142787692</v>
       </c>
       <c r="P31">
-        <v>-0.05275452444000001</v>
+        <v>-0.0697139908</v>
       </c>
       <c r="Q31">
-        <v>0.1182454755599999</v>
+        <v>0.1012860091999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3540374378858452</v>
+        <v>0.3584408298556429</v>
       </c>
       <c r="T31">
-        <v>1.103896864001056</v>
+        <v>1.119666819201071</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1517653071184048</v>
+        <v>0.1467064635477913</v>
       </c>
       <c r="W31">
-        <v>0.1245208529150182</v>
+        <v>0.1252634911511842</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8927371006964989</v>
+        <v>0.862979197339949</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2884876282443053</v>
+        <v>0.2894976282443054</v>
       </c>
       <c r="C32">
-        <v>9.435225808573701</v>
+        <v>9.250359799550335</v>
       </c>
       <c r="D32">
-        <v>11.0209258085737</v>
+        <v>10.97524979955034</v>
       </c>
       <c r="E32">
-        <v>3.2567</v>
+        <v>3.39589</v>
       </c>
       <c r="F32">
-        <v>4.1757</v>
+        <v>4.31489</v>
       </c>
       <c r="G32">
         <v>2.59</v>
@@ -3905,37 +3905,37 @@
         <v>0.529</v>
       </c>
       <c r="M32">
-        <v>0.61299276</v>
+        <v>0.6334258520000001</v>
       </c>
       <c r="N32">
-        <v>-0.08399276</v>
+        <v>-0.1044258520000001</v>
       </c>
       <c r="O32">
-        <v>-0.0142787692</v>
+        <v>-0.01775239484000002</v>
       </c>
       <c r="P32">
-        <v>-0.0697139908</v>
+        <v>-0.08667345716000008</v>
       </c>
       <c r="Q32">
-        <v>0.1012860091999999</v>
+        <v>0.08432654283999985</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3584408298556429</v>
+        <v>0.3629718563752899</v>
       </c>
       <c r="T32">
-        <v>1.119666819201071</v>
+        <v>1.135893874551811</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1467064635477913</v>
+        <v>0.1419739969817335</v>
       </c>
       <c r="W32">
-        <v>0.1252634911511842</v>
+        <v>0.1259582172430815</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.862979197339949</v>
+        <v>0.8351411587160795</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2894976282443054</v>
+        <v>0.2905076282443053</v>
       </c>
       <c r="C33">
-        <v>9.250359799550335</v>
+        <v>9.065870834507532</v>
       </c>
       <c r="D33">
-        <v>10.97524979955034</v>
+        <v>10.92995083450753</v>
       </c>
       <c r="E33">
-        <v>3.39589</v>
+        <v>3.53508</v>
       </c>
       <c r="F33">
-        <v>4.31489</v>
+        <v>4.45408</v>
       </c>
       <c r="G33">
         <v>2.59</v>
@@ -3987,37 +3987,37 @@
         <v>0.529</v>
       </c>
       <c r="M33">
-        <v>0.6334258520000001</v>
+        <v>0.6538589440000001</v>
       </c>
       <c r="N33">
-        <v>-0.1044258520000001</v>
+        <v>-0.1248589440000001</v>
       </c>
       <c r="O33">
-        <v>-0.01775239484000002</v>
+        <v>-0.02122602048000002</v>
       </c>
       <c r="P33">
-        <v>-0.08667345716000008</v>
+        <v>-0.1036329235200001</v>
       </c>
       <c r="Q33">
-        <v>0.08432654283999985</v>
+        <v>0.06736707647999987</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3629718563752899</v>
+        <v>0.3676361483808089</v>
       </c>
       <c r="T33">
-        <v>1.135893874551811</v>
+        <v>1.152598196236396</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1419739969817335</v>
+        <v>0.1375373095760544</v>
       </c>
       <c r="W33">
-        <v>0.1259582172430815</v>
+        <v>0.1266095229542352</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8351411587160795</v>
+        <v>0.8090429975062021</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2905076282443053</v>
+        <v>0.3120471448727048</v>
       </c>
       <c r="C34">
-        <v>9.065870834507532</v>
+        <v>8.042442778696557</v>
       </c>
       <c r="D34">
-        <v>10.92995083450753</v>
+        <v>10.04571277869656</v>
       </c>
       <c r="E34">
-        <v>3.53508</v>
+        <v>3.67427</v>
       </c>
       <c r="F34">
-        <v>4.45408</v>
+        <v>4.59327</v>
       </c>
       <c r="G34">
         <v>2.59</v>
@@ -4069,45 +4069,45 @@
         <v>0.529</v>
       </c>
       <c r="M34">
-        <v>0.6538589440000001</v>
+        <v>0.9223286160000002</v>
       </c>
       <c r="N34">
-        <v>-0.1248589440000001</v>
+        <v>-0.3933286160000001</v>
       </c>
       <c r="O34">
-        <v>-0.02122602048000002</v>
+        <v>-0.06686586472000003</v>
       </c>
       <c r="P34">
-        <v>-0.1036329235200001</v>
+        <v>-0.3264627512800001</v>
       </c>
       <c r="Q34">
-        <v>0.06736707647999987</v>
+        <v>-0.1554627512800002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3676361483808089</v>
+        <v>0.3764837276527605</v>
       </c>
       <c r="T34">
-        <v>1.152598196236396</v>
+        <v>1.184284207771197</v>
       </c>
       <c r="U34">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1375373095760544</v>
+        <v>0.09750320920325863</v>
       </c>
       <c r="W34">
-        <v>0.1266095229542352</v>
+        <v>0.1812213555919857</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.8090429975062021</v>
+        <v>0.5735482894309331</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.3120471448727048</v>
+        <v>0.3135971448727047</v>
       </c>
       <c r="C35">
-        <v>8.042442778696557</v>
+        <v>7.845108563550498</v>
       </c>
       <c r="D35">
-        <v>10.04571277869656</v>
+        <v>9.987568563550498</v>
       </c>
       <c r="E35">
-        <v>3.67427</v>
+        <v>3.813460000000001</v>
       </c>
       <c r="F35">
-        <v>4.59327</v>
+        <v>4.732460000000001</v>
       </c>
       <c r="G35">
         <v>2.59</v>
@@ -4151,37 +4151,37 @@
         <v>0.529</v>
       </c>
       <c r="M35">
-        <v>0.9223286160000002</v>
+        <v>0.9502779680000002</v>
       </c>
       <c r="N35">
-        <v>-0.3933286160000001</v>
+        <v>-0.4212779680000002</v>
       </c>
       <c r="O35">
-        <v>-0.06686586472000003</v>
+        <v>-0.07161725456000004</v>
       </c>
       <c r="P35">
-        <v>-0.3264627512800001</v>
+        <v>-0.3496607134400002</v>
       </c>
       <c r="Q35">
-        <v>-0.1554627512800002</v>
+        <v>-0.1786607134400002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3764837276527605</v>
+        <v>0.3814940871626508</v>
       </c>
       <c r="T35">
-        <v>1.184284207771197</v>
+        <v>1.202227907888942</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.09750320920325863</v>
+        <v>0.09463546775610397</v>
       </c>
       <c r="W35">
-        <v>0.1812213555919857</v>
+        <v>0.1817971980745743</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5735482894309331</v>
+        <v>0.5566792220947292</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.3135971448727047</v>
+        <v>0.3151471448727047</v>
       </c>
       <c r="C36">
-        <v>7.845108563550498</v>
+        <v>7.648443548247032</v>
       </c>
       <c r="D36">
-        <v>9.987568563550498</v>
+        <v>9.930093548247033</v>
       </c>
       <c r="E36">
-        <v>3.813460000000001</v>
+        <v>3.952650000000001</v>
       </c>
       <c r="F36">
-        <v>4.732460000000001</v>
+        <v>4.871650000000001</v>
       </c>
       <c r="G36">
         <v>2.59</v>
@@ -4233,37 +4233,37 @@
         <v>0.529</v>
       </c>
       <c r="M36">
-        <v>0.9502779680000002</v>
+        <v>0.9782273200000001</v>
       </c>
       <c r="N36">
-        <v>-0.4212779680000002</v>
+        <v>-0.4492273200000001</v>
       </c>
       <c r="O36">
-        <v>-0.07161725456000004</v>
+        <v>-0.07636864440000002</v>
       </c>
       <c r="P36">
-        <v>-0.3496607134400002</v>
+        <v>-0.3728586756000001</v>
       </c>
       <c r="Q36">
-        <v>-0.1786607134400002</v>
+        <v>-0.2018586756000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3814940871626508</v>
+        <v>0.3866586115805377</v>
       </c>
       <c r="T36">
-        <v>1.202227907888942</v>
+        <v>1.220723721856464</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.09463546775610397</v>
+        <v>0.0919315972487867</v>
       </c>
       <c r="W36">
-        <v>0.1817971980745743</v>
+        <v>0.1823401352724436</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5566792220947292</v>
+        <v>0.5407741014634513</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.3151471448727047</v>
+        <v>0.3166971448727048</v>
       </c>
       <c r="C37">
-        <v>7.648443548247032</v>
+        <v>7.452436245846093</v>
       </c>
       <c r="D37">
-        <v>9.930093548247033</v>
+        <v>9.873276245846094</v>
       </c>
       <c r="E37">
-        <v>3.952650000000001</v>
+        <v>4.09184</v>
       </c>
       <c r="F37">
-        <v>4.871650000000001</v>
+        <v>5.010840000000001</v>
       </c>
       <c r="G37">
         <v>2.59</v>
@@ -4315,37 +4315,37 @@
         <v>0.529</v>
       </c>
       <c r="M37">
-        <v>0.9782273200000001</v>
+        <v>1.006176672</v>
       </c>
       <c r="N37">
-        <v>-0.4492273200000001</v>
+        <v>-0.4771766720000002</v>
       </c>
       <c r="O37">
-        <v>-0.07636864440000002</v>
+        <v>-0.08112003424000004</v>
       </c>
       <c r="P37">
-        <v>-0.3728586756000001</v>
+        <v>-0.3960566377600002</v>
       </c>
       <c r="Q37">
-        <v>-0.2018586756000001</v>
+        <v>-0.2250566377600003</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3866586115805377</v>
+        <v>0.3919845273864836</v>
       </c>
       <c r="T37">
-        <v>1.220723721856464</v>
+        <v>1.239797530010471</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.0919315972487867</v>
+        <v>0.08937794176965373</v>
       </c>
       <c r="W37">
-        <v>0.1823401352724436</v>
+        <v>0.1828529092926535</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5407741014634513</v>
+        <v>0.525752598645022</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.3166971448727048</v>
+        <v>0.3182471448727048</v>
       </c>
       <c r="C38">
-        <v>7.452436245846092</v>
+        <v>7.257075430812551</v>
       </c>
       <c r="D38">
-        <v>9.873276245846093</v>
+        <v>9.817105430812552</v>
       </c>
       <c r="E38">
-        <v>4.091839999999999</v>
+        <v>4.23103</v>
       </c>
       <c r="F38">
-        <v>5.01084</v>
+        <v>5.15003</v>
       </c>
       <c r="G38">
         <v>2.59</v>
@@ -4397,37 +4397,37 @@
         <v>0.529</v>
       </c>
       <c r="M38">
-        <v>1.006176672</v>
+        <v>1.034126024</v>
       </c>
       <c r="N38">
-        <v>-0.477176672</v>
+        <v>-0.5051260240000001</v>
       </c>
       <c r="O38">
-        <v>-0.08112003424000001</v>
+        <v>-0.08587142408000002</v>
       </c>
       <c r="P38">
-        <v>-0.39605663776</v>
+        <v>-0.41925459992</v>
       </c>
       <c r="Q38">
-        <v>-0.2250566377600001</v>
+        <v>-0.2482545999200001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3919845273864836</v>
+        <v>0.3974795198846818</v>
       </c>
       <c r="T38">
-        <v>1.239797530010471</v>
+        <v>1.259476855883653</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08937794176965376</v>
+        <v>0.08696232172182528</v>
       </c>
       <c r="W38">
-        <v>0.1828529092926535</v>
+        <v>0.1833379657982575</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.525752598645022</v>
+        <v>0.5115430689519134</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.3182471448727048</v>
+        <v>0.3341904675595955</v>
       </c>
       <c r="C39">
-        <v>7.257075430812551</v>
+        <v>6.575158477806285</v>
       </c>
       <c r="D39">
-        <v>9.817105430812552</v>
+        <v>9.274378477806286</v>
       </c>
       <c r="E39">
-        <v>4.23103</v>
+        <v>4.37022</v>
       </c>
       <c r="F39">
-        <v>5.15003</v>
+        <v>5.28922</v>
       </c>
       <c r="G39">
         <v>2.59</v>
@@ -4479,45 +4479,45 @@
         <v>0.529</v>
       </c>
       <c r="M39">
-        <v>1.034126024</v>
+        <v>1.247198076</v>
       </c>
       <c r="N39">
-        <v>-0.5051260240000001</v>
+        <v>-0.7181980760000001</v>
       </c>
       <c r="O39">
-        <v>-0.08587142408000002</v>
+        <v>-0.12209367292</v>
       </c>
       <c r="P39">
-        <v>-0.41925459992</v>
+        <v>-0.59610440308</v>
       </c>
       <c r="Q39">
-        <v>-0.2482545999200001</v>
+        <v>-0.4251044030800001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3974795198846818</v>
+        <v>0.4049151938939358</v>
       </c>
       <c r="T39">
-        <v>1.259476855883653</v>
+        <v>1.286106383032752</v>
       </c>
       <c r="U39">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.08696232172182528</v>
+        <v>0.07210562759078536</v>
       </c>
       <c r="W39">
-        <v>0.1833379657982575</v>
+        <v>0.2187974930140928</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.5115430689519134</v>
+        <v>0.4241507505340314</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.3341904675595955</v>
+        <v>0.3360904675595955</v>
       </c>
       <c r="C40">
-        <v>6.575158477806285</v>
+        <v>6.375266108706913</v>
       </c>
       <c r="D40">
-        <v>9.274378477806286</v>
+        <v>9.213676108706913</v>
       </c>
       <c r="E40">
-        <v>4.37022</v>
+        <v>4.50941</v>
       </c>
       <c r="F40">
-        <v>5.28922</v>
+        <v>5.42841</v>
       </c>
       <c r="G40">
         <v>2.59</v>
@@ -4561,37 +4561,37 @@
         <v>0.529</v>
       </c>
       <c r="M40">
-        <v>1.247198076</v>
+        <v>1.280019078</v>
       </c>
       <c r="N40">
-        <v>-0.7181980760000001</v>
+        <v>-0.7510190780000002</v>
       </c>
       <c r="O40">
-        <v>-0.12209367292</v>
+        <v>-0.12767324326</v>
       </c>
       <c r="P40">
-        <v>-0.59610440308</v>
+        <v>-0.6233458347400002</v>
       </c>
       <c r="Q40">
-        <v>-0.4251044030800001</v>
+        <v>-0.4523458347400002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.4049151938939358</v>
+        <v>0.4108023282200659</v>
       </c>
       <c r="T40">
-        <v>1.286106383032752</v>
+        <v>1.30719009423001</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07210562759078536</v>
+        <v>0.07025676534486777</v>
       </c>
       <c r="W40">
-        <v>0.2187974930140928</v>
+        <v>0.2192334547316802</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4241507505340314</v>
+        <v>0.4132750902639281</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.3360904675595955</v>
+        <v>0.3379904675595954</v>
       </c>
       <c r="C41">
-        <v>6.375266108706913</v>
+        <v>6.176163186999526</v>
       </c>
       <c r="D41">
-        <v>9.213676108706913</v>
+        <v>9.153763186999527</v>
       </c>
       <c r="E41">
-        <v>4.50941</v>
+        <v>4.6486</v>
       </c>
       <c r="F41">
-        <v>5.42841</v>
+        <v>5.567600000000001</v>
       </c>
       <c r="G41">
         <v>2.59</v>
@@ -4643,37 +4643,37 @@
         <v>0.529</v>
       </c>
       <c r="M41">
-        <v>1.280019078</v>
+        <v>1.31284008</v>
       </c>
       <c r="N41">
-        <v>-0.7510190780000002</v>
+        <v>-0.7838400800000002</v>
       </c>
       <c r="O41">
-        <v>-0.12767324326</v>
+        <v>-0.1332528136</v>
       </c>
       <c r="P41">
-        <v>-0.6233458347400002</v>
+        <v>-0.6505872664000001</v>
       </c>
       <c r="Q41">
-        <v>-0.4523458347400002</v>
+        <v>-0.4795872664000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.4108023282200659</v>
+        <v>0.416885700357067</v>
       </c>
       <c r="T41">
-        <v>1.30719009423001</v>
+        <v>1.32897659580051</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07025676534486777</v>
+        <v>0.06850034621124608</v>
       </c>
       <c r="W41">
-        <v>0.2192334547316802</v>
+        <v>0.2196476183633882</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4132750902639281</v>
+        <v>0.4029432130073298</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.3379904675595954</v>
+        <v>0.3398904675595955</v>
       </c>
       <c r="C42">
-        <v>6.176163186999526</v>
+        <v>5.977834411779704</v>
       </c>
       <c r="D42">
-        <v>9.153763186999527</v>
+        <v>9.094624411779705</v>
       </c>
       <c r="E42">
-        <v>4.6486</v>
+        <v>4.78779</v>
       </c>
       <c r="F42">
-        <v>5.567600000000001</v>
+        <v>5.706790000000001</v>
       </c>
       <c r="G42">
         <v>2.59</v>
@@ -4725,37 +4725,37 @@
         <v>0.529</v>
       </c>
       <c r="M42">
-        <v>1.31284008</v>
+        <v>1.345661082</v>
       </c>
       <c r="N42">
-        <v>-0.7838400800000002</v>
+        <v>-0.8166610820000001</v>
       </c>
       <c r="O42">
-        <v>-0.1332528136</v>
+        <v>-0.13883238394</v>
       </c>
       <c r="P42">
-        <v>-0.6505872664000001</v>
+        <v>-0.6778286980600001</v>
       </c>
       <c r="Q42">
-        <v>-0.4795872664000002</v>
+        <v>-0.5068286980600002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.416885700357067</v>
+        <v>0.4231752884987122</v>
       </c>
       <c r="T42">
-        <v>1.32897659580051</v>
+        <v>1.351501622847977</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06850034621124608</v>
+        <v>0.06682960605975227</v>
       </c>
       <c r="W42">
-        <v>0.2196476183633882</v>
+        <v>0.2200415788911104</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4029432130073298</v>
+        <v>0.3931153297632487</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.3398904675595955</v>
+        <v>0.3417904675595955</v>
       </c>
       <c r="C43">
-        <v>5.977834411779704</v>
+        <v>5.780264875016742</v>
       </c>
       <c r="D43">
-        <v>9.094624411779705</v>
+        <v>9.036244875016743</v>
       </c>
       <c r="E43">
-        <v>4.78779</v>
+        <v>4.92698</v>
       </c>
       <c r="F43">
-        <v>5.706790000000001</v>
+        <v>5.845980000000001</v>
       </c>
       <c r="G43">
         <v>2.59</v>
@@ -4807,37 +4807,37 @@
         <v>0.529</v>
       </c>
       <c r="M43">
-        <v>1.345661082</v>
+        <v>1.378482084</v>
       </c>
       <c r="N43">
-        <v>-0.8166610820000001</v>
+        <v>-0.8494820840000002</v>
       </c>
       <c r="O43">
-        <v>-0.13883238394</v>
+        <v>-0.1444119542800001</v>
       </c>
       <c r="P43">
-        <v>-0.6778286980600001</v>
+        <v>-0.7050701297200002</v>
       </c>
       <c r="Q43">
-        <v>-0.5068286980600002</v>
+        <v>-0.5340701297200002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.4231752884987122</v>
+        <v>0.4296817589900693</v>
       </c>
       <c r="T43">
-        <v>1.351501622847977</v>
+        <v>1.374803374966045</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06682960605975227</v>
+        <v>0.0652384249630915</v>
       </c>
       <c r="W43">
-        <v>0.2200415788911104</v>
+        <v>0.220416779393703</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3931153297632487</v>
+        <v>0.3837554409593618</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.3417904675595955</v>
+        <v>0.3436904675595955</v>
       </c>
       <c r="C44">
-        <v>5.780264875016743</v>
+        <v>5.583440049024544</v>
       </c>
       <c r="D44">
-        <v>9.036244875016743</v>
+        <v>8.978610049024544</v>
       </c>
       <c r="E44">
-        <v>4.926979999999999</v>
+        <v>5.06617</v>
       </c>
       <c r="F44">
-        <v>5.84598</v>
+        <v>5.98517</v>
       </c>
       <c r="G44">
         <v>2.59</v>
@@ -4889,37 +4889,37 @@
         <v>0.529</v>
       </c>
       <c r="M44">
-        <v>1.378482084</v>
+        <v>1.411303086</v>
       </c>
       <c r="N44">
-        <v>-0.849482084</v>
+        <v>-0.882303086</v>
       </c>
       <c r="O44">
-        <v>-0.14441195428</v>
+        <v>-0.14999152462</v>
       </c>
       <c r="P44">
-        <v>-0.70507012972</v>
+        <v>-0.73231156138</v>
       </c>
       <c r="Q44">
-        <v>-0.5340701297200001</v>
+        <v>-0.56131156138</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.4296817589900693</v>
+        <v>0.4364165266916495</v>
       </c>
       <c r="T44">
-        <v>1.374803374966045</v>
+        <v>1.39892273242159</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06523842496309151</v>
+        <v>0.06372125228953124</v>
       </c>
       <c r="W44">
-        <v>0.220416779393703</v>
+        <v>0.2207745287101286</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3837554409593618</v>
+        <v>0.374830895820772</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.3436904675595955</v>
+        <v>0.3455904675595955</v>
       </c>
       <c r="C45">
-        <v>5.583440049024544</v>
+        <v>5.387345774408957</v>
       </c>
       <c r="D45">
-        <v>8.978610049024544</v>
+        <v>8.921705774408958</v>
       </c>
       <c r="E45">
-        <v>5.06617</v>
+        <v>5.20536</v>
       </c>
       <c r="F45">
-        <v>5.98517</v>
+        <v>6.12436</v>
       </c>
       <c r="G45">
         <v>2.59</v>
@@ -4971,37 +4971,37 @@
         <v>0.529</v>
       </c>
       <c r="M45">
-        <v>1.411303086</v>
+        <v>1.444124088</v>
       </c>
       <c r="N45">
-        <v>-0.882303086</v>
+        <v>-0.9151240880000001</v>
       </c>
       <c r="O45">
-        <v>-0.14999152462</v>
+        <v>-0.15557109496</v>
       </c>
       <c r="P45">
-        <v>-0.73231156138</v>
+        <v>-0.7595529930400001</v>
       </c>
       <c r="Q45">
-        <v>-0.56131156138</v>
+        <v>-0.5885529930400002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.4364165266916495</v>
+        <v>0.4433918218111432</v>
       </c>
       <c r="T45">
-        <v>1.39892273242159</v>
+        <v>1.423903495500547</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06372125228953124</v>
+        <v>0.06227304201022371</v>
       </c>
       <c r="W45">
-        <v>0.2207745287101286</v>
+        <v>0.2211160166939893</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.374830895820772</v>
+        <v>0.3663120118248453</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.3455904675595955</v>
+        <v>0.3474904675595955</v>
       </c>
       <c r="C46">
-        <v>5.387345774408957</v>
+        <v>5.191968248470543</v>
       </c>
       <c r="D46">
-        <v>8.921705774408958</v>
+        <v>8.865518248470543</v>
       </c>
       <c r="E46">
-        <v>5.20536</v>
+        <v>5.34455</v>
       </c>
       <c r="F46">
-        <v>6.12436</v>
+        <v>6.26355</v>
       </c>
       <c r="G46">
         <v>2.59</v>
@@ -5053,37 +5053,37 @@
         <v>0.529</v>
       </c>
       <c r="M46">
-        <v>1.444124088</v>
+        <v>1.47694509</v>
       </c>
       <c r="N46">
-        <v>-0.9151240880000001</v>
+        <v>-0.94794509</v>
       </c>
       <c r="O46">
-        <v>-0.15557109496</v>
+        <v>-0.1611506653</v>
       </c>
       <c r="P46">
-        <v>-0.7595529930400001</v>
+        <v>-0.7867944247000001</v>
       </c>
       <c r="Q46">
-        <v>-0.5885529930400002</v>
+        <v>-0.6157944247000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.4433918218111432</v>
+        <v>0.4506207640258912</v>
       </c>
       <c r="T46">
-        <v>1.423903495500547</v>
+        <v>1.449792649964193</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06227304201022371</v>
+        <v>0.06088919663221874</v>
       </c>
       <c r="W46">
-        <v>0.2211160166939893</v>
+        <v>0.2214423274341228</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3663120118248453</v>
+        <v>0.3581717448954044</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.3474904675595955</v>
+        <v>0.3493904675595955</v>
       </c>
       <c r="C47">
-        <v>5.191968248470543</v>
+        <v>4.997294014042835</v>
       </c>
       <c r="D47">
-        <v>8.865518248470543</v>
+        <v>8.810034014042836</v>
       </c>
       <c r="E47">
-        <v>5.34455</v>
+        <v>5.48374</v>
       </c>
       <c r="F47">
-        <v>6.26355</v>
+        <v>6.402740000000001</v>
       </c>
       <c r="G47">
         <v>2.59</v>
@@ -5135,37 +5135,37 @@
         <v>0.529</v>
       </c>
       <c r="M47">
-        <v>1.47694509</v>
+        <v>1.509766092</v>
       </c>
       <c r="N47">
-        <v>-0.94794509</v>
+        <v>-0.9807660920000002</v>
       </c>
       <c r="O47">
-        <v>-0.1611506653</v>
+        <v>-0.1667302356400001</v>
       </c>
       <c r="P47">
-        <v>-0.7867944247000001</v>
+        <v>-0.8140358563600001</v>
       </c>
       <c r="Q47">
-        <v>-0.6157944247000001</v>
+        <v>-0.6430358563600002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.4506207640258912</v>
+        <v>0.4581174448411855</v>
       </c>
       <c r="T47">
-        <v>1.449792649964193</v>
+        <v>1.476640662000567</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06088919663221874</v>
+        <v>0.05956551844456181</v>
       </c>
       <c r="W47">
-        <v>0.2214423274341228</v>
+        <v>0.2217544507507723</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3581717448954044</v>
+        <v>0.3503854026150695</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.3493904675595955</v>
+        <v>0.3512904675595955</v>
       </c>
       <c r="C48">
-        <v>4.997294014042835</v>
+        <v>4.803309948747113</v>
       </c>
       <c r="D48">
-        <v>8.810034014042836</v>
+        <v>8.755239948747114</v>
       </c>
       <c r="E48">
-        <v>5.48374</v>
+        <v>5.62293</v>
       </c>
       <c r="F48">
-        <v>6.402740000000001</v>
+        <v>6.541930000000001</v>
       </c>
       <c r="G48">
         <v>2.59</v>
@@ -5217,37 +5217,37 @@
         <v>0.529</v>
       </c>
       <c r="M48">
-        <v>1.509766092</v>
+        <v>1.542587094</v>
       </c>
       <c r="N48">
-        <v>-0.9807660920000002</v>
+        <v>-1.013587094</v>
       </c>
       <c r="O48">
-        <v>-0.1667302356400001</v>
+        <v>-0.17230980598</v>
       </c>
       <c r="P48">
-        <v>-0.8140358563600001</v>
+        <v>-0.84127728802</v>
       </c>
       <c r="Q48">
-        <v>-0.6430358563600002</v>
+        <v>-0.6702772880200001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.4581174448411855</v>
+        <v>0.4658970192721513</v>
       </c>
       <c r="T48">
-        <v>1.476640662000567</v>
+        <v>1.504501806566615</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05956551844456181</v>
+        <v>0.05829816698829454</v>
       </c>
       <c r="W48">
-        <v>0.2217544507507723</v>
+        <v>0.2220532922241602</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3503854026150695</v>
+        <v>0.3429303940487914</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.3512904675595955</v>
+        <v>0.3531904675595954</v>
       </c>
       <c r="C49">
-        <v>4.803309948747113</v>
+        <v>4.61000325464568</v>
       </c>
       <c r="D49">
-        <v>8.755239948747114</v>
+        <v>8.701123254645681</v>
       </c>
       <c r="E49">
-        <v>5.62293</v>
+        <v>5.76212</v>
       </c>
       <c r="F49">
-        <v>6.541930000000001</v>
+        <v>6.681120000000001</v>
       </c>
       <c r="G49">
         <v>2.59</v>
@@ -5299,37 +5299,37 @@
         <v>0.529</v>
       </c>
       <c r="M49">
-        <v>1.542587094</v>
+        <v>1.575408096</v>
       </c>
       <c r="N49">
-        <v>-1.013587094</v>
+        <v>-1.046408096</v>
       </c>
       <c r="O49">
-        <v>-0.17230980598</v>
+        <v>-0.1778893763200001</v>
       </c>
       <c r="P49">
-        <v>-0.84127728802</v>
+        <v>-0.8685187196800004</v>
       </c>
       <c r="Q49">
-        <v>-0.6702772880200001</v>
+        <v>-0.6975187196800005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.4658970192721513</v>
+        <v>0.473975808104308</v>
       </c>
       <c r="T49">
-        <v>1.504501806566615</v>
+        <v>1.533434533615973</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05829816698829454</v>
+        <v>0.05708362184270507</v>
       </c>
       <c r="W49">
-        <v>0.2220532922241602</v>
+        <v>0.2223396819694901</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3429303940487914</v>
+        <v>0.3357860108394415</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3531904675595954</v>
+        <v>0.3550904675595954</v>
       </c>
       <c r="C50">
-        <v>4.610003254645681</v>
+        <v>4.417361448276504</v>
       </c>
       <c r="D50">
-        <v>8.701123254645681</v>
+        <v>8.647671448276505</v>
       </c>
       <c r="E50">
-        <v>5.762119999999999</v>
+        <v>5.90131</v>
       </c>
       <c r="F50">
-        <v>6.68112</v>
+        <v>6.82031</v>
       </c>
       <c r="G50">
         <v>2.59</v>
@@ -5381,37 +5381,37 @@
         <v>0.529</v>
       </c>
       <c r="M50">
-        <v>1.575408096</v>
+        <v>1.608229098</v>
       </c>
       <c r="N50">
-        <v>-1.046408096</v>
+        <v>-1.079229098</v>
       </c>
       <c r="O50">
-        <v>-0.17788937632</v>
+        <v>-0.18346894666</v>
       </c>
       <c r="P50">
-        <v>-0.8685187196799999</v>
+        <v>-0.8957601513399999</v>
       </c>
       <c r="Q50">
-        <v>-0.69751871968</v>
+        <v>-0.7247601513399999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.473975808104308</v>
+        <v>0.4823714121847847</v>
       </c>
       <c r="T50">
-        <v>1.533434533615973</v>
+        <v>1.563501877412365</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05708362184270507</v>
+        <v>0.05591864996836415</v>
       </c>
       <c r="W50">
-        <v>0.2223396819694901</v>
+        <v>0.2226143823374598</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3357860108394416</v>
+        <v>0.3289332351080245</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3550904675595954</v>
+        <v>0.3569904675595955</v>
       </c>
       <c r="C51">
-        <v>4.417361448276504</v>
+        <v>4.225372351052942</v>
       </c>
       <c r="D51">
-        <v>8.647671448276505</v>
+        <v>8.594872351052942</v>
       </c>
       <c r="E51">
-        <v>5.90131</v>
+        <v>6.0405</v>
       </c>
       <c r="F51">
-        <v>6.82031</v>
+        <v>6.9595</v>
       </c>
       <c r="G51">
         <v>2.59</v>
@@ -5463,37 +5463,37 @@
         <v>0.529</v>
       </c>
       <c r="M51">
-        <v>1.608229098</v>
+        <v>1.6410501</v>
       </c>
       <c r="N51">
-        <v>-1.079229098</v>
+        <v>-1.1120501</v>
       </c>
       <c r="O51">
-        <v>-0.18346894666</v>
+        <v>-0.1890485170000001</v>
       </c>
       <c r="P51">
-        <v>-0.8957601513399999</v>
+        <v>-0.9230015830000002</v>
       </c>
       <c r="Q51">
-        <v>-0.7247601513399999</v>
+        <v>-0.7520015830000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.4823714121847847</v>
+        <v>0.4911028404284804</v>
       </c>
       <c r="T51">
-        <v>1.563501877412365</v>
+        <v>1.594771914960612</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05591864996836415</v>
+        <v>0.05480027696899687</v>
       </c>
       <c r="W51">
-        <v>0.2226143823374598</v>
+        <v>0.2228780946907105</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3289332351080245</v>
+        <v>0.3223545704058638</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3569904675595955</v>
+        <v>0.3588904675595955</v>
       </c>
       <c r="C52">
-        <v>4.225372351052942</v>
+        <v>4.034024080012983</v>
       </c>
       <c r="D52">
-        <v>8.594872351052942</v>
+        <v>8.542714080012983</v>
       </c>
       <c r="E52">
-        <v>6.0405</v>
+        <v>6.17969</v>
       </c>
       <c r="F52">
-        <v>6.9595</v>
+        <v>7.09869</v>
       </c>
       <c r="G52">
         <v>2.59</v>
@@ -5545,37 +5545,37 @@
         <v>0.529</v>
       </c>
       <c r="M52">
-        <v>1.6410501</v>
+        <v>1.673871102</v>
       </c>
       <c r="N52">
-        <v>-1.1120501</v>
+        <v>-1.144871102</v>
       </c>
       <c r="O52">
-        <v>-0.1890485170000001</v>
+        <v>-0.1946280873400001</v>
       </c>
       <c r="P52">
-        <v>-0.9230015830000002</v>
+        <v>-0.9502430146600002</v>
       </c>
       <c r="Q52">
-        <v>-0.7520015830000003</v>
+        <v>-0.7792430146600002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.4911028404284804</v>
+        <v>0.5001906534984494</v>
       </c>
       <c r="T52">
-        <v>1.594771914960612</v>
+        <v>1.627318280572053</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05480027696899687</v>
+        <v>0.05372576173431066</v>
       </c>
       <c r="W52">
-        <v>0.2228780946907105</v>
+        <v>0.2231314653830496</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3223545704058638</v>
+        <v>0.3160338925547684</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3588904675595955</v>
+        <v>0.3607904675595954</v>
       </c>
       <c r="C53">
-        <v>4.034024080012983</v>
+        <v>3.843305038903338</v>
       </c>
       <c r="D53">
-        <v>8.542714080012983</v>
+        <v>8.491185038903339</v>
       </c>
       <c r="E53">
-        <v>6.17969</v>
+        <v>6.31888</v>
       </c>
       <c r="F53">
-        <v>7.09869</v>
+        <v>7.237880000000001</v>
       </c>
       <c r="G53">
         <v>2.59</v>
@@ -5627,37 +5627,37 @@
         <v>0.529</v>
       </c>
       <c r="M53">
-        <v>1.673871102</v>
+        <v>1.706692104</v>
       </c>
       <c r="N53">
-        <v>-1.144871102</v>
+        <v>-1.177692104</v>
       </c>
       <c r="O53">
-        <v>-0.1946280873400001</v>
+        <v>-0.20020765768</v>
       </c>
       <c r="P53">
-        <v>-0.9502430146600002</v>
+        <v>-0.9774844463200001</v>
       </c>
       <c r="Q53">
-        <v>-0.7792430146600002</v>
+        <v>-0.8064844463200002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.5001906534984494</v>
+        <v>0.5096571254463337</v>
       </c>
       <c r="T53">
-        <v>1.627318280572053</v>
+        <v>1.661220744750638</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05372576173431066</v>
+        <v>0.05269257400865083</v>
       </c>
       <c r="W53">
-        <v>0.2231314653830496</v>
+        <v>0.2233750910487602</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3160338925547684</v>
+        <v>0.3099563176979461</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3607904675595954</v>
+        <v>0.3626904675595954</v>
       </c>
       <c r="C54">
-        <v>3.843305038903338</v>
+        <v>3.653203909584238</v>
       </c>
       <c r="D54">
-        <v>8.491185038903339</v>
+        <v>8.440273909584239</v>
       </c>
       <c r="E54">
-        <v>6.31888</v>
+        <v>6.45807</v>
       </c>
       <c r="F54">
-        <v>7.237880000000001</v>
+        <v>7.377070000000001</v>
       </c>
       <c r="G54">
         <v>2.59</v>
@@ -5709,37 +5709,37 @@
         <v>0.529</v>
       </c>
       <c r="M54">
-        <v>1.706692104</v>
+        <v>1.739513106</v>
       </c>
       <c r="N54">
-        <v>-1.177692104</v>
+        <v>-1.210513106</v>
       </c>
       <c r="O54">
-        <v>-0.20020765768</v>
+        <v>-0.20578722802</v>
       </c>
       <c r="P54">
-        <v>-0.9774844463200001</v>
+        <v>-1.00472587798</v>
       </c>
       <c r="Q54">
-        <v>-0.8064844463200002</v>
+        <v>-0.8337258779800002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.5096571254463337</v>
+        <v>0.5195264259877451</v>
       </c>
       <c r="T54">
-        <v>1.661220744750638</v>
+        <v>1.696565866979375</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05269257400865083</v>
+        <v>0.05169837449905364</v>
       </c>
       <c r="W54">
-        <v>0.2233750910487602</v>
+        <v>0.2236095232931231</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3099563176979461</v>
+        <v>0.3041080852885509</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3626904675595954</v>
+        <v>0.3645904675595955</v>
       </c>
       <c r="C55">
-        <v>3.653203909584238</v>
+        <v>3.463709643741621</v>
       </c>
       <c r="D55">
-        <v>8.440273909584239</v>
+        <v>8.389969643741622</v>
       </c>
       <c r="E55">
-        <v>6.45807</v>
+        <v>6.59726</v>
       </c>
       <c r="F55">
-        <v>7.377070000000001</v>
+        <v>7.516260000000001</v>
       </c>
       <c r="G55">
         <v>2.59</v>
@@ -5791,37 +5791,37 @@
         <v>0.529</v>
       </c>
       <c r="M55">
-        <v>1.739513106</v>
+        <v>1.772334108</v>
       </c>
       <c r="N55">
-        <v>-1.210513106</v>
+        <v>-1.243334108</v>
       </c>
       <c r="O55">
-        <v>-0.20578722802</v>
+        <v>-0.2113667983600001</v>
       </c>
       <c r="P55">
-        <v>-1.00472587798</v>
+        <v>-1.03196730964</v>
       </c>
       <c r="Q55">
-        <v>-0.8337258779800002</v>
+        <v>-0.8609673096400005</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.5195264259877451</v>
+        <v>0.529824826552696</v>
       </c>
       <c r="T55">
-        <v>1.696565866979375</v>
+        <v>1.73344773365284</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05169837449905364</v>
+        <v>0.05074099719351561</v>
       </c>
       <c r="W55">
-        <v>0.2236095232931231</v>
+        <v>0.223835272861769</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3041080852885509</v>
+        <v>0.2984764540795035</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3645904675595955</v>
+        <v>0.3664904675595955</v>
       </c>
       <c r="C56">
-        <v>3.463709643741621</v>
+        <v>3.274811454893922</v>
       </c>
       <c r="D56">
-        <v>8.389969643741622</v>
+        <v>8.340261454893923</v>
       </c>
       <c r="E56">
-        <v>6.59726</v>
+        <v>6.73645</v>
       </c>
       <c r="F56">
-        <v>7.516260000000001</v>
+        <v>7.655450000000001</v>
       </c>
       <c r="G56">
         <v>2.59</v>
@@ -5873,37 +5873,37 @@
         <v>0.529</v>
       </c>
       <c r="M56">
-        <v>1.772334108</v>
+        <v>1.80515511</v>
       </c>
       <c r="N56">
-        <v>-1.243334108</v>
+        <v>-1.27615511</v>
       </c>
       <c r="O56">
-        <v>-0.2113667983600001</v>
+        <v>-0.2169463687000001</v>
       </c>
       <c r="P56">
-        <v>-1.03196730964</v>
+        <v>-1.0592087413</v>
       </c>
       <c r="Q56">
-        <v>-0.8609673096400005</v>
+        <v>-0.8882087413000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.529824826552696</v>
+        <v>0.5405809338094227</v>
       </c>
       <c r="T56">
-        <v>1.73344773365284</v>
+        <v>1.771968794400681</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05074099719351561</v>
+        <v>0.04981843360817896</v>
       </c>
       <c r="W56">
-        <v>0.223835272861769</v>
+        <v>0.2240528133551914</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2984764540795035</v>
+        <v>0.2930496094598762</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3664904675595955</v>
+        <v>0.3683904675595955</v>
       </c>
       <c r="C57">
-        <v>3.274811454893922</v>
+        <v>3.086498810681347</v>
       </c>
       <c r="D57">
-        <v>8.340261454893923</v>
+        <v>8.291138810681348</v>
       </c>
       <c r="E57">
-        <v>6.73645</v>
+        <v>6.875640000000001</v>
       </c>
       <c r="F57">
-        <v>7.655450000000001</v>
+        <v>7.794640000000001</v>
       </c>
       <c r="G57">
         <v>2.59</v>
@@ -5955,37 +5955,37 @@
         <v>0.529</v>
       </c>
       <c r="M57">
-        <v>1.80515511</v>
+        <v>1.837976112</v>
       </c>
       <c r="N57">
-        <v>-1.27615511</v>
+        <v>-1.308976112</v>
       </c>
       <c r="O57">
-        <v>-0.2169463687000001</v>
+        <v>-0.2225259390400001</v>
       </c>
       <c r="P57">
-        <v>-1.0592087413</v>
+        <v>-1.08645017296</v>
       </c>
       <c r="Q57">
-        <v>-0.8882087413000003</v>
+        <v>-0.9154501729600003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.5405809338094227</v>
+        <v>0.5518259550323641</v>
       </c>
       <c r="T57">
-        <v>1.771968794400681</v>
+        <v>1.812240812455242</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04981843360817896</v>
+        <v>0.04892881872231862</v>
       </c>
       <c r="W57">
-        <v>0.2240528133551914</v>
+        <v>0.2242625845452773</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2930496094598762</v>
+        <v>0.2878165807195213</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3683904675595955</v>
+        <v>0.3702904675595954</v>
       </c>
       <c r="C58">
-        <v>3.086498810681347</v>
+        <v>2.898761425426028</v>
       </c>
       <c r="D58">
-        <v>8.291138810681348</v>
+        <v>8.24259142542603</v>
       </c>
       <c r="E58">
-        <v>6.875640000000001</v>
+        <v>7.014830000000001</v>
       </c>
       <c r="F58">
-        <v>7.794640000000001</v>
+        <v>7.933830000000001</v>
       </c>
       <c r="G58">
         <v>2.59</v>
@@ -6037,37 +6037,37 @@
         <v>0.529</v>
       </c>
       <c r="M58">
-        <v>1.837976112</v>
+        <v>1.870797114</v>
       </c>
       <c r="N58">
-        <v>-1.308976112</v>
+        <v>-1.341797114</v>
       </c>
       <c r="O58">
-        <v>-0.2225259390400001</v>
+        <v>-0.22810550938</v>
       </c>
       <c r="P58">
-        <v>-1.08645017296</v>
+        <v>-1.11369160462</v>
       </c>
       <c r="Q58">
-        <v>-0.9154501729600003</v>
+        <v>-0.9426916046200003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.5518259550323641</v>
+        <v>0.5635940004982329</v>
       </c>
       <c r="T58">
-        <v>1.812240812455242</v>
+        <v>1.854385947628619</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04892881872231862</v>
+        <v>0.0480704183938569</v>
       </c>
       <c r="W58">
-        <v>0.2242625845452773</v>
+        <v>0.2244649953427285</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2878165807195213</v>
+        <v>0.2827671670226877</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3702904675595954</v>
+        <v>0.3721904675595955</v>
       </c>
       <c r="C59">
-        <v>2.898761425426028</v>
+        <v>2.71158925295204</v>
       </c>
       <c r="D59">
-        <v>8.24259142542603</v>
+        <v>8.194609252952041</v>
       </c>
       <c r="E59">
-        <v>7.014830000000001</v>
+        <v>7.154020000000001</v>
       </c>
       <c r="F59">
-        <v>7.933830000000001</v>
+        <v>8.073020000000001</v>
       </c>
       <c r="G59">
         <v>2.59</v>
@@ -6119,37 +6119,37 @@
         <v>0.529</v>
       </c>
       <c r="M59">
-        <v>1.870797114</v>
+        <v>1.903618116</v>
       </c>
       <c r="N59">
-        <v>-1.341797114</v>
+        <v>-1.374618116</v>
       </c>
       <c r="O59">
-        <v>-0.22810550938</v>
+        <v>-0.23368507972</v>
       </c>
       <c r="P59">
-        <v>-1.11369160462</v>
+        <v>-1.14093303628</v>
       </c>
       <c r="Q59">
-        <v>-0.9426916046200003</v>
+        <v>-0.9699330362800002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.5635940004982329</v>
+        <v>0.5759224290815244</v>
       </c>
       <c r="T59">
-        <v>1.854385947628619</v>
+        <v>1.898537994000729</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0480704183938569</v>
+        <v>0.04724161807672143</v>
       </c>
       <c r="W59">
-        <v>0.2244649953427285</v>
+        <v>0.2246604264575091</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2827671670226877</v>
+        <v>0.2778918710395378</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3721904675595954</v>
+        <v>0.3740904675595954</v>
       </c>
       <c r="C60">
-        <v>2.711589252952045</v>
+        <v>2.524972479654757</v>
       </c>
       <c r="D60">
-        <v>8.194609252952045</v>
+        <v>8.147182479654758</v>
       </c>
       <c r="E60">
-        <v>7.154019999999999</v>
+        <v>7.29321</v>
       </c>
       <c r="F60">
-        <v>8.07302</v>
+        <v>8.212210000000001</v>
       </c>
       <c r="G60">
         <v>2.59</v>
@@ -6201,37 +6201,37 @@
         <v>0.529</v>
       </c>
       <c r="M60">
-        <v>1.903618116</v>
+        <v>1.936439118</v>
       </c>
       <c r="N60">
-        <v>-1.374618116</v>
+        <v>-1.407439118</v>
       </c>
       <c r="O60">
-        <v>-0.23368507972</v>
+        <v>-0.23926465006</v>
       </c>
       <c r="P60">
-        <v>-1.14093303628</v>
+        <v>-1.16817446794</v>
       </c>
       <c r="Q60">
-        <v>-0.9699330362800002</v>
+        <v>-0.9971744679400002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.5759224290815241</v>
+        <v>0.588852244424976</v>
       </c>
       <c r="T60">
-        <v>1.898537994000729</v>
+        <v>1.944843798732454</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04724161807672143</v>
+        <v>0.04644091268559056</v>
       </c>
       <c r="W60">
-        <v>0.2246604264575091</v>
+        <v>0.2248492327887378</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2778918710395378</v>
+        <v>0.2731818393270034</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3740904675595954</v>
+        <v>0.3759904675595954</v>
       </c>
       <c r="C61">
-        <v>2.524972479654757</v>
+        <v>2.338901517809456</v>
       </c>
       <c r="D61">
-        <v>8.147182479654758</v>
+        <v>8.100301517809456</v>
       </c>
       <c r="E61">
-        <v>7.29321</v>
+        <v>7.432399999999999</v>
       </c>
       <c r="F61">
-        <v>8.212210000000001</v>
+        <v>8.3514</v>
       </c>
       <c r="G61">
         <v>2.59</v>
@@ -6283,37 +6283,37 @@
         <v>0.529</v>
       </c>
       <c r="M61">
-        <v>1.936439118</v>
+        <v>1.96926012</v>
       </c>
       <c r="N61">
-        <v>-1.407439118</v>
+        <v>-1.44026012</v>
       </c>
       <c r="O61">
-        <v>-0.23926465006</v>
+        <v>-0.2448442204</v>
       </c>
       <c r="P61">
-        <v>-1.16817446794</v>
+        <v>-1.1954158996</v>
       </c>
       <c r="Q61">
-        <v>-0.9971744679400002</v>
+        <v>-1.0244158996</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.588852244424976</v>
+        <v>0.6024285505356003</v>
       </c>
       <c r="T61">
-        <v>1.944843798732454</v>
+        <v>1.993464893700765</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04644091268559056</v>
+        <v>0.04566689747416405</v>
       </c>
       <c r="W61">
-        <v>0.2248492327887378</v>
+        <v>0.2250317455755921</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2731818393270034</v>
+        <v>0.2686288086715533</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3759904675595954</v>
+        <v>0.3778904675595955</v>
       </c>
       <c r="C62">
-        <v>2.338901517809456</v>
+        <v>2.153366999109661</v>
       </c>
       <c r="D62">
-        <v>8.100301517809456</v>
+        <v>8.053956999109662</v>
       </c>
       <c r="E62">
-        <v>7.432399999999999</v>
+        <v>7.57159</v>
       </c>
       <c r="F62">
-        <v>8.3514</v>
+        <v>8.490590000000001</v>
       </c>
       <c r="G62">
         <v>2.59</v>
@@ -6365,37 +6365,37 @@
         <v>0.529</v>
       </c>
       <c r="M62">
-        <v>1.96926012</v>
+        <v>2.002081122</v>
       </c>
       <c r="N62">
-        <v>-1.44026012</v>
+        <v>-1.473081122</v>
       </c>
       <c r="O62">
-        <v>-0.2448442204</v>
+        <v>-0.2504237907400001</v>
       </c>
       <c r="P62">
-        <v>-1.1954158996</v>
+        <v>-1.22265733126</v>
       </c>
       <c r="Q62">
-        <v>-1.0244158996</v>
+        <v>-1.05165733126</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.6024285505356003</v>
+        <v>0.6167010774724108</v>
       </c>
       <c r="T62">
-        <v>1.993464893700765</v>
+        <v>2.044579378154631</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04566689747416405</v>
+        <v>0.04491825981065316</v>
       </c>
       <c r="W62">
-        <v>0.2250317455755921</v>
+        <v>0.225208274336648</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2686288086715533</v>
+        <v>0.2642250577097244</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3778904675595955</v>
+        <v>0.3797904675595954</v>
       </c>
       <c r="C63">
-        <v>2.153366999109661</v>
+        <v>1.968359768426042</v>
       </c>
       <c r="D63">
-        <v>8.053956999109662</v>
+        <v>8.008139768426043</v>
       </c>
       <c r="E63">
-        <v>7.57159</v>
+        <v>7.71078</v>
       </c>
       <c r="F63">
-        <v>8.490590000000001</v>
+        <v>8.62978</v>
       </c>
       <c r="G63">
         <v>2.59</v>
@@ -6447,37 +6447,37 @@
         <v>0.529</v>
       </c>
       <c r="M63">
-        <v>2.002081122</v>
+        <v>2.034902124</v>
       </c>
       <c r="N63">
-        <v>-1.473081122</v>
+        <v>-1.505902124</v>
       </c>
       <c r="O63">
-        <v>-0.2504237907400001</v>
+        <v>-0.2560033610800001</v>
       </c>
       <c r="P63">
-        <v>-1.22265733126</v>
+        <v>-1.24989876292</v>
       </c>
       <c r="Q63">
-        <v>-1.05165733126</v>
+        <v>-1.07889876292</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.6167010774724108</v>
+        <v>0.6317247900374741</v>
       </c>
       <c r="T63">
-        <v>2.044579378154631</v>
+        <v>2.098384098632384</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04491825981065316</v>
+        <v>0.04419377174919101</v>
       </c>
       <c r="W63">
-        <v>0.225208274336648</v>
+        <v>0.2253791086215408</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2642250577097244</v>
+        <v>0.2599633632305354</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3797904675595954</v>
+        <v>0.3816904675595955</v>
       </c>
       <c r="C64">
-        <v>1.968359768426042</v>
+        <v>1.783870877777085</v>
       </c>
       <c r="D64">
-        <v>8.008139768426043</v>
+        <v>7.962840877777085</v>
       </c>
       <c r="E64">
-        <v>7.71078</v>
+        <v>7.849969999999999</v>
       </c>
       <c r="F64">
-        <v>8.62978</v>
+        <v>8.768969999999999</v>
       </c>
       <c r="G64">
         <v>2.59</v>
@@ -6529,37 +6529,37 @@
         <v>0.529</v>
       </c>
       <c r="M64">
-        <v>2.034902124</v>
+        <v>2.067723126</v>
       </c>
       <c r="N64">
-        <v>-1.505902124</v>
+        <v>-1.538723126</v>
       </c>
       <c r="O64">
-        <v>-0.2560033610800001</v>
+        <v>-0.26158293142</v>
       </c>
       <c r="P64">
-        <v>-1.24989876292</v>
+        <v>-1.27714019458</v>
       </c>
       <c r="Q64">
-        <v>-1.07889876292</v>
+        <v>-1.10614019458</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.6317247900374741</v>
+        <v>0.6475605951736222</v>
       </c>
       <c r="T64">
-        <v>2.098384098632384</v>
+        <v>2.155097182379206</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04419377174919101</v>
+        <v>0.04349228330872768</v>
       </c>
       <c r="W64">
-        <v>0.2253791086215408</v>
+        <v>0.225544519595802</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2599633632305354</v>
+        <v>0.2558369606395745</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3816904675595955</v>
+        <v>0.3835904675595955</v>
       </c>
       <c r="C65">
-        <v>1.783870877777085</v>
+        <v>1.599891580503302</v>
       </c>
       <c r="D65">
-        <v>7.962840877777085</v>
+        <v>7.918051580503302</v>
       </c>
       <c r="E65">
-        <v>7.849969999999999</v>
+        <v>7.98916</v>
       </c>
       <c r="F65">
-        <v>8.768969999999999</v>
+        <v>8.908160000000001</v>
       </c>
       <c r="G65">
         <v>2.59</v>
@@ -6611,37 +6611,37 @@
         <v>0.529</v>
       </c>
       <c r="M65">
-        <v>2.067723126</v>
+        <v>2.100544128</v>
       </c>
       <c r="N65">
-        <v>-1.538723126</v>
+        <v>-1.571544128</v>
       </c>
       <c r="O65">
-        <v>-0.26158293142</v>
+        <v>-0.2671625017600001</v>
       </c>
       <c r="P65">
-        <v>-1.27714019458</v>
+        <v>-1.30438162624</v>
       </c>
       <c r="Q65">
-        <v>-1.10614019458</v>
+        <v>-1.13338162624</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.6475605951736222</v>
+        <v>0.6642761672617784</v>
       </c>
       <c r="T65">
-        <v>2.155097182379206</v>
+        <v>2.214960993000851</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04349228330872768</v>
+        <v>0.04281271638202881</v>
       </c>
       <c r="W65">
-        <v>0.225544519595802</v>
+        <v>0.2257047614771176</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2558369606395745</v>
+        <v>0.2518395081295811</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3835904675595955</v>
+        <v>0.3854904675595954</v>
       </c>
       <c r="C66">
-        <v>1.599891580503302</v>
+        <v>1.416413325636933</v>
       </c>
       <c r="D66">
-        <v>7.918051580503302</v>
+        <v>7.873763325636932</v>
       </c>
       <c r="E66">
-        <v>7.98916</v>
+        <v>8.128349999999999</v>
       </c>
       <c r="F66">
-        <v>8.908160000000001</v>
+        <v>9.04735</v>
       </c>
       <c r="G66">
         <v>2.59</v>
@@ -6693,37 +6693,37 @@
         <v>0.529</v>
       </c>
       <c r="M66">
-        <v>2.100544128</v>
+        <v>2.13336513</v>
       </c>
       <c r="N66">
-        <v>-1.571544128</v>
+        <v>-1.60436513</v>
       </c>
       <c r="O66">
-        <v>-0.2671625017600001</v>
+        <v>-0.2727420721000001</v>
       </c>
       <c r="P66">
-        <v>-1.30438162624</v>
+        <v>-1.3316230579</v>
       </c>
       <c r="Q66">
-        <v>-1.13338162624</v>
+        <v>-1.1606230579</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.6642761672617784</v>
+        <v>0.6819469148978291</v>
       </c>
       <c r="T66">
-        <v>2.214960993000851</v>
+        <v>2.278245592800875</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04281271638202881</v>
+        <v>0.04215405920692067</v>
       </c>
       <c r="W66">
-        <v>0.2257047614771176</v>
+        <v>0.2258600728390081</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2518395081295811</v>
+        <v>0.2479650541583568</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3854904675595954</v>
+        <v>0.3873904675595955</v>
       </c>
       <c r="C67">
-        <v>1.416413325636933</v>
+        <v>1.233427752459525</v>
       </c>
       <c r="D67">
-        <v>7.873763325636932</v>
+        <v>7.829967752459526</v>
       </c>
       <c r="E67">
-        <v>8.128349999999999</v>
+        <v>8.26754</v>
       </c>
       <c r="F67">
-        <v>9.04735</v>
+        <v>9.186540000000001</v>
       </c>
       <c r="G67">
         <v>2.59</v>
@@ -6775,37 +6775,37 @@
         <v>0.529</v>
       </c>
       <c r="M67">
-        <v>2.13336513</v>
+        <v>2.166186132</v>
       </c>
       <c r="N67">
-        <v>-1.60436513</v>
+        <v>-1.637186132000001</v>
       </c>
       <c r="O67">
-        <v>-0.2727420721000001</v>
+        <v>-0.2783216424400001</v>
       </c>
       <c r="P67">
-        <v>-1.3316230579</v>
+        <v>-1.35886448956</v>
       </c>
       <c r="Q67">
-        <v>-1.1606230579</v>
+        <v>-1.18786448956</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.6819469148978291</v>
+        <v>0.700657118277177</v>
       </c>
       <c r="T67">
-        <v>2.278245592800875</v>
+        <v>2.345252816118548</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04215405920692067</v>
+        <v>0.04151536134014913</v>
       </c>
       <c r="W67">
-        <v>0.2258600728390081</v>
+        <v>0.2260106777959928</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2479650541583568</v>
+        <v>0.2442080078832302</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3873904675595955</v>
+        <v>0.3892904675595955</v>
       </c>
       <c r="C68">
-        <v>1.233427752459525</v>
+        <v>1.050926685240194</v>
       </c>
       <c r="D68">
-        <v>7.829967752459526</v>
+        <v>7.786656685240194</v>
       </c>
       <c r="E68">
-        <v>8.26754</v>
+        <v>8.40673</v>
       </c>
       <c r="F68">
-        <v>9.186540000000001</v>
+        <v>9.32573</v>
       </c>
       <c r="G68">
         <v>2.59</v>
@@ -6857,37 +6857,37 @@
         <v>0.529</v>
       </c>
       <c r="M68">
-        <v>2.166186132</v>
+        <v>2.199007134</v>
       </c>
       <c r="N68">
-        <v>-1.637186132000001</v>
+        <v>-1.670007134</v>
       </c>
       <c r="O68">
-        <v>-0.2783216424400001</v>
+        <v>-0.28390121278</v>
       </c>
       <c r="P68">
-        <v>-1.35886448956</v>
+        <v>-1.38610592122</v>
       </c>
       <c r="Q68">
-        <v>-1.18786448956</v>
+        <v>-1.21510592122</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.700657118277177</v>
+        <v>0.7205012733764855</v>
       </c>
       <c r="T68">
-        <v>2.345252816118548</v>
+        <v>2.416321083273655</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04151536134014913</v>
+        <v>0.04089572908134095</v>
       </c>
       <c r="W68">
-        <v>0.2260106777959928</v>
+        <v>0.2261567870826198</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2442080078832302</v>
+        <v>0.2405631122431819</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3892904675595955</v>
+        <v>0.3911904675595954</v>
       </c>
       <c r="C69">
-        <v>1.050926685240194</v>
+        <v>0.8689021281474911</v>
       </c>
       <c r="D69">
-        <v>7.786656685240194</v>
+        <v>7.743822128147493</v>
       </c>
       <c r="E69">
-        <v>8.40673</v>
+        <v>8.545920000000001</v>
       </c>
       <c r="F69">
-        <v>9.32573</v>
+        <v>9.464920000000001</v>
       </c>
       <c r="G69">
         <v>2.59</v>
@@ -6939,37 +6939,37 @@
         <v>0.529</v>
       </c>
       <c r="M69">
-        <v>2.199007134</v>
+        <v>2.231828136</v>
       </c>
       <c r="N69">
-        <v>-1.670007134</v>
+        <v>-1.702828136</v>
       </c>
       <c r="O69">
-        <v>-0.28390121278</v>
+        <v>-0.2894807831200001</v>
       </c>
       <c r="P69">
-        <v>-1.38610592122</v>
+        <v>-1.41334735288</v>
       </c>
       <c r="Q69">
-        <v>-1.21510592122</v>
+        <v>-1.24234735288</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.7205012733764855</v>
+        <v>0.7415856881695005</v>
       </c>
       <c r="T69">
-        <v>2.416321083273655</v>
+        <v>2.491831117125957</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04089572908134095</v>
+        <v>0.04029432130073299</v>
       </c>
       <c r="W69">
-        <v>0.2261567870826198</v>
+        <v>0.2262985990372872</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2405631122431819</v>
+        <v>0.2370254194160764</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3911904675595954</v>
+        <v>0.3930904675595954</v>
       </c>
       <c r="C70">
-        <v>0.8689021281474911</v>
+        <v>0.6873462603283436</v>
       </c>
       <c r="D70">
-        <v>7.743822128147493</v>
+        <v>7.701456260328344</v>
       </c>
       <c r="E70">
-        <v>8.545920000000001</v>
+        <v>8.68511</v>
       </c>
       <c r="F70">
-        <v>9.464920000000001</v>
+        <v>9.60411</v>
       </c>
       <c r="G70">
         <v>2.59</v>
@@ -7021,37 +7021,37 @@
         <v>0.529</v>
       </c>
       <c r="M70">
-        <v>2.231828136</v>
+        <v>2.264649138</v>
       </c>
       <c r="N70">
-        <v>-1.702828136</v>
+        <v>-1.735649138</v>
       </c>
       <c r="O70">
-        <v>-0.2894807831200001</v>
+        <v>-0.2950603534600001</v>
       </c>
       <c r="P70">
-        <v>-1.41334735288</v>
+        <v>-1.44058878454</v>
       </c>
       <c r="Q70">
-        <v>-1.24234735288</v>
+        <v>-1.26958878454</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.7415856881695005</v>
+        <v>0.7640303877878716</v>
       </c>
       <c r="T70">
-        <v>2.491831117125957</v>
+        <v>2.572212766065504</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04029432130073299</v>
+        <v>0.03971034562970787</v>
       </c>
       <c r="W70">
-        <v>0.2262985990372872</v>
+        <v>0.2264363005005149</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2370254194160764</v>
+        <v>0.2335902684100463</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3930904675595954</v>
+        <v>0.3949904675595954</v>
       </c>
       <c r="C71">
-        <v>0.6873462603283436</v>
+        <v>0.5062514311476143</v>
       </c>
       <c r="D71">
-        <v>7.701456260328344</v>
+        <v>7.659551431147615</v>
       </c>
       <c r="E71">
-        <v>8.68511</v>
+        <v>8.824300000000001</v>
       </c>
       <c r="F71">
-        <v>9.60411</v>
+        <v>9.743300000000001</v>
       </c>
       <c r="G71">
         <v>2.59</v>
@@ -7103,37 +7103,37 @@
         <v>0.529</v>
       </c>
       <c r="M71">
-        <v>2.264649138</v>
+        <v>2.297470140000001</v>
       </c>
       <c r="N71">
-        <v>-1.735649138</v>
+        <v>-1.768470140000001</v>
       </c>
       <c r="O71">
-        <v>-0.2950603534600001</v>
+        <v>-0.3006399238000002</v>
       </c>
       <c r="P71">
-        <v>-1.44058878454</v>
+        <v>-1.467830216200001</v>
       </c>
       <c r="Q71">
-        <v>-1.26958878454</v>
+        <v>-1.2968302162</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.7640303877878716</v>
+        <v>0.7879714007141341</v>
       </c>
       <c r="T71">
-        <v>2.572212766065504</v>
+        <v>2.657953191601021</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03971034562970787</v>
+        <v>0.0391430549778549</v>
       </c>
       <c r="W71">
-        <v>0.2264363005005149</v>
+        <v>0.2265700676362218</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2335902684100463</v>
+        <v>0.230253264575617</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3949904675595954</v>
+        <v>0.3968904675595955</v>
       </c>
       <c r="C72">
-        <v>0.5062514311476143</v>
+        <v>0.3256101555822646</v>
       </c>
       <c r="D72">
-        <v>7.659551431147615</v>
+        <v>7.618100155582264</v>
       </c>
       <c r="E72">
-        <v>8.824300000000001</v>
+        <v>8.96349</v>
       </c>
       <c r="F72">
-        <v>9.743300000000001</v>
+        <v>9.882490000000001</v>
       </c>
       <c r="G72">
         <v>2.59</v>
@@ -7185,37 +7185,37 @@
         <v>0.529</v>
       </c>
       <c r="M72">
-        <v>2.297470140000001</v>
+        <v>2.330291142</v>
       </c>
       <c r="N72">
-        <v>-1.768470140000001</v>
+        <v>-1.801291142</v>
       </c>
       <c r="O72">
-        <v>-0.3006399238000002</v>
+        <v>-0.30621949414</v>
       </c>
       <c r="P72">
-        <v>-1.467830216200001</v>
+        <v>-1.49507164786</v>
       </c>
       <c r="Q72">
-        <v>-1.2968302162</v>
+        <v>-1.32407164786</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.7879714007141341</v>
+        <v>0.8135635179801388</v>
       </c>
       <c r="T72">
-        <v>2.657953191601021</v>
+        <v>2.749606749932091</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0391430549778549</v>
+        <v>0.03859174434436399</v>
       </c>
       <c r="W72">
-        <v>0.2265700676362218</v>
+        <v>0.226700066683599</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.230253264575617</v>
+        <v>0.2270102608491998</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3968904675595955</v>
+        <v>0.3987904675595955</v>
       </c>
       <c r="C73">
-        <v>0.3256101555822646</v>
+        <v>0.1454151097642438</v>
       </c>
       <c r="D73">
-        <v>7.618100155582264</v>
+        <v>7.577095109764243</v>
       </c>
       <c r="E73">
-        <v>8.96349</v>
+        <v>9.102679999999999</v>
       </c>
       <c r="F73">
-        <v>9.882490000000001</v>
+        <v>10.02168</v>
       </c>
       <c r="G73">
         <v>2.59</v>
@@ -7267,37 +7267,37 @@
         <v>0.529</v>
       </c>
       <c r="M73">
-        <v>2.330291142</v>
+        <v>2.363112144</v>
       </c>
       <c r="N73">
-        <v>-1.801291142</v>
+        <v>-1.834112144</v>
       </c>
       <c r="O73">
-        <v>-0.30621949414</v>
+        <v>-0.3117990644800001</v>
       </c>
       <c r="P73">
-        <v>-1.49507164786</v>
+        <v>-1.52231307952</v>
       </c>
       <c r="Q73">
-        <v>-1.32407164786</v>
+        <v>-1.35131307952</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.8135635179801385</v>
+        <v>0.8409836436222864</v>
       </c>
       <c r="T73">
-        <v>2.74960674993209</v>
+        <v>2.847806991001093</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03859174434436399</v>
+        <v>0.03805574789513672</v>
       </c>
       <c r="W73">
-        <v>0.226700066683599</v>
+        <v>0.2268264546463268</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2270102608491998</v>
+        <v>0.2238573405596277</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3987904675595955</v>
+        <v>0.4006904675595954</v>
       </c>
       <c r="C74">
-        <v>0.1454151097642438</v>
+        <v>-0.03434087333344316</v>
       </c>
       <c r="D74">
-        <v>7.577095109764243</v>
+        <v>7.536529126666559</v>
       </c>
       <c r="E74">
-        <v>9.102679999999999</v>
+        <v>9.24187</v>
       </c>
       <c r="F74">
-        <v>10.02168</v>
+        <v>10.16087</v>
       </c>
       <c r="G74">
         <v>2.59</v>
@@ -7349,37 +7349,37 @@
         <v>0.529</v>
       </c>
       <c r="M74">
-        <v>2.363112144</v>
+        <v>2.395933146</v>
       </c>
       <c r="N74">
-        <v>-1.834112144</v>
+        <v>-1.866933146</v>
       </c>
       <c r="O74">
-        <v>-0.3117990644800001</v>
+        <v>-0.3173786348200001</v>
       </c>
       <c r="P74">
-        <v>-1.52231307952</v>
+        <v>-1.54955451118</v>
       </c>
       <c r="Q74">
-        <v>-1.35131307952</v>
+        <v>-1.37855451118</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.8409836436222864</v>
+        <v>0.8704348896823709</v>
       </c>
       <c r="T74">
-        <v>2.847806991001093</v>
+        <v>2.953281324001134</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03805574789513672</v>
+        <v>0.03753443628013484</v>
       </c>
       <c r="W74">
-        <v>0.2268264546463268</v>
+        <v>0.2269493799251442</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2238573405596277</v>
+        <v>0.2207908016478519</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.4006904675595954</v>
+        <v>0.4025904675595954</v>
       </c>
       <c r="C75">
-        <v>-0.03434087333344316</v>
+        <v>-0.2136648080728119</v>
       </c>
       <c r="D75">
-        <v>7.536529126666559</v>
+        <v>7.496395191927189</v>
       </c>
       <c r="E75">
-        <v>9.24187</v>
+        <v>9.38106</v>
       </c>
       <c r="F75">
-        <v>10.16087</v>
+        <v>10.30006</v>
       </c>
       <c r="G75">
         <v>2.59</v>
@@ -7431,37 +7431,37 @@
         <v>0.529</v>
       </c>
       <c r="M75">
-        <v>2.395933146</v>
+        <v>2.428754148</v>
       </c>
       <c r="N75">
-        <v>-1.866933146</v>
+        <v>-1.899754148</v>
       </c>
       <c r="O75">
-        <v>-0.3173786348200001</v>
+        <v>-0.3229582051600001</v>
       </c>
       <c r="P75">
-        <v>-1.54955451118</v>
+        <v>-1.57679594284</v>
       </c>
       <c r="Q75">
-        <v>-1.37855451118</v>
+        <v>-1.405795942840001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.8704348896823709</v>
+        <v>0.9021516162086159</v>
       </c>
       <c r="T75">
-        <v>2.953281324001134</v>
+        <v>3.066869067231946</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03753443628013484</v>
+        <v>0.03702721416824113</v>
       </c>
       <c r="W75">
-        <v>0.2269493799251442</v>
+        <v>0.2270689828991287</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2207908016478519</v>
+        <v>0.2178071421661242</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.4025904675595954</v>
+        <v>0.4044904675595954</v>
       </c>
       <c r="C76">
-        <v>-0.2136648080728119</v>
+        <v>-0.3925635601942936</v>
       </c>
       <c r="D76">
-        <v>7.496395191927189</v>
+        <v>7.456686439805708</v>
       </c>
       <c r="E76">
-        <v>9.38106</v>
+        <v>9.520250000000001</v>
       </c>
       <c r="F76">
-        <v>10.30006</v>
+        <v>10.43925</v>
       </c>
       <c r="G76">
         <v>2.59</v>
@@ -7513,37 +7513,37 @@
         <v>0.529</v>
       </c>
       <c r="M76">
-        <v>2.428754148</v>
+        <v>2.46157515</v>
       </c>
       <c r="N76">
-        <v>-1.899754148</v>
+        <v>-1.93257515</v>
       </c>
       <c r="O76">
-        <v>-0.3229582051600001</v>
+        <v>-0.3285377755000001</v>
       </c>
       <c r="P76">
-        <v>-1.57679594284</v>
+        <v>-1.6040373745</v>
       </c>
       <c r="Q76">
-        <v>-1.405795942840001</v>
+        <v>-1.4330373745</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.9021516162086159</v>
+        <v>0.9364056808569607</v>
       </c>
       <c r="T76">
-        <v>3.066869067231946</v>
+        <v>3.189543829921225</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03702721416824113</v>
+        <v>0.03653351797933124</v>
       </c>
       <c r="W76">
-        <v>0.2270689828991287</v>
+        <v>0.2271853964604737</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2178071421661242</v>
+        <v>0.2149030469372425</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.4044904675595954</v>
+        <v>0.4063904675595954</v>
       </c>
       <c r="C77">
-        <v>-0.3925635601942936</v>
+        <v>-0.5710438507322397</v>
       </c>
       <c r="D77">
-        <v>7.456686439805708</v>
+        <v>7.417396149267761</v>
       </c>
       <c r="E77">
-        <v>9.520250000000001</v>
+        <v>9.65944</v>
       </c>
       <c r="F77">
-        <v>10.43925</v>
+        <v>10.57844</v>
       </c>
       <c r="G77">
         <v>2.59</v>
@@ -7595,37 +7595,37 @@
         <v>0.529</v>
       </c>
       <c r="M77">
-        <v>2.46157515</v>
+        <v>2.494396152</v>
       </c>
       <c r="N77">
-        <v>-1.93257515</v>
+        <v>-1.965396152</v>
       </c>
       <c r="O77">
-        <v>-0.3285377755000001</v>
+        <v>-0.3341173458400001</v>
       </c>
       <c r="P77">
-        <v>-1.6040373745</v>
+        <v>-1.63127880616</v>
       </c>
       <c r="Q77">
-        <v>-1.4330373745</v>
+        <v>-1.46027880616</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.9364056808569607</v>
+        <v>0.9735142508926674</v>
       </c>
       <c r="T77">
-        <v>3.189543829921225</v>
+        <v>3.322441489501275</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03653351797933124</v>
+        <v>0.03605281379539268</v>
       </c>
       <c r="W77">
-        <v>0.2271853964604737</v>
+        <v>0.2272987465070464</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2149030469372425</v>
+        <v>0.2120753752670157</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.4063904675595954</v>
+        <v>0.4082904675595955</v>
       </c>
       <c r="C78">
-        <v>-0.5710438507322397</v>
+        <v>-0.7491122598073474</v>
       </c>
       <c r="D78">
-        <v>7.417396149267761</v>
+        <v>7.378517740192652</v>
       </c>
       <c r="E78">
-        <v>9.65944</v>
+        <v>9.798629999999999</v>
       </c>
       <c r="F78">
-        <v>10.57844</v>
+        <v>10.71763</v>
       </c>
       <c r="G78">
         <v>2.59</v>
@@ -7677,37 +7677,37 @@
         <v>0.529</v>
       </c>
       <c r="M78">
-        <v>2.494396152</v>
+        <v>2.527217154</v>
       </c>
       <c r="N78">
-        <v>-1.965396152</v>
+        <v>-1.998217154</v>
       </c>
       <c r="O78">
-        <v>-0.3341173458400001</v>
+        <v>-0.3396969161800001</v>
       </c>
       <c r="P78">
-        <v>-1.63127880616</v>
+        <v>-1.65852023782</v>
       </c>
       <c r="Q78">
-        <v>-1.46027880616</v>
+        <v>-1.48752023782</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.9735142508926674</v>
+        <v>1.013849653105392</v>
       </c>
       <c r="T78">
-        <v>3.322441489501275</v>
+        <v>3.466895467305679</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03605281379539268</v>
+        <v>0.03558459543441355</v>
       </c>
       <c r="W78">
-        <v>0.2272987465070464</v>
+        <v>0.2274091523965653</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2120753752670157</v>
+        <v>0.2093211496141973</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.4082904675595955</v>
+        <v>0.4101904675595954</v>
       </c>
       <c r="C79">
-        <v>-0.7491122598073474</v>
+        <v>-0.9267752303003878</v>
       </c>
       <c r="D79">
-        <v>7.378517740192652</v>
+        <v>7.340044769699612</v>
       </c>
       <c r="E79">
-        <v>9.798629999999999</v>
+        <v>9.93782</v>
       </c>
       <c r="F79">
-        <v>10.71763</v>
+        <v>10.85682</v>
       </c>
       <c r="G79">
         <v>2.59</v>
@@ -7759,37 +7759,37 @@
         <v>0.529</v>
       </c>
       <c r="M79">
-        <v>2.527217154</v>
+        <v>2.560038156000001</v>
       </c>
       <c r="N79">
-        <v>-1.998217154</v>
+        <v>-2.031038156000001</v>
       </c>
       <c r="O79">
-        <v>-0.3396969161800001</v>
+        <v>-0.3452764865200001</v>
       </c>
       <c r="P79">
-        <v>-1.65852023782</v>
+        <v>-1.68576166948</v>
       </c>
       <c r="Q79">
-        <v>-1.48752023782</v>
+        <v>-1.51476166948</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>1.013849653105392</v>
+        <v>1.057851910064728</v>
       </c>
       <c r="T79">
-        <v>3.466895467305679</v>
+        <v>3.624481624910483</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03558459543441355</v>
+        <v>0.03512838267243389</v>
       </c>
       <c r="W79">
-        <v>0.2274091523965653</v>
+        <v>0.2275167273658401</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2093211496141973</v>
+        <v>0.206637545131964</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.4101904675595954</v>
+        <v>0.4120904675595955</v>
       </c>
       <c r="C80">
-        <v>-0.9267752303003878</v>
+        <v>-1.104039071411639</v>
       </c>
       <c r="D80">
-        <v>7.340044769699612</v>
+        <v>7.301970928588361</v>
       </c>
       <c r="E80">
-        <v>9.93782</v>
+        <v>10.07701</v>
       </c>
       <c r="F80">
-        <v>10.85682</v>
+        <v>10.99601</v>
       </c>
       <c r="G80">
         <v>2.59</v>
@@ -7841,37 +7841,37 @@
         <v>0.529</v>
       </c>
       <c r="M80">
-        <v>2.560038156000001</v>
+        <v>2.592859158</v>
       </c>
       <c r="N80">
-        <v>-2.031038156000001</v>
+        <v>-2.063859158</v>
       </c>
       <c r="O80">
-        <v>-0.3452764865200001</v>
+        <v>-0.35085605686</v>
       </c>
       <c r="P80">
-        <v>-1.68576166948</v>
+        <v>-1.71300310114</v>
       </c>
       <c r="Q80">
-        <v>-1.51476166948</v>
+        <v>-1.54200310114</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>1.057851910064728</v>
+        <v>1.106044858163049</v>
       </c>
       <c r="T80">
-        <v>3.624481624910483</v>
+        <v>3.797075988001459</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03512838267243389</v>
+        <v>0.03468371960063094</v>
       </c>
       <c r="W80">
-        <v>0.2275167273658401</v>
+        <v>0.2276215789181713</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.206637545131964</v>
+        <v>0.2040218800037114</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.4120904675595955</v>
+        <v>0.4139904675595955</v>
       </c>
       <c r="C81">
-        <v>-1.104039071411639</v>
+        <v>-1.280909962110073</v>
       </c>
       <c r="D81">
-        <v>7.301970928588361</v>
+        <v>7.264290037889929</v>
       </c>
       <c r="E81">
-        <v>10.07701</v>
+        <v>10.2162</v>
       </c>
       <c r="F81">
-        <v>10.99601</v>
+        <v>11.1352</v>
       </c>
       <c r="G81">
         <v>2.59</v>
@@ -7923,37 +7923,37 @@
         <v>0.529</v>
       </c>
       <c r="M81">
-        <v>2.592859158</v>
+        <v>2.62568016</v>
       </c>
       <c r="N81">
-        <v>-2.063859158</v>
+        <v>-2.09668016</v>
       </c>
       <c r="O81">
-        <v>-0.35085605686</v>
+        <v>-0.3564356272000001</v>
       </c>
       <c r="P81">
-        <v>-1.71300310114</v>
+        <v>-1.7402445328</v>
       </c>
       <c r="Q81">
-        <v>-1.54200310114</v>
+        <v>-1.5692445328</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>1.106044858163049</v>
+        <v>1.159057101071201</v>
       </c>
       <c r="T81">
-        <v>3.797075988001459</v>
+        <v>3.986929787401531</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03468371960063094</v>
+        <v>0.03425017310562304</v>
       </c>
       <c r="W81">
-        <v>0.2276215789181713</v>
+        <v>0.2277238091816941</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2040218800037114</v>
+        <v>0.2014716065036649</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.4139904675595955</v>
+        <v>0.4158904675595955</v>
       </c>
       <c r="C82">
-        <v>-1.280909962110073</v>
+        <v>-1.457393954476327</v>
       </c>
       <c r="D82">
-        <v>7.264290037889929</v>
+        <v>7.226996045523674</v>
       </c>
       <c r="E82">
-        <v>10.2162</v>
+        <v>10.35539</v>
       </c>
       <c r="F82">
-        <v>11.1352</v>
+        <v>11.27439</v>
       </c>
       <c r="G82">
         <v>2.59</v>
@@ -8005,37 +8005,37 @@
         <v>0.529</v>
       </c>
       <c r="M82">
-        <v>2.62568016</v>
+        <v>2.658501162</v>
       </c>
       <c r="N82">
-        <v>-2.09668016</v>
+        <v>-2.129501162</v>
       </c>
       <c r="O82">
-        <v>-0.3564356272000001</v>
+        <v>-0.3620151975400001</v>
       </c>
       <c r="P82">
-        <v>-1.7402445328</v>
+        <v>-1.76748596446</v>
       </c>
       <c r="Q82">
-        <v>-1.5692445328</v>
+        <v>-1.59648596446</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>1.159057101071201</v>
+        <v>1.217649580074949</v>
       </c>
       <c r="T82">
-        <v>3.986929787401531</v>
+        <v>4.19676819726477</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03425017310562304</v>
+        <v>0.03382733146234375</v>
       </c>
       <c r="W82">
-        <v>0.2277238091816941</v>
+        <v>0.2278235152411794</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2014716065036649</v>
+        <v>0.198984302719669</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.4158904675595955</v>
+        <v>0.4177904675595955</v>
       </c>
       <c r="C83">
-        <v>-1.457393954476327</v>
+        <v>-1.633496976943213</v>
       </c>
       <c r="D83">
-        <v>7.226996045523674</v>
+        <v>7.190083023056788</v>
       </c>
       <c r="E83">
-        <v>10.35539</v>
+        <v>10.49458</v>
       </c>
       <c r="F83">
-        <v>11.27439</v>
+        <v>11.41358</v>
       </c>
       <c r="G83">
         <v>2.59</v>
@@ -8087,37 +8087,37 @@
         <v>0.529</v>
       </c>
       <c r="M83">
-        <v>2.658501162</v>
+        <v>2.691322164</v>
       </c>
       <c r="N83">
-        <v>-2.129501162</v>
+        <v>-2.162322164</v>
       </c>
       <c r="O83">
-        <v>-0.3620151975400001</v>
+        <v>-0.3675947678800001</v>
       </c>
       <c r="P83">
-        <v>-1.76748596446</v>
+        <v>-1.79472739612</v>
       </c>
       <c r="Q83">
-        <v>-1.59648596446</v>
+        <v>-1.62372739612</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>1.217649580074949</v>
+        <v>1.282752334523557</v>
       </c>
       <c r="T83">
-        <v>4.19676819726477</v>
+        <v>4.429921986001703</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03382733146234375</v>
+        <v>0.03341480302987614</v>
       </c>
       <c r="W83">
-        <v>0.2278235152411794</v>
+        <v>0.2279207894455552</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.198984302719669</v>
+        <v>0.1965576648816243</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.4177904675595955</v>
+        <v>0.4196904675595955</v>
       </c>
       <c r="C84">
-        <v>-1.633496976943213</v>
+        <v>-1.809224837437425</v>
       </c>
       <c r="D84">
-        <v>7.190083023056788</v>
+        <v>7.153545162562576</v>
       </c>
       <c r="E84">
-        <v>10.49458</v>
+        <v>10.63377</v>
       </c>
       <c r="F84">
-        <v>11.41358</v>
+        <v>11.55277</v>
       </c>
       <c r="G84">
         <v>2.59</v>
@@ -8169,37 +8169,37 @@
         <v>0.529</v>
       </c>
       <c r="M84">
-        <v>2.691322164</v>
+        <v>2.724143166</v>
       </c>
       <c r="N84">
-        <v>-2.162322164</v>
+        <v>-2.195143166</v>
       </c>
       <c r="O84">
-        <v>-0.3675947678800001</v>
+        <v>-0.3731743382200001</v>
       </c>
       <c r="P84">
-        <v>-1.79472739612</v>
+        <v>-1.82196882778</v>
       </c>
       <c r="Q84">
-        <v>-1.62372739612</v>
+        <v>-1.65096882778</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.282752334523557</v>
+        <v>1.355514236554355</v>
       </c>
       <c r="T84">
-        <v>4.429921986001703</v>
+        <v>4.690505632237097</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03341480302987614</v>
+        <v>0.03301221504156438</v>
       </c>
       <c r="W84">
-        <v>0.2279207894455552</v>
+        <v>0.2280157196931991</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1965576648816243</v>
+        <v>0.1941895002444963</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.4196904675595955</v>
+        <v>0.4215904675595955</v>
       </c>
       <c r="C85">
-        <v>-1.809224837437425</v>
+        <v>-1.984583226425933</v>
       </c>
       <c r="D85">
-        <v>7.153545162562576</v>
+        <v>7.117376773574069</v>
       </c>
       <c r="E85">
-        <v>10.63377</v>
+        <v>10.77296</v>
       </c>
       <c r="F85">
-        <v>11.55277</v>
+        <v>11.69196</v>
       </c>
       <c r="G85">
         <v>2.59</v>
@@ -8251,37 +8251,37 @@
         <v>0.529</v>
       </c>
       <c r="M85">
-        <v>2.724143166</v>
+        <v>2.756964168000001</v>
       </c>
       <c r="N85">
-        <v>-2.195143166</v>
+        <v>-2.227964168000001</v>
       </c>
       <c r="O85">
-        <v>-0.3731743382200001</v>
+        <v>-0.3787539085600001</v>
       </c>
       <c r="P85">
-        <v>-1.82196882778</v>
+        <v>-1.84921025944</v>
       </c>
       <c r="Q85">
-        <v>-1.65096882778</v>
+        <v>-1.678210259440001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.355514236554355</v>
+        <v>1.437371376339002</v>
       </c>
       <c r="T85">
-        <v>4.690505632237097</v>
+        <v>4.983662234251916</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03301221504156438</v>
+        <v>0.03261921248154575</v>
       </c>
       <c r="W85">
-        <v>0.2280157196931991</v>
+        <v>0.2281083896968515</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1941895002444963</v>
+        <v>0.1918777204796809</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.4215904675595955</v>
+        <v>0.4234904675595955</v>
       </c>
       <c r="C86">
-        <v>-1.984583226425931</v>
+        <v>-2.159577719870441</v>
       </c>
       <c r="D86">
-        <v>7.117376773574069</v>
+        <v>7.081572280129559</v>
       </c>
       <c r="E86">
-        <v>10.77296</v>
+        <v>10.91215</v>
       </c>
       <c r="F86">
-        <v>11.69196</v>
+        <v>11.83115</v>
       </c>
       <c r="G86">
         <v>2.59</v>
@@ -8333,37 +8333,37 @@
         <v>0.529</v>
       </c>
       <c r="M86">
-        <v>2.756964168</v>
+        <v>2.78978517</v>
       </c>
       <c r="N86">
-        <v>-2.227964168</v>
+        <v>-2.260785170000001</v>
       </c>
       <c r="O86">
-        <v>-0.3787539085600001</v>
+        <v>-0.3843334789000001</v>
       </c>
       <c r="P86">
-        <v>-1.84921025944</v>
+        <v>-1.8764516911</v>
       </c>
       <c r="Q86">
-        <v>-1.67821025944</v>
+        <v>-1.7054516911</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.437371376339001</v>
+        <v>1.530142801428268</v>
       </c>
       <c r="T86">
-        <v>4.983662234251913</v>
+        <v>5.315906383202041</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03261921248154576</v>
+        <v>0.03223545704058639</v>
       </c>
       <c r="W86">
-        <v>0.2281083896968515</v>
+        <v>0.2281988792298297</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1918777204796809</v>
+        <v>0.1896203355328611</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.4234904675595955</v>
+        <v>0.4253904675595955</v>
       </c>
       <c r="C87">
-        <v>-2.159577719870441</v>
+        <v>-2.334213782093101</v>
       </c>
       <c r="D87">
-        <v>7.081572280129559</v>
+        <v>7.0461262179069</v>
       </c>
       <c r="E87">
-        <v>10.91215</v>
+        <v>11.05134</v>
       </c>
       <c r="F87">
-        <v>11.83115</v>
+        <v>11.97034</v>
       </c>
       <c r="G87">
         <v>2.59</v>
@@ -8415,37 +8415,37 @@
         <v>0.529</v>
       </c>
       <c r="M87">
-        <v>2.78978517</v>
+        <v>2.822606172</v>
       </c>
       <c r="N87">
-        <v>-2.260785170000001</v>
+        <v>-2.293606172</v>
       </c>
       <c r="O87">
-        <v>-0.3843334789000001</v>
+        <v>-0.38991304924</v>
       </c>
       <c r="P87">
-        <v>-1.8764516911</v>
+        <v>-1.90369312276</v>
       </c>
       <c r="Q87">
-        <v>-1.7054516911</v>
+        <v>-1.73269312276</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.530142801428268</v>
+        <v>1.636167287244573</v>
       </c>
       <c r="T87">
-        <v>5.315906383202041</v>
+        <v>5.695613982002186</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03223545704058639</v>
+        <v>0.03186062614476562</v>
       </c>
       <c r="W87">
-        <v>0.2281988792298297</v>
+        <v>0.2282872643550643</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1896203355328611</v>
+        <v>0.187415447910386</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.4253904675595955</v>
+        <v>0.4272904675595954</v>
       </c>
       <c r="C88">
-        <v>-2.334213782093101</v>
+        <v>-2.508496768556599</v>
       </c>
       <c r="D88">
-        <v>7.0461262179069</v>
+        <v>7.011033231443402</v>
       </c>
       <c r="E88">
-        <v>11.05134</v>
+        <v>11.19053</v>
       </c>
       <c r="F88">
-        <v>11.97034</v>
+        <v>12.10953</v>
       </c>
       <c r="G88">
         <v>2.59</v>
@@ -8497,37 +8497,37 @@
         <v>0.529</v>
       </c>
       <c r="M88">
-        <v>2.822606172</v>
+        <v>2.855427174</v>
       </c>
       <c r="N88">
-        <v>-2.293606172</v>
+        <v>-2.326427174</v>
       </c>
       <c r="O88">
-        <v>-0.38991304924</v>
+        <v>-0.3954926195800001</v>
       </c>
       <c r="P88">
-        <v>-1.90369312276</v>
+        <v>-1.93093455442</v>
       </c>
       <c r="Q88">
-        <v>-1.73269312276</v>
+        <v>-1.75993455442</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.636167287244573</v>
+        <v>1.758503232417232</v>
       </c>
       <c r="T88">
-        <v>5.695613982002186</v>
+        <v>6.133738134463893</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03186062614476562</v>
+        <v>0.03149441205114762</v>
       </c>
       <c r="W88">
-        <v>0.2282872643550643</v>
+        <v>0.2283736176383394</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.187415447910386</v>
+        <v>0.1852612473596918</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.4272904675595954</v>
+        <v>0.4291904675595954</v>
       </c>
       <c r="C89">
-        <v>-2.508496768556599</v>
+        <v>-2.682431928561581</v>
       </c>
       <c r="D89">
-        <v>7.011033231443402</v>
+        <v>6.97628807143842</v>
       </c>
       <c r="E89">
-        <v>11.19053</v>
+        <v>11.32972</v>
       </c>
       <c r="F89">
-        <v>12.10953</v>
+        <v>12.24872</v>
       </c>
       <c r="G89">
         <v>2.59</v>
@@ -8579,37 +8579,37 @@
         <v>0.529</v>
       </c>
       <c r="M89">
-        <v>2.855427174</v>
+        <v>2.888248176</v>
       </c>
       <c r="N89">
-        <v>-2.326427174</v>
+        <v>-2.359248176</v>
       </c>
       <c r="O89">
-        <v>-0.3954926195800001</v>
+        <v>-0.4010721899200001</v>
       </c>
       <c r="P89">
-        <v>-1.93093455442</v>
+        <v>-1.95817598608</v>
       </c>
       <c r="Q89">
-        <v>-1.75993455442</v>
+        <v>-1.78717598608</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.758503232417232</v>
+        <v>1.901228501785335</v>
       </c>
       <c r="T89">
-        <v>6.133738134463893</v>
+        <v>6.644882979002551</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03149441205114762</v>
+        <v>0.03113652100511186</v>
       </c>
       <c r="W89">
-        <v>0.2283736176383394</v>
+        <v>0.2284580083469946</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1852612473596918</v>
+        <v>0.1831560059124226</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.4291904675595954</v>
+        <v>0.4310904675595955</v>
       </c>
       <c r="C90">
-        <v>-2.682431928561581</v>
+        <v>-2.856024407864245</v>
       </c>
       <c r="D90">
-        <v>6.97628807143842</v>
+        <v>6.941885592135755</v>
       </c>
       <c r="E90">
-        <v>11.32972</v>
+        <v>11.46891</v>
       </c>
       <c r="F90">
-        <v>12.24872</v>
+        <v>12.38791</v>
       </c>
       <c r="G90">
         <v>2.59</v>
@@ -8661,37 +8661,37 @@
         <v>0.529</v>
       </c>
       <c r="M90">
-        <v>2.888248176</v>
+        <v>2.921069178</v>
       </c>
       <c r="N90">
-        <v>-2.359248176</v>
+        <v>-2.392069178</v>
       </c>
       <c r="O90">
-        <v>-0.4010721899200001</v>
+        <v>-0.4066517602600001</v>
       </c>
       <c r="P90">
-        <v>-1.95817598608</v>
+        <v>-1.98541741774</v>
       </c>
       <c r="Q90">
-        <v>-1.78717598608</v>
+        <v>-1.81441741774</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.901228501785335</v>
+        <v>2.069903820129456</v>
       </c>
       <c r="T90">
-        <v>6.644882979002551</v>
+        <v>7.248963249820966</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03113652100511186</v>
+        <v>0.03078667245449262</v>
       </c>
       <c r="W90">
-        <v>0.2284580083469946</v>
+        <v>0.2285405026352307</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1831560059124226</v>
+        <v>0.1810980732617212</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.4310904675595955</v>
+        <v>0.4329904675595955</v>
       </c>
       <c r="C91">
-        <v>-2.856024407864245</v>
+        <v>-3.029279251216899</v>
       </c>
       <c r="D91">
-        <v>6.941885592135755</v>
+        <v>6.907820748783102</v>
       </c>
       <c r="E91">
-        <v>11.46891</v>
+        <v>11.6081</v>
       </c>
       <c r="F91">
-        <v>12.38791</v>
+        <v>12.5271</v>
       </c>
       <c r="G91">
         <v>2.59</v>
@@ -8743,37 +8743,37 @@
         <v>0.529</v>
       </c>
       <c r="M91">
-        <v>2.921069178</v>
+        <v>2.95389018</v>
       </c>
       <c r="N91">
-        <v>-2.392069178</v>
+        <v>-2.42489018</v>
       </c>
       <c r="O91">
-        <v>-0.4066517602600001</v>
+        <v>-0.4122313306000001</v>
       </c>
       <c r="P91">
-        <v>-1.98541741774</v>
+        <v>-2.0126588494</v>
       </c>
       <c r="Q91">
-        <v>-1.81441741774</v>
+        <v>-1.8416588494</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>2.069903820129456</v>
+        <v>2.272314202142402</v>
       </c>
       <c r="T91">
-        <v>7.248963249820966</v>
+        <v>7.973859574803063</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03078667245449262</v>
+        <v>0.03044459831610937</v>
       </c>
       <c r="W91">
-        <v>0.2285405026352307</v>
+        <v>0.2286211637170614</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1810980732617212</v>
+        <v>0.1790858724477021</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.4329904675595955</v>
+        <v>0.4348904675595955</v>
       </c>
       <c r="C92">
-        <v>-3.029279251216899</v>
+        <v>-3.202201404834046</v>
       </c>
       <c r="D92">
-        <v>6.907820748783102</v>
+        <v>6.874088595165954</v>
       </c>
       <c r="E92">
-        <v>11.6081</v>
+        <v>11.74729</v>
       </c>
       <c r="F92">
-        <v>12.5271</v>
+        <v>12.66629</v>
       </c>
       <c r="G92">
         <v>2.59</v>
@@ -8825,37 +8825,37 @@
         <v>0.529</v>
       </c>
       <c r="M92">
-        <v>2.95389018</v>
+        <v>2.986711182</v>
       </c>
       <c r="N92">
-        <v>-2.42489018</v>
+        <v>-2.457711182</v>
       </c>
       <c r="O92">
-        <v>-0.4122313306000001</v>
+        <v>-0.4178109009400001</v>
       </c>
       <c r="P92">
-        <v>-2.0126588494</v>
+        <v>-2.03990028106</v>
       </c>
       <c r="Q92">
-        <v>-1.8416588494</v>
+        <v>-1.86890028106</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>2.272314202142402</v>
+        <v>2.519704669047114</v>
       </c>
       <c r="T92">
-        <v>7.973859574803063</v>
+        <v>8.859843972003405</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03044459831610937</v>
+        <v>0.03011004229065762</v>
       </c>
       <c r="W92">
-        <v>0.2286211637170614</v>
+        <v>0.2287000520278629</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1790858724477021</v>
+        <v>0.1771178958273977</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.4348904675595955</v>
+        <v>0.4367904675595955</v>
       </c>
       <c r="C93">
-        <v>-3.202201404834046</v>
+        <v>-3.374795718786597</v>
       </c>
       <c r="D93">
-        <v>6.874088595165954</v>
+        <v>6.840684281213404</v>
       </c>
       <c r="E93">
-        <v>11.74729</v>
+        <v>11.88648</v>
       </c>
       <c r="F93">
-        <v>12.66629</v>
+        <v>12.80548</v>
       </c>
       <c r="G93">
         <v>2.59</v>
@@ -8907,37 +8907,37 @@
         <v>0.529</v>
       </c>
       <c r="M93">
-        <v>2.986711182</v>
+        <v>3.019532184</v>
       </c>
       <c r="N93">
-        <v>-2.457711182</v>
+        <v>-2.490532184000001</v>
       </c>
       <c r="O93">
-        <v>-0.4178109009400001</v>
+        <v>-0.4233904712800001</v>
       </c>
       <c r="P93">
-        <v>-2.03990028106</v>
+        <v>-2.06714171272</v>
       </c>
       <c r="Q93">
-        <v>-1.86890028106</v>
+        <v>-1.89614171272</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.519704669047114</v>
+        <v>2.828942752678004</v>
       </c>
       <c r="T93">
-        <v>8.859843972003405</v>
+        <v>9.967324468503833</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03011004229065762</v>
+        <v>0.0297827592222809</v>
       </c>
       <c r="W93">
-        <v>0.2287000520278629</v>
+        <v>0.2287772253753862</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1771178958273977</v>
+        <v>0.1751927013075347</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.4367904675595955</v>
+        <v>0.4386904675595955</v>
       </c>
       <c r="C94">
-        <v>-3.374795718786597</v>
+        <v>-3.54706694932659</v>
       </c>
       <c r="D94">
-        <v>6.840684281213404</v>
+        <v>6.80760305067341</v>
       </c>
       <c r="E94">
-        <v>11.88648</v>
+        <v>12.02567</v>
       </c>
       <c r="F94">
-        <v>12.80548</v>
+        <v>12.94467</v>
       </c>
       <c r="G94">
         <v>2.59</v>
@@ -8989,37 +8989,37 @@
         <v>0.529</v>
       </c>
       <c r="M94">
-        <v>3.019532184</v>
+        <v>3.052353186</v>
       </c>
       <c r="N94">
-        <v>-2.490532184000001</v>
+        <v>-2.523353186</v>
       </c>
       <c r="O94">
-        <v>-0.4233904712800001</v>
+        <v>-0.4289700416200001</v>
       </c>
       <c r="P94">
-        <v>-2.06714171272</v>
+        <v>-2.094383144380001</v>
       </c>
       <c r="Q94">
-        <v>-1.89614171272</v>
+        <v>-1.923383144380001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.828942752678004</v>
+        <v>3.226534574489147</v>
       </c>
       <c r="T94">
-        <v>9.967324468503833</v>
+        <v>11.39122796400438</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0297827592222809</v>
+        <v>0.02946251449946068</v>
       </c>
       <c r="W94">
-        <v>0.2287772253753862</v>
+        <v>0.2288527390810272</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1751927013075347</v>
+        <v>0.1733089088203569</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.4386904675595955</v>
+        <v>0.4405904675595954</v>
       </c>
       <c r="C95">
-        <v>-3.54706694932659</v>
+        <v>-3.719019761144803</v>
       </c>
       <c r="D95">
-        <v>6.80760305067341</v>
+        <v>6.774840238855197</v>
       </c>
       <c r="E95">
-        <v>12.02567</v>
+        <v>12.16486</v>
       </c>
       <c r="F95">
-        <v>12.94467</v>
+        <v>13.08386</v>
       </c>
       <c r="G95">
         <v>2.59</v>
@@ -9071,37 +9071,37 @@
         <v>0.529</v>
       </c>
       <c r="M95">
-        <v>3.052353186</v>
+        <v>3.085174188</v>
       </c>
       <c r="N95">
-        <v>-2.523353186</v>
+        <v>-2.556174188</v>
       </c>
       <c r="O95">
-        <v>-0.4289700416200001</v>
+        <v>-0.4345496119600001</v>
       </c>
       <c r="P95">
-        <v>-2.094383144380001</v>
+        <v>-2.12162457604</v>
       </c>
       <c r="Q95">
-        <v>-1.923383144380001</v>
+        <v>-1.950624576040001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>3.226534574489147</v>
+        <v>3.756657003570672</v>
       </c>
       <c r="T95">
-        <v>11.39122796400438</v>
+        <v>13.28976595800511</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02946251449946068</v>
+        <v>0.02914908349414727</v>
       </c>
       <c r="W95">
-        <v>0.2288527390810272</v>
+        <v>0.2289266461120801</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1733089088203569</v>
+        <v>0.1714651970243957</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.4405904675595954</v>
+        <v>0.4424904675595955</v>
       </c>
       <c r="C96">
-        <v>-3.719019761144803</v>
+        <v>-3.890658729563466</v>
       </c>
       <c r="D96">
-        <v>6.774840238855197</v>
+        <v>6.742391270436536</v>
       </c>
       <c r="E96">
-        <v>12.16486</v>
+        <v>12.30405</v>
       </c>
       <c r="F96">
-        <v>13.08386</v>
+        <v>13.22305</v>
       </c>
       <c r="G96">
         <v>2.59</v>
@@ -9153,37 +9153,37 @@
         <v>0.529</v>
       </c>
       <c r="M96">
-        <v>3.085174188</v>
+        <v>3.11799519</v>
       </c>
       <c r="N96">
-        <v>-2.556174188</v>
+        <v>-2.58899519</v>
       </c>
       <c r="O96">
-        <v>-0.4345496119600001</v>
+        <v>-0.4401291823000001</v>
       </c>
       <c r="P96">
-        <v>-2.12162457604</v>
+        <v>-2.1488660077</v>
       </c>
       <c r="Q96">
-        <v>-1.950624576040001</v>
+        <v>-1.9778660077</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.756657003570672</v>
+        <v>4.49882840428481</v>
       </c>
       <c r="T96">
-        <v>13.28976595800511</v>
+        <v>15.94771914960615</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02914908349414727</v>
+        <v>0.02884225103631414</v>
       </c>
       <c r="W96">
-        <v>0.2289266461120801</v>
+        <v>0.2289989972056372</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1714651970243957</v>
+        <v>0.1696603002136126</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.4424904675595955</v>
+        <v>0.4443904675595955</v>
       </c>
       <c r="C97">
-        <v>-3.890658729563466</v>
+        <v>-4.061988342666266</v>
       </c>
       <c r="D97">
-        <v>6.742391270436536</v>
+        <v>6.710251657333736</v>
       </c>
       <c r="E97">
-        <v>12.30405</v>
+        <v>12.44324</v>
       </c>
       <c r="F97">
-        <v>13.22305</v>
+        <v>13.36224</v>
       </c>
       <c r="G97">
         <v>2.59</v>
@@ -9235,37 +9235,37 @@
         <v>0.529</v>
       </c>
       <c r="M97">
-        <v>3.11799519</v>
+        <v>3.150816192000001</v>
       </c>
       <c r="N97">
-        <v>-2.58899519</v>
+        <v>-2.621816192000001</v>
       </c>
       <c r="O97">
-        <v>-0.4401291823000001</v>
+        <v>-0.4457087526400001</v>
       </c>
       <c r="P97">
-        <v>-2.1488660077</v>
+        <v>-2.17610743936</v>
       </c>
       <c r="Q97">
-        <v>-1.9778660077</v>
+        <v>-2.005107439360001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>4.49882840428481</v>
+        <v>5.612085505356015</v>
       </c>
       <c r="T97">
-        <v>15.94771914960615</v>
+        <v>19.93464893700769</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02884225103631414</v>
+        <v>0.02854181092135253</v>
       </c>
       <c r="W97">
-        <v>0.2289989972056372</v>
+        <v>0.2290698409847451</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1696603002136126</v>
+        <v>0.1678930054197207</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.4443904675595954</v>
+        <v>0.4462904675595954</v>
       </c>
       <c r="C98">
-        <v>-4.061988342666265</v>
+        <v>-4.233013003367736</v>
       </c>
       <c r="D98">
-        <v>6.710251657333736</v>
+        <v>6.678416996632264</v>
       </c>
       <c r="E98">
-        <v>12.44324</v>
+        <v>12.58243</v>
       </c>
       <c r="F98">
-        <v>13.36224</v>
+        <v>13.50143</v>
       </c>
       <c r="G98">
         <v>2.59</v>
@@ -9317,37 +9317,37 @@
         <v>0.529</v>
       </c>
       <c r="M98">
-        <v>3.150816192</v>
+        <v>3.183637194000001</v>
       </c>
       <c r="N98">
-        <v>-2.621816192</v>
+        <v>-2.654637194000001</v>
       </c>
       <c r="O98">
-        <v>-0.4457087526400001</v>
+        <v>-0.4512883229800002</v>
       </c>
       <c r="P98">
-        <v>-2.17610743936</v>
+        <v>-2.203348871020001</v>
       </c>
       <c r="Q98">
-        <v>-2.00510743936</v>
+        <v>-2.032348871020001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>5.612085505355999</v>
+        <v>7.467514007141334</v>
       </c>
       <c r="T98">
-        <v>19.93464893700763</v>
+        <v>26.57953191601019</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02854181092135253</v>
+        <v>0.02824756544793653</v>
       </c>
       <c r="W98">
-        <v>0.2290698409847451</v>
+        <v>0.2291392240673766</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1678930054197207</v>
+        <v>0.1661621496937442</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.4462904675595954</v>
+        <v>0.4481904675595955</v>
       </c>
       <c r="C99">
-        <v>-4.233013003367736</v>
+        <v>-4.403737031424011</v>
       </c>
       <c r="D99">
-        <v>6.678416996632264</v>
+        <v>6.646882968575989</v>
       </c>
       <c r="E99">
-        <v>12.58243</v>
+        <v>12.72162</v>
       </c>
       <c r="F99">
-        <v>13.50143</v>
+        <v>13.64062</v>
       </c>
       <c r="G99">
         <v>2.59</v>
@@ -9399,37 +9399,37 @@
         <v>0.529</v>
       </c>
       <c r="M99">
-        <v>3.183637194000001</v>
+        <v>3.216458196</v>
       </c>
       <c r="N99">
-        <v>-2.654637194000001</v>
+        <v>-2.687458196</v>
       </c>
       <c r="O99">
-        <v>-0.4512883229800002</v>
+        <v>-0.4568678933200001</v>
       </c>
       <c r="P99">
-        <v>-2.203348871020001</v>
+        <v>-2.23059030268</v>
       </c>
       <c r="Q99">
-        <v>-2.032348871020001</v>
+        <v>-2.05959030268</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>7.467514007141334</v>
+        <v>11.178371010712</v>
       </c>
       <c r="T99">
-        <v>26.57953191601019</v>
+        <v>39.86929787401527</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02824756544793653</v>
+        <v>0.02795932498418208</v>
       </c>
       <c r="W99">
-        <v>0.2291392240673766</v>
+        <v>0.2292071911687299</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1661621496937442</v>
+        <v>0.1644666175540122</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.4481904675595955</v>
+        <v>0.4500904675595955</v>
       </c>
       <c r="C100">
-        <v>-4.403737031424011</v>
+        <v>-4.574164665386856</v>
       </c>
       <c r="D100">
-        <v>6.646882968575989</v>
+        <v>6.615645334613144</v>
       </c>
       <c r="E100">
-        <v>12.72162</v>
+        <v>12.86081</v>
       </c>
       <c r="F100">
-        <v>13.64062</v>
+        <v>13.77981</v>
       </c>
       <c r="G100">
         <v>2.59</v>
@@ -9481,37 +9481,37 @@
         <v>0.529</v>
       </c>
       <c r="M100">
-        <v>3.216458196</v>
+        <v>3.249279198</v>
       </c>
       <c r="N100">
-        <v>-2.687458196</v>
+        <v>-2.720279198000001</v>
       </c>
       <c r="O100">
-        <v>-0.4568678933200001</v>
+        <v>-0.4624474636600001</v>
       </c>
       <c r="P100">
-        <v>-2.23059030268</v>
+        <v>-2.25783173434</v>
       </c>
       <c r="Q100">
-        <v>-2.05959030268</v>
+        <v>-2.08683173434</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>11.178371010712</v>
+        <v>22.310942021424</v>
       </c>
       <c r="T100">
-        <v>39.86929787401527</v>
+        <v>79.73859574803053</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02795932498418208</v>
+        <v>0.02767690756009943</v>
       </c>
       <c r="W100">
-        <v>0.2292071911687299</v>
+        <v>0.2292737851973286</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1644666175540122</v>
+        <v>0.1628053385888201</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.4500904675595955</v>
-      </c>
-      <c r="C101">
-        <v>-4.574164665386856</v>
-      </c>
-      <c r="D101">
-        <v>6.615645334613144</v>
-      </c>
-      <c r="E101">
-        <v>12.86081</v>
-      </c>
-      <c r="F101">
-        <v>13.77981</v>
-      </c>
-      <c r="G101">
-        <v>2.59</v>
-      </c>
-      <c r="H101">
-        <v>13</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.7</v>
-      </c>
-      <c r="K101">
-        <v>0.1709999999999999</v>
-      </c>
-      <c r="L101">
-        <v>0.529</v>
-      </c>
-      <c r="M101">
-        <v>3.249279198</v>
-      </c>
-      <c r="N101">
-        <v>-2.720279198000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.4624474636600001</v>
-      </c>
-      <c r="P101">
-        <v>-2.25783173434</v>
-      </c>
-      <c r="Q101">
-        <v>-2.08683173434</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>22.310942021424</v>
-      </c>
-      <c r="T101">
-        <v>79.73859574803053</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02767690756009943</v>
-      </c>
-      <c r="W101">
-        <v>0.2292737851973286</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1628053385888201</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
